--- a/data/corpus/corpus_multidominio_500_oraciones.xlsx
+++ b/data/corpus/corpus_multidominio_500_oraciones.xlsx
@@ -447,6 +447,19 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -716,7 +729,7 @@
     <row r="2" ht="27.75" customHeight="1" s="31">
       <c r="A2" s="56" t="inlineStr">
         <is>
-          <t>Recolección CERRADA y auditada. Los objetivos reflejan exactamente lo recolectado: 100 oraciones por dominio, 500 en total. El % de avance mide la ANOTACIÓN: arranca en 0% y sube a medida que se llena la columna 'direccion' de cada oración en la hoja 'Corpus - oraciones'.</t>
+          <t>Recolección CERRADA y auditada. Los objetivos reflejan exactamente lo recolectado: 100 oraciones por dominio, 500 en total. El % de avance mide la ANOTACIÓN: una oración cuenta como terminada solo cuando tiene las 9 categorías marcadas (TRUE o FALSE) y su 'direccion' definida.</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2319,7 @@
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>La oración. Toda oración revisada recibe exactamente una fila, incluso si todas las categorías quedan en FALSE: las oraciones neutras son tan necesarias como las sesgadas, no se omiten.</t>
+          <t>La oración. Toda oración revisada recibe exactamente una fila, incluso si todas las categorías quedan en FALSE: las oraciones neutras son tan necesarias como las sesgadas, no se omiten. Una fila se considera terminada cuando las 9 categorías están marcadas (TRUE o FALSE) y 'direccion' tiene valor.</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2379,7 @@
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Tablero de control por medio × dominio. 'Objetivo' = lo realmente recolectado (ya cerrado). 'Artículos de origen' indica de cuántos artículos distintos salieron esas oraciones. 'Oraciones ya anotadas' y el '% avance' se calculan solos: cuentan las oraciones que ya tienen 'direccion' llena, así que arrancan en 0% y llegan a 100% cuando se termina esa celda. Edite solo Estado (Pendiente / En progreso / Completo) y Notas.</t>
+          <t>Tablero de control por medio × dominio. 'Objetivo' = lo realmente recolectado (ya cerrado). 'Artículos de origen' indica de cuántos artículos distintos salieron esas oraciones. 'Oraciones ya anotadas' y el '% avance' se calculan solos: una oración cuenta como terminada únicamente cuando tiene sus 9 categorías marcadas (TRUE o FALSE) y su 'direccion' definida. Arrancan en 0% y llegan a 100% al cerrar la celda. Edite solo Estado y Notas.</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2427,7 @@
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Se llena SOLO si direccion != neutral; si direccion = neutral, déjelo vacío. Nueve opciones: Gobierno / Ejecutivo; Oposición / partidos políticos; Instituciones del Estado; Empresas y gremios; Sindicatos y organizaciones sociales; Ciudadanía afectada; Actores del deporte; Actor internacional; Otro / no identificable. Regla clave: anote el ROL institucional, no la persona (Petro como presidente → Gobierno / Ejecutivo; Néstor Lorenzo como DT → Actores del deporte).</t>
+          <t>Se llena SOLO si direccion != neutral; si direccion = neutral, déjelo vacío. Nueve opciones: Gobierno / Ejecutivo; Oposición / partidos políticos; Instituciones del Estado; Empresas y gremios; Sindicatos y organizaciones sociales; Ciudadanía afectada; Actores del deporte; Actor internacional; Otro / no identificable. Regla clave: anote el ROL institucional, no la persona (Petro como presidente → Gobierno / Ejecutivo; Néstor Lorenzo como DT → Actores del deporte). La celda se pinta en rojo si queda incoherente: con actor cuando la dirección es neutral, o sin actor cuando la dirección es favorece o perjudica.</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2764,7 @@
       <c r="AB5" s="68" t="n"/>
       <c r="AC5" s="69" t="n"/>
       <c r="AD5" s="70">
-        <f>IF(AND(COUNTIF($B$5:B5,B5)=1,$B5&lt;&gt;"",$AB5&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B5,B5)=1,$B5&lt;&gt;"",$AB5&lt;&gt;"",COUNTA($J5,$L5,$N5,$P5,$R5,$T5,$V5,$X5,$Z5)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE5" s="67" t="inlineStr">
@@ -2825,7 +2838,7 @@
       <c r="AB6" s="68" t="n"/>
       <c r="AC6" s="69" t="n"/>
       <c r="AD6" s="70">
-        <f>IF(AND(COUNTIF($B$5:B6,B6)=1,$B6&lt;&gt;"",$AB6&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B6,B6)=1,$B6&lt;&gt;"",$AB6&lt;&gt;"",COUNTA($J6,$L6,$N6,$P6,$R6,$T6,$V6,$X6,$Z6)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE6" s="67" t="inlineStr">
@@ -2895,7 +2908,7 @@
       <c r="AB7" s="68" t="n"/>
       <c r="AC7" s="69" t="n"/>
       <c r="AD7" s="70">
-        <f>IF(AND(COUNTIF($B$5:B7,B7)=1,$B7&lt;&gt;"",$AB7&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B7,B7)=1,$B7&lt;&gt;"",$AB7&lt;&gt;"",COUNTA($J7,$L7,$N7,$P7,$R7,$T7,$V7,$X7,$Z7)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE7" s="67" t="inlineStr">
@@ -2969,7 +2982,7 @@
       <c r="AB8" s="68" t="n"/>
       <c r="AC8" s="69" t="n"/>
       <c r="AD8" s="70">
-        <f>IF(AND(COUNTIF($B$5:B8,B8)=1,$B8&lt;&gt;"",$AB8&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B8,B8)=1,$B8&lt;&gt;"",$AB8&lt;&gt;"",COUNTA($J8,$L8,$N8,$P8,$R8,$T8,$V8,$X8,$Z8)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE8" s="67" t="inlineStr">
@@ -3047,7 +3060,7 @@
       <c r="AB9" s="68" t="n"/>
       <c r="AC9" s="69" t="n"/>
       <c r="AD9" s="70">
-        <f>IF(AND(COUNTIF($B$5:B9,B9)=1,$B9&lt;&gt;"",$AB9&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B9,B9)=1,$B9&lt;&gt;"",$AB9&lt;&gt;"",COUNTA($J9,$L9,$N9,$P9,$R9,$T9,$V9,$X9,$Z9)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE9" s="67" t="inlineStr">
@@ -3125,7 +3138,7 @@
       <c r="AB10" s="68" t="n"/>
       <c r="AC10" s="69" t="n"/>
       <c r="AD10" s="70">
-        <f>IF(AND(COUNTIF($B$5:B10,B10)=1,$B10&lt;&gt;"",$AB10&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B10,B10)=1,$B10&lt;&gt;"",$AB10&lt;&gt;"",COUNTA($J10,$L10,$N10,$P10,$R10,$T10,$V10,$X10,$Z10)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE10" s="67" t="inlineStr">
@@ -3203,7 +3216,7 @@
       <c r="AB11" s="68" t="n"/>
       <c r="AC11" s="69" t="n"/>
       <c r="AD11" s="70">
-        <f>IF(AND(COUNTIF($B$5:B11,B11)=1,$B11&lt;&gt;"",$AB11&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B11,B11)=1,$B11&lt;&gt;"",$AB11&lt;&gt;"",COUNTA($J11,$L11,$N11,$P11,$R11,$T11,$V11,$X11,$Z11)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE11" s="67" t="inlineStr">
@@ -3281,7 +3294,7 @@
       <c r="AB12" s="68" t="n"/>
       <c r="AC12" s="69" t="n"/>
       <c r="AD12" s="70">
-        <f>IF(AND(COUNTIF($B$5:B12,B12)=1,$B12&lt;&gt;"",$AB12&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B12,B12)=1,$B12&lt;&gt;"",$AB12&lt;&gt;"",COUNTA($J12,$L12,$N12,$P12,$R12,$T12,$V12,$X12,$Z12)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE12" s="67" t="inlineStr">
@@ -3355,7 +3368,7 @@
       <c r="AB13" s="68" t="n"/>
       <c r="AC13" s="69" t="n"/>
       <c r="AD13" s="70">
-        <f>IF(AND(COUNTIF($B$5:B13,B13)=1,$B13&lt;&gt;"",$AB13&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B13,B13)=1,$B13&lt;&gt;"",$AB13&lt;&gt;"",COUNTA($J13,$L13,$N13,$P13,$R13,$T13,$V13,$X13,$Z13)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE13" s="67" t="inlineStr">
@@ -3425,7 +3438,7 @@
       <c r="AB14" s="68" t="n"/>
       <c r="AC14" s="69" t="n"/>
       <c r="AD14" s="70">
-        <f>IF(AND(COUNTIF($B$5:B14,B14)=1,$B14&lt;&gt;"",$AB14&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B14,B14)=1,$B14&lt;&gt;"",$AB14&lt;&gt;"",COUNTA($J14,$L14,$N14,$P14,$R14,$T14,$V14,$X14,$Z14)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE14" s="67" t="inlineStr">
@@ -3495,7 +3508,7 @@
       <c r="AB15" s="68" t="n"/>
       <c r="AC15" s="69" t="n"/>
       <c r="AD15" s="70">
-        <f>IF(AND(COUNTIF($B$5:B15,B15)=1,$B15&lt;&gt;"",$AB15&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B15,B15)=1,$B15&lt;&gt;"",$AB15&lt;&gt;"",COUNTA($J15,$L15,$N15,$P15,$R15,$T15,$V15,$X15,$Z15)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE15" s="67" t="inlineStr">
@@ -3569,7 +3582,7 @@
       <c r="AB16" s="68" t="n"/>
       <c r="AC16" s="69" t="n"/>
       <c r="AD16" s="70">
-        <f>IF(AND(COUNTIF($B$5:B16,B16)=1,$B16&lt;&gt;"",$AB16&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B16,B16)=1,$B16&lt;&gt;"",$AB16&lt;&gt;"",COUNTA($J16,$L16,$N16,$P16,$R16,$T16,$V16,$X16,$Z16)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE16" s="67" t="inlineStr">
@@ -3643,7 +3656,7 @@
       <c r="AB17" s="68" t="n"/>
       <c r="AC17" s="69" t="n"/>
       <c r="AD17" s="70">
-        <f>IF(AND(COUNTIF($B$5:B17,B17)=1,$B17&lt;&gt;"",$AB17&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B17,B17)=1,$B17&lt;&gt;"",$AB17&lt;&gt;"",COUNTA($J17,$L17,$N17,$P17,$R17,$T17,$V17,$X17,$Z17)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE17" s="67" t="inlineStr">
@@ -3713,7 +3726,7 @@
       <c r="AB18" s="68" t="n"/>
       <c r="AC18" s="69" t="n"/>
       <c r="AD18" s="70">
-        <f>IF(AND(COUNTIF($B$5:B18,B18)=1,$B18&lt;&gt;"",$AB18&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B18,B18)=1,$B18&lt;&gt;"",$AB18&lt;&gt;"",COUNTA($J18,$L18,$N18,$P18,$R18,$T18,$V18,$X18,$Z18)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE18" s="67" t="inlineStr">
@@ -3787,7 +3800,7 @@
       <c r="AB19" s="68" t="n"/>
       <c r="AC19" s="69" t="n"/>
       <c r="AD19" s="70">
-        <f>IF(AND(COUNTIF($B$5:B19,B19)=1,$B19&lt;&gt;"",$AB19&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B19,B19)=1,$B19&lt;&gt;"",$AB19&lt;&gt;"",COUNTA($J19,$L19,$N19,$P19,$R19,$T19,$V19,$X19,$Z19)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE19" s="67" t="inlineStr">
@@ -3861,7 +3874,7 @@
       <c r="AB20" s="68" t="n"/>
       <c r="AC20" s="69" t="n"/>
       <c r="AD20" s="70">
-        <f>IF(AND(COUNTIF($B$5:B20,B20)=1,$B20&lt;&gt;"",$AB20&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B20,B20)=1,$B20&lt;&gt;"",$AB20&lt;&gt;"",COUNTA($J20,$L20,$N20,$P20,$R20,$T20,$V20,$X20,$Z20)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE20" s="67" t="inlineStr">
@@ -3931,7 +3944,7 @@
       <c r="AB21" s="68" t="n"/>
       <c r="AC21" s="69" t="n"/>
       <c r="AD21" s="70">
-        <f>IF(AND(COUNTIF($B$5:B21,B21)=1,$B21&lt;&gt;"",$AB21&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B21,B21)=1,$B21&lt;&gt;"",$AB21&lt;&gt;"",COUNTA($J21,$L21,$N21,$P21,$R21,$T21,$V21,$X21,$Z21)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE21" s="67" t="inlineStr">
@@ -4005,7 +4018,7 @@
       <c r="AB22" s="68" t="n"/>
       <c r="AC22" s="69" t="n"/>
       <c r="AD22" s="70">
-        <f>IF(AND(COUNTIF($B$5:B22,B22)=1,$B22&lt;&gt;"",$AB22&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B22,B22)=1,$B22&lt;&gt;"",$AB22&lt;&gt;"",COUNTA($J22,$L22,$N22,$P22,$R22,$T22,$V22,$X22,$Z22)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE22" s="67" t="inlineStr">
@@ -4079,7 +4092,7 @@
       <c r="AB23" s="68" t="n"/>
       <c r="AC23" s="69" t="n"/>
       <c r="AD23" s="70">
-        <f>IF(AND(COUNTIF($B$5:B23,B23)=1,$B23&lt;&gt;"",$AB23&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B23,B23)=1,$B23&lt;&gt;"",$AB23&lt;&gt;"",COUNTA($J23,$L23,$N23,$P23,$R23,$T23,$V23,$X23,$Z23)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE23" s="67" t="inlineStr">
@@ -4153,7 +4166,7 @@
       <c r="AB24" s="68" t="n"/>
       <c r="AC24" s="69" t="n"/>
       <c r="AD24" s="70">
-        <f>IF(AND(COUNTIF($B$5:B24,B24)=1,$B24&lt;&gt;"",$AB24&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B24,B24)=1,$B24&lt;&gt;"",$AB24&lt;&gt;"",COUNTA($J24,$L24,$N24,$P24,$R24,$T24,$V24,$X24,$Z24)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE24" s="67" t="inlineStr">
@@ -4227,7 +4240,7 @@
       <c r="AB25" s="68" t="n"/>
       <c r="AC25" s="69" t="n"/>
       <c r="AD25" s="70">
-        <f>IF(AND(COUNTIF($B$5:B25,B25)=1,$B25&lt;&gt;"",$AB25&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B25,B25)=1,$B25&lt;&gt;"",$AB25&lt;&gt;"",COUNTA($J25,$L25,$N25,$P25,$R25,$T25,$V25,$X25,$Z25)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE25" s="67" t="inlineStr">
@@ -4301,7 +4314,7 @@
       <c r="AB26" s="68" t="n"/>
       <c r="AC26" s="69" t="n"/>
       <c r="AD26" s="70">
-        <f>IF(AND(COUNTIF($B$5:B26,B26)=1,$B26&lt;&gt;"",$AB26&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B26,B26)=1,$B26&lt;&gt;"",$AB26&lt;&gt;"",COUNTA($J26,$L26,$N26,$P26,$R26,$T26,$V26,$X26,$Z26)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE26" s="67" t="inlineStr">
@@ -4375,7 +4388,7 @@
       <c r="AB27" s="68" t="n"/>
       <c r="AC27" s="69" t="n"/>
       <c r="AD27" s="70">
-        <f>IF(AND(COUNTIF($B$5:B27,B27)=1,$B27&lt;&gt;"",$AB27&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B27,B27)=1,$B27&lt;&gt;"",$AB27&lt;&gt;"",COUNTA($J27,$L27,$N27,$P27,$R27,$T27,$V27,$X27,$Z27)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE27" s="67" t="inlineStr">
@@ -4449,7 +4462,7 @@
       <c r="AB28" s="68" t="n"/>
       <c r="AC28" s="69" t="n"/>
       <c r="AD28" s="70">
-        <f>IF(AND(COUNTIF($B$5:B28,B28)=1,$B28&lt;&gt;"",$AB28&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B28,B28)=1,$B28&lt;&gt;"",$AB28&lt;&gt;"",COUNTA($J28,$L28,$N28,$P28,$R28,$T28,$V28,$X28,$Z28)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE28" s="67" t="inlineStr">
@@ -4527,7 +4540,7 @@
       <c r="AB29" s="68" t="n"/>
       <c r="AC29" s="69" t="n"/>
       <c r="AD29" s="70">
-        <f>IF(AND(COUNTIF($B$5:B29,B29)=1,$B29&lt;&gt;"",$AB29&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B29,B29)=1,$B29&lt;&gt;"",$AB29&lt;&gt;"",COUNTA($J29,$L29,$N29,$P29,$R29,$T29,$V29,$X29,$Z29)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE29" s="67" t="inlineStr">
@@ -4605,7 +4618,7 @@
       <c r="AB30" s="68" t="n"/>
       <c r="AC30" s="69" t="n"/>
       <c r="AD30" s="70">
-        <f>IF(AND(COUNTIF($B$5:B30,B30)=1,$B30&lt;&gt;"",$AB30&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B30,B30)=1,$B30&lt;&gt;"",$AB30&lt;&gt;"",COUNTA($J30,$L30,$N30,$P30,$R30,$T30,$V30,$X30,$Z30)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE30" s="67" t="inlineStr">
@@ -4683,7 +4696,7 @@
       <c r="AB31" s="68" t="n"/>
       <c r="AC31" s="69" t="n"/>
       <c r="AD31" s="70">
-        <f>IF(AND(COUNTIF($B$5:B31,B31)=1,$B31&lt;&gt;"",$AB31&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B31,B31)=1,$B31&lt;&gt;"",$AB31&lt;&gt;"",COUNTA($J31,$L31,$N31,$P31,$R31,$T31,$V31,$X31,$Z31)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE31" s="67" t="inlineStr">
@@ -4761,7 +4774,7 @@
       <c r="AB32" s="68" t="n"/>
       <c r="AC32" s="69" t="n"/>
       <c r="AD32" s="70">
-        <f>IF(AND(COUNTIF($B$5:B32,B32)=1,$B32&lt;&gt;"",$AB32&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B32,B32)=1,$B32&lt;&gt;"",$AB32&lt;&gt;"",COUNTA($J32,$L32,$N32,$P32,$R32,$T32,$V32,$X32,$Z32)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE32" s="67" t="inlineStr">
@@ -4835,7 +4848,7 @@
       <c r="AB33" s="68" t="n"/>
       <c r="AC33" s="69" t="n"/>
       <c r="AD33" s="70">
-        <f>IF(AND(COUNTIF($B$5:B33,B33)=1,$B33&lt;&gt;"",$AB33&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B33,B33)=1,$B33&lt;&gt;"",$AB33&lt;&gt;"",COUNTA($J33,$L33,$N33,$P33,$R33,$T33,$V33,$X33,$Z33)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE33" s="67" t="inlineStr">
@@ -4909,7 +4922,7 @@
       <c r="AB34" s="68" t="n"/>
       <c r="AC34" s="69" t="n"/>
       <c r="AD34" s="70">
-        <f>IF(AND(COUNTIF($B$5:B34,B34)=1,$B34&lt;&gt;"",$AB34&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B34,B34)=1,$B34&lt;&gt;"",$AB34&lt;&gt;"",COUNTA($J34,$L34,$N34,$P34,$R34,$T34,$V34,$X34,$Z34)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE34" s="67" t="inlineStr">
@@ -4987,7 +5000,7 @@
       <c r="AB35" s="68" t="n"/>
       <c r="AC35" s="69" t="n"/>
       <c r="AD35" s="70">
-        <f>IF(AND(COUNTIF($B$5:B35,B35)=1,$B35&lt;&gt;"",$AB35&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B35,B35)=1,$B35&lt;&gt;"",$AB35&lt;&gt;"",COUNTA($J35,$L35,$N35,$P35,$R35,$T35,$V35,$X35,$Z35)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE35" s="67" t="inlineStr">
@@ -5065,7 +5078,7 @@
       <c r="AB36" s="68" t="n"/>
       <c r="AC36" s="69" t="n"/>
       <c r="AD36" s="70">
-        <f>IF(AND(COUNTIF($B$5:B36,B36)=1,$B36&lt;&gt;"",$AB36&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B36,B36)=1,$B36&lt;&gt;"",$AB36&lt;&gt;"",COUNTA($J36,$L36,$N36,$P36,$R36,$T36,$V36,$X36,$Z36)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE36" s="67" t="inlineStr">
@@ -5143,7 +5156,7 @@
       <c r="AB37" s="68" t="n"/>
       <c r="AC37" s="69" t="n"/>
       <c r="AD37" s="70">
-        <f>IF(AND(COUNTIF($B$5:B37,B37)=1,$B37&lt;&gt;"",$AB37&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B37,B37)=1,$B37&lt;&gt;"",$AB37&lt;&gt;"",COUNTA($J37,$L37,$N37,$P37,$R37,$T37,$V37,$X37,$Z37)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE37" s="67" t="inlineStr">
@@ -5217,7 +5230,7 @@
       <c r="AB38" s="68" t="n"/>
       <c r="AC38" s="69" t="n"/>
       <c r="AD38" s="70">
-        <f>IF(AND(COUNTIF($B$5:B38,B38)=1,$B38&lt;&gt;"",$AB38&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B38,B38)=1,$B38&lt;&gt;"",$AB38&lt;&gt;"",COUNTA($J38,$L38,$N38,$P38,$R38,$T38,$V38,$X38,$Z38)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE38" s="67" t="inlineStr">
@@ -5291,7 +5304,7 @@
       <c r="AB39" s="68" t="n"/>
       <c r="AC39" s="69" t="n"/>
       <c r="AD39" s="70">
-        <f>IF(AND(COUNTIF($B$5:B39,B39)=1,$B39&lt;&gt;"",$AB39&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B39,B39)=1,$B39&lt;&gt;"",$AB39&lt;&gt;"",COUNTA($J39,$L39,$N39,$P39,$R39,$T39,$V39,$X39,$Z39)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE39" s="67" t="inlineStr">
@@ -5369,7 +5382,7 @@
       <c r="AB40" s="68" t="n"/>
       <c r="AC40" s="69" t="n"/>
       <c r="AD40" s="70">
-        <f>IF(AND(COUNTIF($B$5:B40,B40)=1,$B40&lt;&gt;"",$AB40&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B40,B40)=1,$B40&lt;&gt;"",$AB40&lt;&gt;"",COUNTA($J40,$L40,$N40,$P40,$R40,$T40,$V40,$X40,$Z40)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE40" s="67" t="inlineStr">
@@ -5447,7 +5460,7 @@
       <c r="AB41" s="68" t="n"/>
       <c r="AC41" s="69" t="n"/>
       <c r="AD41" s="70">
-        <f>IF(AND(COUNTIF($B$5:B41,B41)=1,$B41&lt;&gt;"",$AB41&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B41,B41)=1,$B41&lt;&gt;"",$AB41&lt;&gt;"",COUNTA($J41,$L41,$N41,$P41,$R41,$T41,$V41,$X41,$Z41)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE41" s="67" t="inlineStr">
@@ -5521,7 +5534,7 @@
       <c r="AB42" s="68" t="n"/>
       <c r="AC42" s="69" t="n"/>
       <c r="AD42" s="70">
-        <f>IF(AND(COUNTIF($B$5:B42,B42)=1,$B42&lt;&gt;"",$AB42&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B42,B42)=1,$B42&lt;&gt;"",$AB42&lt;&gt;"",COUNTA($J42,$L42,$N42,$P42,$R42,$T42,$V42,$X42,$Z42)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE42" s="67" t="inlineStr">
@@ -5595,7 +5608,7 @@
       <c r="AB43" s="68" t="n"/>
       <c r="AC43" s="69" t="n"/>
       <c r="AD43" s="70">
-        <f>IF(AND(COUNTIF($B$5:B43,B43)=1,$B43&lt;&gt;"",$AB43&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B43,B43)=1,$B43&lt;&gt;"",$AB43&lt;&gt;"",COUNTA($J43,$L43,$N43,$P43,$R43,$T43,$V43,$X43,$Z43)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE43" s="67" t="inlineStr">
@@ -5673,7 +5686,7 @@
       <c r="AB44" s="68" t="n"/>
       <c r="AC44" s="69" t="n"/>
       <c r="AD44" s="70">
-        <f>IF(AND(COUNTIF($B$5:B44,B44)=1,$B44&lt;&gt;"",$AB44&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B44,B44)=1,$B44&lt;&gt;"",$AB44&lt;&gt;"",COUNTA($J44,$L44,$N44,$P44,$R44,$T44,$V44,$X44,$Z44)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE44" s="67" t="inlineStr">
@@ -5751,7 +5764,7 @@
       <c r="AB45" s="68" t="n"/>
       <c r="AC45" s="69" t="n"/>
       <c r="AD45" s="70">
-        <f>IF(AND(COUNTIF($B$5:B45,B45)=1,$B45&lt;&gt;"",$AB45&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B45,B45)=1,$B45&lt;&gt;"",$AB45&lt;&gt;"",COUNTA($J45,$L45,$N45,$P45,$R45,$T45,$V45,$X45,$Z45)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE45" s="67" t="inlineStr">
@@ -5829,7 +5842,7 @@
       <c r="AB46" s="68" t="n"/>
       <c r="AC46" s="69" t="n"/>
       <c r="AD46" s="70">
-        <f>IF(AND(COUNTIF($B$5:B46,B46)=1,$B46&lt;&gt;"",$AB46&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B46,B46)=1,$B46&lt;&gt;"",$AB46&lt;&gt;"",COUNTA($J46,$L46,$N46,$P46,$R46,$T46,$V46,$X46,$Z46)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE46" s="67" t="inlineStr">
@@ -5907,7 +5920,7 @@
       <c r="AB47" s="68" t="n"/>
       <c r="AC47" s="69" t="n"/>
       <c r="AD47" s="70">
-        <f>IF(AND(COUNTIF($B$5:B47,B47)=1,$B47&lt;&gt;"",$AB47&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B47,B47)=1,$B47&lt;&gt;"",$AB47&lt;&gt;"",COUNTA($J47,$L47,$N47,$P47,$R47,$T47,$V47,$X47,$Z47)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE47" s="67" t="inlineStr">
@@ -5981,7 +5994,7 @@
       <c r="AB48" s="68" t="n"/>
       <c r="AC48" s="69" t="n"/>
       <c r="AD48" s="70">
-        <f>IF(AND(COUNTIF($B$5:B48,B48)=1,$B48&lt;&gt;"",$AB48&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B48,B48)=1,$B48&lt;&gt;"",$AB48&lt;&gt;"",COUNTA($J48,$L48,$N48,$P48,$R48,$T48,$V48,$X48,$Z48)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE48" s="67" t="inlineStr">
@@ -6055,7 +6068,7 @@
       <c r="AB49" s="68" t="n"/>
       <c r="AC49" s="69" t="n"/>
       <c r="AD49" s="70">
-        <f>IF(AND(COUNTIF($B$5:B49,B49)=1,$B49&lt;&gt;"",$AB49&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B49,B49)=1,$B49&lt;&gt;"",$AB49&lt;&gt;"",COUNTA($J49,$L49,$N49,$P49,$R49,$T49,$V49,$X49,$Z49)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE49" s="67" t="inlineStr">
@@ -6133,7 +6146,7 @@
       <c r="AB50" s="68" t="n"/>
       <c r="AC50" s="69" t="n"/>
       <c r="AD50" s="70">
-        <f>IF(AND(COUNTIF($B$5:B50,B50)=1,$B50&lt;&gt;"",$AB50&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B50,B50)=1,$B50&lt;&gt;"",$AB50&lt;&gt;"",COUNTA($J50,$L50,$N50,$P50,$R50,$T50,$V50,$X50,$Z50)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE50" s="67" t="inlineStr">
@@ -6211,7 +6224,7 @@
       <c r="AB51" s="68" t="n"/>
       <c r="AC51" s="69" t="n"/>
       <c r="AD51" s="70">
-        <f>IF(AND(COUNTIF($B$5:B51,B51)=1,$B51&lt;&gt;"",$AB51&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B51,B51)=1,$B51&lt;&gt;"",$AB51&lt;&gt;"",COUNTA($J51,$L51,$N51,$P51,$R51,$T51,$V51,$X51,$Z51)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE51" s="67" t="inlineStr">
@@ -6289,7 +6302,7 @@
       <c r="AB52" s="68" t="n"/>
       <c r="AC52" s="69" t="n"/>
       <c r="AD52" s="70">
-        <f>IF(AND(COUNTIF($B$5:B52,B52)=1,$B52&lt;&gt;"",$AB52&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B52,B52)=1,$B52&lt;&gt;"",$AB52&lt;&gt;"",COUNTA($J52,$L52,$N52,$P52,$R52,$T52,$V52,$X52,$Z52)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE52" s="67" t="inlineStr">
@@ -6363,7 +6376,7 @@
       <c r="AB53" s="68" t="n"/>
       <c r="AC53" s="69" t="n"/>
       <c r="AD53" s="70">
-        <f>IF(AND(COUNTIF($B$5:B53,B53)=1,$B53&lt;&gt;"",$AB53&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B53,B53)=1,$B53&lt;&gt;"",$AB53&lt;&gt;"",COUNTA($J53,$L53,$N53,$P53,$R53,$T53,$V53,$X53,$Z53)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE53" s="67" t="inlineStr">
@@ -6433,7 +6446,7 @@
       <c r="AB54" s="68" t="n"/>
       <c r="AC54" s="69" t="n"/>
       <c r="AD54" s="70">
-        <f>IF(AND(COUNTIF($B$5:B54,B54)=1,$B54&lt;&gt;"",$AB54&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B54,B54)=1,$B54&lt;&gt;"",$AB54&lt;&gt;"",COUNTA($J54,$L54,$N54,$P54,$R54,$T54,$V54,$X54,$Z54)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE54" s="67" t="inlineStr">
@@ -6503,7 +6516,7 @@
       <c r="AB55" s="68" t="n"/>
       <c r="AC55" s="69" t="n"/>
       <c r="AD55" s="70">
-        <f>IF(AND(COUNTIF($B$5:B55,B55)=1,$B55&lt;&gt;"",$AB55&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B55,B55)=1,$B55&lt;&gt;"",$AB55&lt;&gt;"",COUNTA($J55,$L55,$N55,$P55,$R55,$T55,$V55,$X55,$Z55)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE55" s="67" t="inlineStr">
@@ -6573,7 +6586,7 @@
       <c r="AB56" s="68" t="n"/>
       <c r="AC56" s="69" t="n"/>
       <c r="AD56" s="70">
-        <f>IF(AND(COUNTIF($B$5:B56,B56)=1,$B56&lt;&gt;"",$AB56&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B56,B56)=1,$B56&lt;&gt;"",$AB56&lt;&gt;"",COUNTA($J56,$L56,$N56,$P56,$R56,$T56,$V56,$X56,$Z56)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE56" s="67" t="inlineStr">
@@ -6643,7 +6656,7 @@
       <c r="AB57" s="68" t="n"/>
       <c r="AC57" s="69" t="n"/>
       <c r="AD57" s="70">
-        <f>IF(AND(COUNTIF($B$5:B57,B57)=1,$B57&lt;&gt;"",$AB57&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B57,B57)=1,$B57&lt;&gt;"",$AB57&lt;&gt;"",COUNTA($J57,$L57,$N57,$P57,$R57,$T57,$V57,$X57,$Z57)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE57" s="67" t="inlineStr">
@@ -6713,7 +6726,7 @@
       <c r="AB58" s="68" t="n"/>
       <c r="AC58" s="69" t="n"/>
       <c r="AD58" s="70">
-        <f>IF(AND(COUNTIF($B$5:B58,B58)=1,$B58&lt;&gt;"",$AB58&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B58,B58)=1,$B58&lt;&gt;"",$AB58&lt;&gt;"",COUNTA($J58,$L58,$N58,$P58,$R58,$T58,$V58,$X58,$Z58)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE58" s="67" t="inlineStr">
@@ -6783,7 +6796,7 @@
       <c r="AB59" s="68" t="n"/>
       <c r="AC59" s="69" t="n"/>
       <c r="AD59" s="70">
-        <f>IF(AND(COUNTIF($B$5:B59,B59)=1,$B59&lt;&gt;"",$AB59&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B59,B59)=1,$B59&lt;&gt;"",$AB59&lt;&gt;"",COUNTA($J59,$L59,$N59,$P59,$R59,$T59,$V59,$X59,$Z59)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE59" s="67" t="inlineStr">
@@ -6853,7 +6866,7 @@
       <c r="AB60" s="68" t="n"/>
       <c r="AC60" s="69" t="n"/>
       <c r="AD60" s="70">
-        <f>IF(AND(COUNTIF($B$5:B60,B60)=1,$B60&lt;&gt;"",$AB60&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B60,B60)=1,$B60&lt;&gt;"",$AB60&lt;&gt;"",COUNTA($J60,$L60,$N60,$P60,$R60,$T60,$V60,$X60,$Z60)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE60" s="67" t="inlineStr">
@@ -6923,7 +6936,7 @@
       <c r="AB61" s="68" t="n"/>
       <c r="AC61" s="69" t="n"/>
       <c r="AD61" s="70">
-        <f>IF(AND(COUNTIF($B$5:B61,B61)=1,$B61&lt;&gt;"",$AB61&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B61,B61)=1,$B61&lt;&gt;"",$AB61&lt;&gt;"",COUNTA($J61,$L61,$N61,$P61,$R61,$T61,$V61,$X61,$Z61)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE61" s="67" t="inlineStr">
@@ -6993,7 +7006,7 @@
       <c r="AB62" s="68" t="n"/>
       <c r="AC62" s="69" t="n"/>
       <c r="AD62" s="70">
-        <f>IF(AND(COUNTIF($B$5:B62,B62)=1,$B62&lt;&gt;"",$AB62&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B62,B62)=1,$B62&lt;&gt;"",$AB62&lt;&gt;"",COUNTA($J62,$L62,$N62,$P62,$R62,$T62,$V62,$X62,$Z62)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE62" s="67" t="inlineStr">
@@ -7063,7 +7076,7 @@
       <c r="AB63" s="68" t="n"/>
       <c r="AC63" s="69" t="n"/>
       <c r="AD63" s="70">
-        <f>IF(AND(COUNTIF($B$5:B63,B63)=1,$B63&lt;&gt;"",$AB63&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B63,B63)=1,$B63&lt;&gt;"",$AB63&lt;&gt;"",COUNTA($J63,$L63,$N63,$P63,$R63,$T63,$V63,$X63,$Z63)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE63" s="67" t="inlineStr">
@@ -7133,7 +7146,7 @@
       <c r="AB64" s="68" t="n"/>
       <c r="AC64" s="69" t="n"/>
       <c r="AD64" s="70">
-        <f>IF(AND(COUNTIF($B$5:B64,B64)=1,$B64&lt;&gt;"",$AB64&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B64,B64)=1,$B64&lt;&gt;"",$AB64&lt;&gt;"",COUNTA($J64,$L64,$N64,$P64,$R64,$T64,$V64,$X64,$Z64)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE64" s="67" t="inlineStr">
@@ -7207,7 +7220,7 @@
       <c r="AB65" s="68" t="n"/>
       <c r="AC65" s="69" t="n"/>
       <c r="AD65" s="70">
-        <f>IF(AND(COUNTIF($B$5:B65,B65)=1,$B65&lt;&gt;"",$AB65&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B65,B65)=1,$B65&lt;&gt;"",$AB65&lt;&gt;"",COUNTA($J65,$L65,$N65,$P65,$R65,$T65,$V65,$X65,$Z65)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE65" s="67" t="inlineStr">
@@ -7285,7 +7298,7 @@
       <c r="AB66" s="68" t="n"/>
       <c r="AC66" s="69" t="n"/>
       <c r="AD66" s="70">
-        <f>IF(AND(COUNTIF($B$5:B66,B66)=1,$B66&lt;&gt;"",$AB66&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B66,B66)=1,$B66&lt;&gt;"",$AB66&lt;&gt;"",COUNTA($J66,$L66,$N66,$P66,$R66,$T66,$V66,$X66,$Z66)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE66" s="67" t="inlineStr">
@@ -7363,7 +7376,7 @@
       <c r="AB67" s="68" t="n"/>
       <c r="AC67" s="69" t="n"/>
       <c r="AD67" s="70">
-        <f>IF(AND(COUNTIF($B$5:B67,B67)=1,$B67&lt;&gt;"",$AB67&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B67,B67)=1,$B67&lt;&gt;"",$AB67&lt;&gt;"",COUNTA($J67,$L67,$N67,$P67,$R67,$T67,$V67,$X67,$Z67)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE67" s="67" t="inlineStr">
@@ -7441,7 +7454,7 @@
       <c r="AB68" s="68" t="n"/>
       <c r="AC68" s="69" t="n"/>
       <c r="AD68" s="70">
-        <f>IF(AND(COUNTIF($B$5:B68,B68)=1,$B68&lt;&gt;"",$AB68&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B68,B68)=1,$B68&lt;&gt;"",$AB68&lt;&gt;"",COUNTA($J68,$L68,$N68,$P68,$R68,$T68,$V68,$X68,$Z68)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE68" s="67" t="inlineStr">
@@ -7519,7 +7532,7 @@
       <c r="AB69" s="68" t="n"/>
       <c r="AC69" s="69" t="n"/>
       <c r="AD69" s="70">
-        <f>IF(AND(COUNTIF($B$5:B69,B69)=1,$B69&lt;&gt;"",$AB69&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B69,B69)=1,$B69&lt;&gt;"",$AB69&lt;&gt;"",COUNTA($J69,$L69,$N69,$P69,$R69,$T69,$V69,$X69,$Z69)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE69" s="67" t="inlineStr">
@@ -7597,7 +7610,7 @@
       <c r="AB70" s="68" t="n"/>
       <c r="AC70" s="69" t="n"/>
       <c r="AD70" s="70">
-        <f>IF(AND(COUNTIF($B$5:B70,B70)=1,$B70&lt;&gt;"",$AB70&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B70,B70)=1,$B70&lt;&gt;"",$AB70&lt;&gt;"",COUNTA($J70,$L70,$N70,$P70,$R70,$T70,$V70,$X70,$Z70)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE70" s="67" t="inlineStr">
@@ -7675,7 +7688,7 @@
       <c r="AB71" s="68" t="n"/>
       <c r="AC71" s="69" t="n"/>
       <c r="AD71" s="70">
-        <f>IF(AND(COUNTIF($B$5:B71,B71)=1,$B71&lt;&gt;"",$AB71&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B71,B71)=1,$B71&lt;&gt;"",$AB71&lt;&gt;"",COUNTA($J71,$L71,$N71,$P71,$R71,$T71,$V71,$X71,$Z71)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE71" s="67" t="inlineStr">
@@ -7753,7 +7766,7 @@
       <c r="AB72" s="68" t="n"/>
       <c r="AC72" s="69" t="n"/>
       <c r="AD72" s="70">
-        <f>IF(AND(COUNTIF($B$5:B72,B72)=1,$B72&lt;&gt;"",$AB72&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B72,B72)=1,$B72&lt;&gt;"",$AB72&lt;&gt;"",COUNTA($J72,$L72,$N72,$P72,$R72,$T72,$V72,$X72,$Z72)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE72" s="67" t="inlineStr">
@@ -7831,7 +7844,7 @@
       <c r="AB73" s="68" t="n"/>
       <c r="AC73" s="69" t="n"/>
       <c r="AD73" s="70">
-        <f>IF(AND(COUNTIF($B$5:B73,B73)=1,$B73&lt;&gt;"",$AB73&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B73,B73)=1,$B73&lt;&gt;"",$AB73&lt;&gt;"",COUNTA($J73,$L73,$N73,$P73,$R73,$T73,$V73,$X73,$Z73)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE73" s="67" t="inlineStr">
@@ -7905,7 +7918,7 @@
       <c r="AB74" s="68" t="n"/>
       <c r="AC74" s="69" t="n"/>
       <c r="AD74" s="70">
-        <f>IF(AND(COUNTIF($B$5:B74,B74)=1,$B74&lt;&gt;"",$AB74&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B74,B74)=1,$B74&lt;&gt;"",$AB74&lt;&gt;"",COUNTA($J74,$L74,$N74,$P74,$R74,$T74,$V74,$X74,$Z74)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE74" s="67" t="inlineStr">
@@ -7979,7 +7992,7 @@
       <c r="AB75" s="68" t="n"/>
       <c r="AC75" s="69" t="n"/>
       <c r="AD75" s="70">
-        <f>IF(AND(COUNTIF($B$5:B75,B75)=1,$B75&lt;&gt;"",$AB75&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B75,B75)=1,$B75&lt;&gt;"",$AB75&lt;&gt;"",COUNTA($J75,$L75,$N75,$P75,$R75,$T75,$V75,$X75,$Z75)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE75" s="67" t="inlineStr">
@@ -8057,7 +8070,7 @@
       <c r="AB76" s="68" t="n"/>
       <c r="AC76" s="69" t="n"/>
       <c r="AD76" s="70">
-        <f>IF(AND(COUNTIF($B$5:B76,B76)=1,$B76&lt;&gt;"",$AB76&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B76,B76)=1,$B76&lt;&gt;"",$AB76&lt;&gt;"",COUNTA($J76,$L76,$N76,$P76,$R76,$T76,$V76,$X76,$Z76)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE76" s="67" t="inlineStr">
@@ -8135,7 +8148,7 @@
       <c r="AB77" s="68" t="n"/>
       <c r="AC77" s="69" t="n"/>
       <c r="AD77" s="70">
-        <f>IF(AND(COUNTIF($B$5:B77,B77)=1,$B77&lt;&gt;"",$AB77&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B77,B77)=1,$B77&lt;&gt;"",$AB77&lt;&gt;"",COUNTA($J77,$L77,$N77,$P77,$R77,$T77,$V77,$X77,$Z77)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE77" s="67" t="inlineStr">
@@ -8213,7 +8226,7 @@
       <c r="AB78" s="68" t="n"/>
       <c r="AC78" s="69" t="n"/>
       <c r="AD78" s="70">
-        <f>IF(AND(COUNTIF($B$5:B78,B78)=1,$B78&lt;&gt;"",$AB78&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B78,B78)=1,$B78&lt;&gt;"",$AB78&lt;&gt;"",COUNTA($J78,$L78,$N78,$P78,$R78,$T78,$V78,$X78,$Z78)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE78" s="67" t="inlineStr">
@@ -8291,7 +8304,7 @@
       <c r="AB79" s="68" t="n"/>
       <c r="AC79" s="69" t="n"/>
       <c r="AD79" s="70">
-        <f>IF(AND(COUNTIF($B$5:B79,B79)=1,$B79&lt;&gt;"",$AB79&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B79,B79)=1,$B79&lt;&gt;"",$AB79&lt;&gt;"",COUNTA($J79,$L79,$N79,$P79,$R79,$T79,$V79,$X79,$Z79)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE79" s="67" t="inlineStr">
@@ -8369,7 +8382,7 @@
       <c r="AB80" s="68" t="n"/>
       <c r="AC80" s="69" t="n"/>
       <c r="AD80" s="70">
-        <f>IF(AND(COUNTIF($B$5:B80,B80)=1,$B80&lt;&gt;"",$AB80&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B80,B80)=1,$B80&lt;&gt;"",$AB80&lt;&gt;"",COUNTA($J80,$L80,$N80,$P80,$R80,$T80,$V80,$X80,$Z80)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE80" s="67" t="inlineStr">
@@ -8447,7 +8460,7 @@
       <c r="AB81" s="68" t="n"/>
       <c r="AC81" s="69" t="n"/>
       <c r="AD81" s="70">
-        <f>IF(AND(COUNTIF($B$5:B81,B81)=1,$B81&lt;&gt;"",$AB81&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B81,B81)=1,$B81&lt;&gt;"",$AB81&lt;&gt;"",COUNTA($J81,$L81,$N81,$P81,$R81,$T81,$V81,$X81,$Z81)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE81" s="67" t="inlineStr">
@@ -8525,7 +8538,7 @@
       <c r="AB82" s="68" t="n"/>
       <c r="AC82" s="69" t="n"/>
       <c r="AD82" s="70">
-        <f>IF(AND(COUNTIF($B$5:B82,B82)=1,$B82&lt;&gt;"",$AB82&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B82,B82)=1,$B82&lt;&gt;"",$AB82&lt;&gt;"",COUNTA($J82,$L82,$N82,$P82,$R82,$T82,$V82,$X82,$Z82)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE82" s="67" t="inlineStr">
@@ -8603,7 +8616,7 @@
       <c r="AB83" s="68" t="n"/>
       <c r="AC83" s="69" t="n"/>
       <c r="AD83" s="70">
-        <f>IF(AND(COUNTIF($B$5:B83,B83)=1,$B83&lt;&gt;"",$AB83&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B83,B83)=1,$B83&lt;&gt;"",$AB83&lt;&gt;"",COUNTA($J83,$L83,$N83,$P83,$R83,$T83,$V83,$X83,$Z83)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE83" s="67" t="inlineStr">
@@ -8677,7 +8690,7 @@
       <c r="AB84" s="68" t="n"/>
       <c r="AC84" s="69" t="n"/>
       <c r="AD84" s="70">
-        <f>IF(AND(COUNTIF($B$5:B84,B84)=1,$B84&lt;&gt;"",$AB84&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B84,B84)=1,$B84&lt;&gt;"",$AB84&lt;&gt;"",COUNTA($J84,$L84,$N84,$P84,$R84,$T84,$V84,$X84,$Z84)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE84" s="67" t="inlineStr">
@@ -8751,7 +8764,7 @@
       <c r="AB85" s="68" t="n"/>
       <c r="AC85" s="69" t="n"/>
       <c r="AD85" s="70">
-        <f>IF(AND(COUNTIF($B$5:B85,B85)=1,$B85&lt;&gt;"",$AB85&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B85,B85)=1,$B85&lt;&gt;"",$AB85&lt;&gt;"",COUNTA($J85,$L85,$N85,$P85,$R85,$T85,$V85,$X85,$Z85)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE85" s="67" t="inlineStr">
@@ -8829,7 +8842,7 @@
       <c r="AB86" s="68" t="n"/>
       <c r="AC86" s="69" t="n"/>
       <c r="AD86" s="70">
-        <f>IF(AND(COUNTIF($B$5:B86,B86)=1,$B86&lt;&gt;"",$AB86&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B86,B86)=1,$B86&lt;&gt;"",$AB86&lt;&gt;"",COUNTA($J86,$L86,$N86,$P86,$R86,$T86,$V86,$X86,$Z86)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE86" s="67" t="inlineStr">
@@ -8907,7 +8920,7 @@
       <c r="AB87" s="68" t="n"/>
       <c r="AC87" s="69" t="n"/>
       <c r="AD87" s="70">
-        <f>IF(AND(COUNTIF($B$5:B87,B87)=1,$B87&lt;&gt;"",$AB87&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B87,B87)=1,$B87&lt;&gt;"",$AB87&lt;&gt;"",COUNTA($J87,$L87,$N87,$P87,$R87,$T87,$V87,$X87,$Z87)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE87" s="67" t="inlineStr">
@@ -8985,7 +8998,7 @@
       <c r="AB88" s="68" t="n"/>
       <c r="AC88" s="69" t="n"/>
       <c r="AD88" s="70">
-        <f>IF(AND(COUNTIF($B$5:B88,B88)=1,$B88&lt;&gt;"",$AB88&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B88,B88)=1,$B88&lt;&gt;"",$AB88&lt;&gt;"",COUNTA($J88,$L88,$N88,$P88,$R88,$T88,$V88,$X88,$Z88)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE88" s="67" t="inlineStr">
@@ -9063,7 +9076,7 @@
       <c r="AB89" s="68" t="n"/>
       <c r="AC89" s="69" t="n"/>
       <c r="AD89" s="70">
-        <f>IF(AND(COUNTIF($B$5:B89,B89)=1,$B89&lt;&gt;"",$AB89&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B89,B89)=1,$B89&lt;&gt;"",$AB89&lt;&gt;"",COUNTA($J89,$L89,$N89,$P89,$R89,$T89,$V89,$X89,$Z89)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE89" s="67" t="inlineStr">
@@ -9141,7 +9154,7 @@
       <c r="AB90" s="68" t="n"/>
       <c r="AC90" s="69" t="n"/>
       <c r="AD90" s="70">
-        <f>IF(AND(COUNTIF($B$5:B90,B90)=1,$B90&lt;&gt;"",$AB90&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B90,B90)=1,$B90&lt;&gt;"",$AB90&lt;&gt;"",COUNTA($J90,$L90,$N90,$P90,$R90,$T90,$V90,$X90,$Z90)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE90" s="67" t="inlineStr">
@@ -9219,7 +9232,7 @@
       <c r="AB91" s="68" t="n"/>
       <c r="AC91" s="69" t="n"/>
       <c r="AD91" s="70">
-        <f>IF(AND(COUNTIF($B$5:B91,B91)=1,$B91&lt;&gt;"",$AB91&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B91,B91)=1,$B91&lt;&gt;"",$AB91&lt;&gt;"",COUNTA($J91,$L91,$N91,$P91,$R91,$T91,$V91,$X91,$Z91)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE91" s="67" t="inlineStr">
@@ -9297,7 +9310,7 @@
       <c r="AB92" s="68" t="n"/>
       <c r="AC92" s="69" t="n"/>
       <c r="AD92" s="70">
-        <f>IF(AND(COUNTIF($B$5:B92,B92)=1,$B92&lt;&gt;"",$AB92&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B92,B92)=1,$B92&lt;&gt;"",$AB92&lt;&gt;"",COUNTA($J92,$L92,$N92,$P92,$R92,$T92,$V92,$X92,$Z92)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE92" s="67" t="inlineStr">
@@ -9375,7 +9388,7 @@
       <c r="AB93" s="68" t="n"/>
       <c r="AC93" s="69" t="n"/>
       <c r="AD93" s="70">
-        <f>IF(AND(COUNTIF($B$5:B93,B93)=1,$B93&lt;&gt;"",$AB93&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B93,B93)=1,$B93&lt;&gt;"",$AB93&lt;&gt;"",COUNTA($J93,$L93,$N93,$P93,$R93,$T93,$V93,$X93,$Z93)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE93" s="67" t="inlineStr">
@@ -9449,7 +9462,7 @@
       <c r="AB94" s="68" t="n"/>
       <c r="AC94" s="69" t="n"/>
       <c r="AD94" s="70">
-        <f>IF(AND(COUNTIF($B$5:B94,B94)=1,$B94&lt;&gt;"",$AB94&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B94,B94)=1,$B94&lt;&gt;"",$AB94&lt;&gt;"",COUNTA($J94,$L94,$N94,$P94,$R94,$T94,$V94,$X94,$Z94)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE94" s="67" t="inlineStr">
@@ -9523,7 +9536,7 @@
       <c r="AB95" s="68" t="n"/>
       <c r="AC95" s="69" t="n"/>
       <c r="AD95" s="70">
-        <f>IF(AND(COUNTIF($B$5:B95,B95)=1,$B95&lt;&gt;"",$AB95&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B95,B95)=1,$B95&lt;&gt;"",$AB95&lt;&gt;"",COUNTA($J95,$L95,$N95,$P95,$R95,$T95,$V95,$X95,$Z95)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE95" s="67" t="inlineStr">
@@ -9601,7 +9614,7 @@
       <c r="AB96" s="68" t="n"/>
       <c r="AC96" s="69" t="n"/>
       <c r="AD96" s="70">
-        <f>IF(AND(COUNTIF($B$5:B96,B96)=1,$B96&lt;&gt;"",$AB96&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B96,B96)=1,$B96&lt;&gt;"",$AB96&lt;&gt;"",COUNTA($J96,$L96,$N96,$P96,$R96,$T96,$V96,$X96,$Z96)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE96" s="67" t="inlineStr">
@@ -9679,7 +9692,7 @@
       <c r="AB97" s="68" t="n"/>
       <c r="AC97" s="69" t="n"/>
       <c r="AD97" s="70">
-        <f>IF(AND(COUNTIF($B$5:B97,B97)=1,$B97&lt;&gt;"",$AB97&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B97,B97)=1,$B97&lt;&gt;"",$AB97&lt;&gt;"",COUNTA($J97,$L97,$N97,$P97,$R97,$T97,$V97,$X97,$Z97)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE97" s="67" t="inlineStr">
@@ -9757,7 +9770,7 @@
       <c r="AB98" s="68" t="n"/>
       <c r="AC98" s="69" t="n"/>
       <c r="AD98" s="70">
-        <f>IF(AND(COUNTIF($B$5:B98,B98)=1,$B98&lt;&gt;"",$AB98&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B98,B98)=1,$B98&lt;&gt;"",$AB98&lt;&gt;"",COUNTA($J98,$L98,$N98,$P98,$R98,$T98,$V98,$X98,$Z98)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE98" s="67" t="inlineStr">
@@ -9835,7 +9848,7 @@
       <c r="AB99" s="68" t="n"/>
       <c r="AC99" s="69" t="n"/>
       <c r="AD99" s="70">
-        <f>IF(AND(COUNTIF($B$5:B99,B99)=1,$B99&lt;&gt;"",$AB99&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B99,B99)=1,$B99&lt;&gt;"",$AB99&lt;&gt;"",COUNTA($J99,$L99,$N99,$P99,$R99,$T99,$V99,$X99,$Z99)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE99" s="67" t="inlineStr">
@@ -9913,7 +9926,7 @@
       <c r="AB100" s="68" t="n"/>
       <c r="AC100" s="69" t="n"/>
       <c r="AD100" s="70">
-        <f>IF(AND(COUNTIF($B$5:B100,B100)=1,$B100&lt;&gt;"",$AB100&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B100,B100)=1,$B100&lt;&gt;"",$AB100&lt;&gt;"",COUNTA($J100,$L100,$N100,$P100,$R100,$T100,$V100,$X100,$Z100)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE100" s="67" t="inlineStr">
@@ -9991,7 +10004,7 @@
       <c r="AB101" s="68" t="n"/>
       <c r="AC101" s="69" t="n"/>
       <c r="AD101" s="70">
-        <f>IF(AND(COUNTIF($B$5:B101,B101)=1,$B101&lt;&gt;"",$AB101&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B101,B101)=1,$B101&lt;&gt;"",$AB101&lt;&gt;"",COUNTA($J101,$L101,$N101,$P101,$R101,$T101,$V101,$X101,$Z101)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE101" s="67" t="inlineStr">
@@ -10069,7 +10082,7 @@
       <c r="AB102" s="68" t="n"/>
       <c r="AC102" s="69" t="n"/>
       <c r="AD102" s="70">
-        <f>IF(AND(COUNTIF($B$5:B102,B102)=1,$B102&lt;&gt;"",$AB102&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B102,B102)=1,$B102&lt;&gt;"",$AB102&lt;&gt;"",COUNTA($J102,$L102,$N102,$P102,$R102,$T102,$V102,$X102,$Z102)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE102" s="67" t="inlineStr">
@@ -10147,7 +10160,7 @@
       <c r="AB103" s="68" t="n"/>
       <c r="AC103" s="69" t="n"/>
       <c r="AD103" s="70">
-        <f>IF(AND(COUNTIF($B$5:B103,B103)=1,$B103&lt;&gt;"",$AB103&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B103,B103)=1,$B103&lt;&gt;"",$AB103&lt;&gt;"",COUNTA($J103,$L103,$N103,$P103,$R103,$T103,$V103,$X103,$Z103)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE103" s="67" t="inlineStr">
@@ -10221,7 +10234,7 @@
       <c r="AB104" s="68" t="n"/>
       <c r="AC104" s="69" t="n"/>
       <c r="AD104" s="70">
-        <f>IF(AND(COUNTIF($B$5:B104,B104)=1,$B104&lt;&gt;"",$AB104&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B104,B104)=1,$B104&lt;&gt;"",$AB104&lt;&gt;"",COUNTA($J104,$L104,$N104,$P104,$R104,$T104,$V104,$X104,$Z104)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE104" s="67" t="inlineStr">
@@ -10295,7 +10308,7 @@
       <c r="AB105" s="68" t="n"/>
       <c r="AC105" s="69" t="n"/>
       <c r="AD105" s="70">
-        <f>IF(AND(COUNTIF($B$5:B105,B105)=1,$B105&lt;&gt;"",$AB105&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B105,B105)=1,$B105&lt;&gt;"",$AB105&lt;&gt;"",COUNTA($J105,$L105,$N105,$P105,$R105,$T105,$V105,$X105,$Z105)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE105" s="67" t="inlineStr">
@@ -10373,7 +10386,7 @@
       <c r="AB106" s="68" t="n"/>
       <c r="AC106" s="69" t="n"/>
       <c r="AD106" s="70">
-        <f>IF(AND(COUNTIF($B$5:B106,B106)=1,$B106&lt;&gt;"",$AB106&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B106,B106)=1,$B106&lt;&gt;"",$AB106&lt;&gt;"",COUNTA($J106,$L106,$N106,$P106,$R106,$T106,$V106,$X106,$Z106)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE106" s="67" t="inlineStr">
@@ -10451,7 +10464,7 @@
       <c r="AB107" s="68" t="n"/>
       <c r="AC107" s="69" t="n"/>
       <c r="AD107" s="70">
-        <f>IF(AND(COUNTIF($B$5:B107,B107)=1,$B107&lt;&gt;"",$AB107&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B107,B107)=1,$B107&lt;&gt;"",$AB107&lt;&gt;"",COUNTA($J107,$L107,$N107,$P107,$R107,$T107,$V107,$X107,$Z107)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE107" s="67" t="inlineStr">
@@ -10529,7 +10542,7 @@
       <c r="AB108" s="68" t="n"/>
       <c r="AC108" s="69" t="n"/>
       <c r="AD108" s="70">
-        <f>IF(AND(COUNTIF($B$5:B108,B108)=1,$B108&lt;&gt;"",$AB108&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B108,B108)=1,$B108&lt;&gt;"",$AB108&lt;&gt;"",COUNTA($J108,$L108,$N108,$P108,$R108,$T108,$V108,$X108,$Z108)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE108" s="67" t="inlineStr">
@@ -10607,7 +10620,7 @@
       <c r="AB109" s="68" t="n"/>
       <c r="AC109" s="69" t="n"/>
       <c r="AD109" s="70">
-        <f>IF(AND(COUNTIF($B$5:B109,B109)=1,$B109&lt;&gt;"",$AB109&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B109,B109)=1,$B109&lt;&gt;"",$AB109&lt;&gt;"",COUNTA($J109,$L109,$N109,$P109,$R109,$T109,$V109,$X109,$Z109)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE109" s="67" t="inlineStr">
@@ -10685,7 +10698,7 @@
       <c r="AB110" s="68" t="n"/>
       <c r="AC110" s="69" t="n"/>
       <c r="AD110" s="70">
-        <f>IF(AND(COUNTIF($B$5:B110,B110)=1,$B110&lt;&gt;"",$AB110&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B110,B110)=1,$B110&lt;&gt;"",$AB110&lt;&gt;"",COUNTA($J110,$L110,$N110,$P110,$R110,$T110,$V110,$X110,$Z110)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE110" s="67" t="inlineStr">
@@ -10763,7 +10776,7 @@
       <c r="AB111" s="68" t="n"/>
       <c r="AC111" s="69" t="n"/>
       <c r="AD111" s="70">
-        <f>IF(AND(COUNTIF($B$5:B111,B111)=1,$B111&lt;&gt;"",$AB111&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B111,B111)=1,$B111&lt;&gt;"",$AB111&lt;&gt;"",COUNTA($J111,$L111,$N111,$P111,$R111,$T111,$V111,$X111,$Z111)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE111" s="67" t="inlineStr">
@@ -10841,7 +10854,7 @@
       <c r="AB112" s="68" t="n"/>
       <c r="AC112" s="69" t="n"/>
       <c r="AD112" s="70">
-        <f>IF(AND(COUNTIF($B$5:B112,B112)=1,$B112&lt;&gt;"",$AB112&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B112,B112)=1,$B112&lt;&gt;"",$AB112&lt;&gt;"",COUNTA($J112,$L112,$N112,$P112,$R112,$T112,$V112,$X112,$Z112)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE112" s="67" t="inlineStr">
@@ -10919,7 +10932,7 @@
       <c r="AB113" s="68" t="n"/>
       <c r="AC113" s="69" t="n"/>
       <c r="AD113" s="70">
-        <f>IF(AND(COUNTIF($B$5:B113,B113)=1,$B113&lt;&gt;"",$AB113&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B113,B113)=1,$B113&lt;&gt;"",$AB113&lt;&gt;"",COUNTA($J113,$L113,$N113,$P113,$R113,$T113,$V113,$X113,$Z113)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE113" s="67" t="inlineStr">
@@ -10993,7 +11006,7 @@
       <c r="AB114" s="68" t="n"/>
       <c r="AC114" s="69" t="n"/>
       <c r="AD114" s="70">
-        <f>IF(AND(COUNTIF($B$5:B114,B114)=1,$B114&lt;&gt;"",$AB114&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B114,B114)=1,$B114&lt;&gt;"",$AB114&lt;&gt;"",COUNTA($J114,$L114,$N114,$P114,$R114,$T114,$V114,$X114,$Z114)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE114" s="67" t="inlineStr">
@@ -11067,7 +11080,7 @@
       <c r="AB115" s="68" t="n"/>
       <c r="AC115" s="69" t="n"/>
       <c r="AD115" s="70">
-        <f>IF(AND(COUNTIF($B$5:B115,B115)=1,$B115&lt;&gt;"",$AB115&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B115,B115)=1,$B115&lt;&gt;"",$AB115&lt;&gt;"",COUNTA($J115,$L115,$N115,$P115,$R115,$T115,$V115,$X115,$Z115)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE115" s="67" t="inlineStr">
@@ -11145,7 +11158,7 @@
       <c r="AB116" s="68" t="n"/>
       <c r="AC116" s="69" t="n"/>
       <c r="AD116" s="70">
-        <f>IF(AND(COUNTIF($B$5:B116,B116)=1,$B116&lt;&gt;"",$AB116&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B116,B116)=1,$B116&lt;&gt;"",$AB116&lt;&gt;"",COUNTA($J116,$L116,$N116,$P116,$R116,$T116,$V116,$X116,$Z116)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE116" s="67" t="inlineStr">
@@ -11223,7 +11236,7 @@
       <c r="AB117" s="68" t="n"/>
       <c r="AC117" s="69" t="n"/>
       <c r="AD117" s="70">
-        <f>IF(AND(COUNTIF($B$5:B117,B117)=1,$B117&lt;&gt;"",$AB117&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B117,B117)=1,$B117&lt;&gt;"",$AB117&lt;&gt;"",COUNTA($J117,$L117,$N117,$P117,$R117,$T117,$V117,$X117,$Z117)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE117" s="67" t="inlineStr">
@@ -11301,7 +11314,7 @@
       <c r="AB118" s="68" t="n"/>
       <c r="AC118" s="69" t="n"/>
       <c r="AD118" s="70">
-        <f>IF(AND(COUNTIF($B$5:B118,B118)=1,$B118&lt;&gt;"",$AB118&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B118,B118)=1,$B118&lt;&gt;"",$AB118&lt;&gt;"",COUNTA($J118,$L118,$N118,$P118,$R118,$T118,$V118,$X118,$Z118)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE118" s="67" t="inlineStr">
@@ -11379,7 +11392,7 @@
       <c r="AB119" s="68" t="n"/>
       <c r="AC119" s="69" t="n"/>
       <c r="AD119" s="70">
-        <f>IF(AND(COUNTIF($B$5:B119,B119)=1,$B119&lt;&gt;"",$AB119&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B119,B119)=1,$B119&lt;&gt;"",$AB119&lt;&gt;"",COUNTA($J119,$L119,$N119,$P119,$R119,$T119,$V119,$X119,$Z119)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE119" s="67" t="inlineStr">
@@ -11457,7 +11470,7 @@
       <c r="AB120" s="68" t="n"/>
       <c r="AC120" s="69" t="n"/>
       <c r="AD120" s="70">
-        <f>IF(AND(COUNTIF($B$5:B120,B120)=1,$B120&lt;&gt;"",$AB120&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B120,B120)=1,$B120&lt;&gt;"",$AB120&lt;&gt;"",COUNTA($J120,$L120,$N120,$P120,$R120,$T120,$V120,$X120,$Z120)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE120" s="67" t="inlineStr">
@@ -11531,7 +11544,7 @@
       <c r="AB121" s="68" t="n"/>
       <c r="AC121" s="69" t="n"/>
       <c r="AD121" s="70">
-        <f>IF(AND(COUNTIF($B$5:B121,B121)=1,$B121&lt;&gt;"",$AB121&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B121,B121)=1,$B121&lt;&gt;"",$AB121&lt;&gt;"",COUNTA($J121,$L121,$N121,$P121,$R121,$T121,$V121,$X121,$Z121)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE121" s="67" t="inlineStr">
@@ -11605,7 +11618,7 @@
       <c r="AB122" s="68" t="n"/>
       <c r="AC122" s="69" t="n"/>
       <c r="AD122" s="70">
-        <f>IF(AND(COUNTIF($B$5:B122,B122)=1,$B122&lt;&gt;"",$AB122&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B122,B122)=1,$B122&lt;&gt;"",$AB122&lt;&gt;"",COUNTA($J122,$L122,$N122,$P122,$R122,$T122,$V122,$X122,$Z122)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE122" s="67" t="inlineStr">
@@ -11683,7 +11696,7 @@
       <c r="AB123" s="68" t="n"/>
       <c r="AC123" s="69" t="n"/>
       <c r="AD123" s="70">
-        <f>IF(AND(COUNTIF($B$5:B123,B123)=1,$B123&lt;&gt;"",$AB123&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B123,B123)=1,$B123&lt;&gt;"",$AB123&lt;&gt;"",COUNTA($J123,$L123,$N123,$P123,$R123,$T123,$V123,$X123,$Z123)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE123" s="67" t="inlineStr">
@@ -11757,7 +11770,7 @@
       <c r="AB124" s="68" t="n"/>
       <c r="AC124" s="69" t="n"/>
       <c r="AD124" s="70">
-        <f>IF(AND(COUNTIF($B$5:B124,B124)=1,$B124&lt;&gt;"",$AB124&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B124,B124)=1,$B124&lt;&gt;"",$AB124&lt;&gt;"",COUNTA($J124,$L124,$N124,$P124,$R124,$T124,$V124,$X124,$Z124)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE124" s="67" t="inlineStr">
@@ -11831,7 +11844,7 @@
       <c r="AB125" s="68" t="n"/>
       <c r="AC125" s="69" t="n"/>
       <c r="AD125" s="70">
-        <f>IF(AND(COUNTIF($B$5:B125,B125)=1,$B125&lt;&gt;"",$AB125&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B125,B125)=1,$B125&lt;&gt;"",$AB125&lt;&gt;"",COUNTA($J125,$L125,$N125,$P125,$R125,$T125,$V125,$X125,$Z125)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE125" s="67" t="inlineStr">
@@ -11909,7 +11922,7 @@
       <c r="AB126" s="68" t="n"/>
       <c r="AC126" s="69" t="n"/>
       <c r="AD126" s="70">
-        <f>IF(AND(COUNTIF($B$5:B126,B126)=1,$B126&lt;&gt;"",$AB126&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B126,B126)=1,$B126&lt;&gt;"",$AB126&lt;&gt;"",COUNTA($J126,$L126,$N126,$P126,$R126,$T126,$V126,$X126,$Z126)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE126" s="67" t="inlineStr">
@@ -11987,7 +12000,7 @@
       <c r="AB127" s="68" t="n"/>
       <c r="AC127" s="69" t="n"/>
       <c r="AD127" s="70">
-        <f>IF(AND(COUNTIF($B$5:B127,B127)=1,$B127&lt;&gt;"",$AB127&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B127,B127)=1,$B127&lt;&gt;"",$AB127&lt;&gt;"",COUNTA($J127,$L127,$N127,$P127,$R127,$T127,$V127,$X127,$Z127)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE127" s="67" t="inlineStr">
@@ -12065,7 +12078,7 @@
       <c r="AB128" s="68" t="n"/>
       <c r="AC128" s="69" t="n"/>
       <c r="AD128" s="70">
-        <f>IF(AND(COUNTIF($B$5:B128,B128)=1,$B128&lt;&gt;"",$AB128&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B128,B128)=1,$B128&lt;&gt;"",$AB128&lt;&gt;"",COUNTA($J128,$L128,$N128,$P128,$R128,$T128,$V128,$X128,$Z128)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE128" s="67" t="inlineStr">
@@ -12143,7 +12156,7 @@
       <c r="AB129" s="68" t="n"/>
       <c r="AC129" s="69" t="n"/>
       <c r="AD129" s="70">
-        <f>IF(AND(COUNTIF($B$5:B129,B129)=1,$B129&lt;&gt;"",$AB129&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B129,B129)=1,$B129&lt;&gt;"",$AB129&lt;&gt;"",COUNTA($J129,$L129,$N129,$P129,$R129,$T129,$V129,$X129,$Z129)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE129" s="67" t="inlineStr">
@@ -12221,7 +12234,7 @@
       <c r="AB130" s="68" t="n"/>
       <c r="AC130" s="69" t="n"/>
       <c r="AD130" s="70">
-        <f>IF(AND(COUNTIF($B$5:B130,B130)=1,$B130&lt;&gt;"",$AB130&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B130,B130)=1,$B130&lt;&gt;"",$AB130&lt;&gt;"",COUNTA($J130,$L130,$N130,$P130,$R130,$T130,$V130,$X130,$Z130)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE130" s="67" t="inlineStr">
@@ -12299,7 +12312,7 @@
       <c r="AB131" s="68" t="n"/>
       <c r="AC131" s="69" t="n"/>
       <c r="AD131" s="70">
-        <f>IF(AND(COUNTIF($B$5:B131,B131)=1,$B131&lt;&gt;"",$AB131&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B131,B131)=1,$B131&lt;&gt;"",$AB131&lt;&gt;"",COUNTA($J131,$L131,$N131,$P131,$R131,$T131,$V131,$X131,$Z131)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE131" s="67" t="inlineStr">
@@ -12377,7 +12390,7 @@
       <c r="AB132" s="68" t="n"/>
       <c r="AC132" s="69" t="n"/>
       <c r="AD132" s="70">
-        <f>IF(AND(COUNTIF($B$5:B132,B132)=1,$B132&lt;&gt;"",$AB132&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B132,B132)=1,$B132&lt;&gt;"",$AB132&lt;&gt;"",COUNTA($J132,$L132,$N132,$P132,$R132,$T132,$V132,$X132,$Z132)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE132" s="67" t="inlineStr">
@@ -12455,7 +12468,7 @@
       <c r="AB133" s="68" t="n"/>
       <c r="AC133" s="69" t="n"/>
       <c r="AD133" s="70">
-        <f>IF(AND(COUNTIF($B$5:B133,B133)=1,$B133&lt;&gt;"",$AB133&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B133,B133)=1,$B133&lt;&gt;"",$AB133&lt;&gt;"",COUNTA($J133,$L133,$N133,$P133,$R133,$T133,$V133,$X133,$Z133)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE133" s="67" t="inlineStr">
@@ -12533,7 +12546,7 @@
       <c r="AB134" s="68" t="n"/>
       <c r="AC134" s="69" t="n"/>
       <c r="AD134" s="70">
-        <f>IF(AND(COUNTIF($B$5:B134,B134)=1,$B134&lt;&gt;"",$AB134&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B134,B134)=1,$B134&lt;&gt;"",$AB134&lt;&gt;"",COUNTA($J134,$L134,$N134,$P134,$R134,$T134,$V134,$X134,$Z134)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE134" s="67" t="inlineStr">
@@ -12611,7 +12624,7 @@
       <c r="AB135" s="68" t="n"/>
       <c r="AC135" s="69" t="n"/>
       <c r="AD135" s="70">
-        <f>IF(AND(COUNTIF($B$5:B135,B135)=1,$B135&lt;&gt;"",$AB135&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B135,B135)=1,$B135&lt;&gt;"",$AB135&lt;&gt;"",COUNTA($J135,$L135,$N135,$P135,$R135,$T135,$V135,$X135,$Z135)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE135" s="67" t="inlineStr">
@@ -12685,7 +12698,7 @@
       <c r="AB136" s="68" t="n"/>
       <c r="AC136" s="69" t="n"/>
       <c r="AD136" s="70">
-        <f>IF(AND(COUNTIF($B$5:B136,B136)=1,$B136&lt;&gt;"",$AB136&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B136,B136)=1,$B136&lt;&gt;"",$AB136&lt;&gt;"",COUNTA($J136,$L136,$N136,$P136,$R136,$T136,$V136,$X136,$Z136)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE136" s="67" t="inlineStr">
@@ -12759,7 +12772,7 @@
       <c r="AB137" s="68" t="n"/>
       <c r="AC137" s="69" t="n"/>
       <c r="AD137" s="70">
-        <f>IF(AND(COUNTIF($B$5:B137,B137)=1,$B137&lt;&gt;"",$AB137&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B137,B137)=1,$B137&lt;&gt;"",$AB137&lt;&gt;"",COUNTA($J137,$L137,$N137,$P137,$R137,$T137,$V137,$X137,$Z137)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE137" s="67" t="inlineStr">
@@ -12833,7 +12846,7 @@
       <c r="AB138" s="68" t="n"/>
       <c r="AC138" s="69" t="n"/>
       <c r="AD138" s="70">
-        <f>IF(AND(COUNTIF($B$5:B138,B138)=1,$B138&lt;&gt;"",$AB138&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B138,B138)=1,$B138&lt;&gt;"",$AB138&lt;&gt;"",COUNTA($J138,$L138,$N138,$P138,$R138,$T138,$V138,$X138,$Z138)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE138" s="67" t="inlineStr">
@@ -12907,7 +12920,7 @@
       <c r="AB139" s="68" t="n"/>
       <c r="AC139" s="69" t="n"/>
       <c r="AD139" s="70">
-        <f>IF(AND(COUNTIF($B$5:B139,B139)=1,$B139&lt;&gt;"",$AB139&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B139,B139)=1,$B139&lt;&gt;"",$AB139&lt;&gt;"",COUNTA($J139,$L139,$N139,$P139,$R139,$T139,$V139,$X139,$Z139)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE139" s="67" t="inlineStr">
@@ -12985,7 +12998,7 @@
       <c r="AB140" s="68" t="n"/>
       <c r="AC140" s="69" t="n"/>
       <c r="AD140" s="70">
-        <f>IF(AND(COUNTIF($B$5:B140,B140)=1,$B140&lt;&gt;"",$AB140&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B140,B140)=1,$B140&lt;&gt;"",$AB140&lt;&gt;"",COUNTA($J140,$L140,$N140,$P140,$R140,$T140,$V140,$X140,$Z140)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE140" s="67" t="inlineStr">
@@ -13063,7 +13076,7 @@
       <c r="AB141" s="68" t="n"/>
       <c r="AC141" s="69" t="n"/>
       <c r="AD141" s="70">
-        <f>IF(AND(COUNTIF($B$5:B141,B141)=1,$B141&lt;&gt;"",$AB141&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B141,B141)=1,$B141&lt;&gt;"",$AB141&lt;&gt;"",COUNTA($J141,$L141,$N141,$P141,$R141,$T141,$V141,$X141,$Z141)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE141" s="67" t="inlineStr">
@@ -13141,7 +13154,7 @@
       <c r="AB142" s="68" t="n"/>
       <c r="AC142" s="69" t="n"/>
       <c r="AD142" s="70">
-        <f>IF(AND(COUNTIF($B$5:B142,B142)=1,$B142&lt;&gt;"",$AB142&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B142,B142)=1,$B142&lt;&gt;"",$AB142&lt;&gt;"",COUNTA($J142,$L142,$N142,$P142,$R142,$T142,$V142,$X142,$Z142)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE142" s="67" t="inlineStr">
@@ -13219,7 +13232,7 @@
       <c r="AB143" s="68" t="n"/>
       <c r="AC143" s="69" t="n"/>
       <c r="AD143" s="70">
-        <f>IF(AND(COUNTIF($B$5:B143,B143)=1,$B143&lt;&gt;"",$AB143&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B143,B143)=1,$B143&lt;&gt;"",$AB143&lt;&gt;"",COUNTA($J143,$L143,$N143,$P143,$R143,$T143,$V143,$X143,$Z143)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE143" s="67" t="inlineStr">
@@ -13293,7 +13306,7 @@
       <c r="AB144" s="68" t="n"/>
       <c r="AC144" s="69" t="n"/>
       <c r="AD144" s="70">
-        <f>IF(AND(COUNTIF($B$5:B144,B144)=1,$B144&lt;&gt;"",$AB144&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B144,B144)=1,$B144&lt;&gt;"",$AB144&lt;&gt;"",COUNTA($J144,$L144,$N144,$P144,$R144,$T144,$V144,$X144,$Z144)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE144" s="67" t="inlineStr">
@@ -13367,7 +13380,7 @@
       <c r="AB145" s="68" t="n"/>
       <c r="AC145" s="69" t="n"/>
       <c r="AD145" s="70">
-        <f>IF(AND(COUNTIF($B$5:B145,B145)=1,$B145&lt;&gt;"",$AB145&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B145,B145)=1,$B145&lt;&gt;"",$AB145&lt;&gt;"",COUNTA($J145,$L145,$N145,$P145,$R145,$T145,$V145,$X145,$Z145)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE145" s="67" t="inlineStr">
@@ -13445,7 +13458,7 @@
       <c r="AB146" s="68" t="n"/>
       <c r="AC146" s="69" t="n"/>
       <c r="AD146" s="70">
-        <f>IF(AND(COUNTIF($B$5:B146,B146)=1,$B146&lt;&gt;"",$AB146&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B146,B146)=1,$B146&lt;&gt;"",$AB146&lt;&gt;"",COUNTA($J146,$L146,$N146,$P146,$R146,$T146,$V146,$X146,$Z146)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE146" s="67" t="inlineStr">
@@ -13523,7 +13536,7 @@
       <c r="AB147" s="68" t="n"/>
       <c r="AC147" s="69" t="n"/>
       <c r="AD147" s="70">
-        <f>IF(AND(COUNTIF($B$5:B147,B147)=1,$B147&lt;&gt;"",$AB147&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B147,B147)=1,$B147&lt;&gt;"",$AB147&lt;&gt;"",COUNTA($J147,$L147,$N147,$P147,$R147,$T147,$V147,$X147,$Z147)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE147" s="67" t="inlineStr">
@@ -13601,7 +13614,7 @@
       <c r="AB148" s="68" t="n"/>
       <c r="AC148" s="69" t="n"/>
       <c r="AD148" s="70">
-        <f>IF(AND(COUNTIF($B$5:B148,B148)=1,$B148&lt;&gt;"",$AB148&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B148,B148)=1,$B148&lt;&gt;"",$AB148&lt;&gt;"",COUNTA($J148,$L148,$N148,$P148,$R148,$T148,$V148,$X148,$Z148)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE148" s="67" t="inlineStr">
@@ -13679,7 +13692,7 @@
       <c r="AB149" s="68" t="n"/>
       <c r="AC149" s="69" t="n"/>
       <c r="AD149" s="70">
-        <f>IF(AND(COUNTIF($B$5:B149,B149)=1,$B149&lt;&gt;"",$AB149&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B149,B149)=1,$B149&lt;&gt;"",$AB149&lt;&gt;"",COUNTA($J149,$L149,$N149,$P149,$R149,$T149,$V149,$X149,$Z149)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE149" s="67" t="inlineStr">
@@ -13753,7 +13766,7 @@
       <c r="AB150" s="68" t="n"/>
       <c r="AC150" s="69" t="n"/>
       <c r="AD150" s="70">
-        <f>IF(AND(COUNTIF($B$5:B150,B150)=1,$B150&lt;&gt;"",$AB150&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B150,B150)=1,$B150&lt;&gt;"",$AB150&lt;&gt;"",COUNTA($J150,$L150,$N150,$P150,$R150,$T150,$V150,$X150,$Z150)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE150" s="67" t="inlineStr">
@@ -13827,7 +13840,7 @@
       <c r="AB151" s="68" t="n"/>
       <c r="AC151" s="69" t="n"/>
       <c r="AD151" s="70">
-        <f>IF(AND(COUNTIF($B$5:B151,B151)=1,$B151&lt;&gt;"",$AB151&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B151,B151)=1,$B151&lt;&gt;"",$AB151&lt;&gt;"",COUNTA($J151,$L151,$N151,$P151,$R151,$T151,$V151,$X151,$Z151)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE151" s="67" t="inlineStr">
@@ -13905,7 +13918,7 @@
       <c r="AB152" s="68" t="n"/>
       <c r="AC152" s="69" t="n"/>
       <c r="AD152" s="70">
-        <f>IF(AND(COUNTIF($B$5:B152,B152)=1,$B152&lt;&gt;"",$AB152&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B152,B152)=1,$B152&lt;&gt;"",$AB152&lt;&gt;"",COUNTA($J152,$L152,$N152,$P152,$R152,$T152,$V152,$X152,$Z152)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE152" s="67" t="inlineStr">
@@ -13983,7 +13996,7 @@
       <c r="AB153" s="68" t="n"/>
       <c r="AC153" s="69" t="n"/>
       <c r="AD153" s="70">
-        <f>IF(AND(COUNTIF($B$5:B153,B153)=1,$B153&lt;&gt;"",$AB153&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B153,B153)=1,$B153&lt;&gt;"",$AB153&lt;&gt;"",COUNTA($J153,$L153,$N153,$P153,$R153,$T153,$V153,$X153,$Z153)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE153" s="67" t="inlineStr">
@@ -14061,7 +14074,7 @@
       <c r="AB154" s="68" t="n"/>
       <c r="AC154" s="69" t="n"/>
       <c r="AD154" s="70">
-        <f>IF(AND(COUNTIF($B$5:B154,B154)=1,$B154&lt;&gt;"",$AB154&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B154,B154)=1,$B154&lt;&gt;"",$AB154&lt;&gt;"",COUNTA($J154,$L154,$N154,$P154,$R154,$T154,$V154,$X154,$Z154)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE154" s="67" t="inlineStr">
@@ -14139,7 +14152,7 @@
       <c r="AB155" s="68" t="n"/>
       <c r="AC155" s="69" t="n"/>
       <c r="AD155" s="70">
-        <f>IF(AND(COUNTIF($B$5:B155,B155)=1,$B155&lt;&gt;"",$AB155&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B155,B155)=1,$B155&lt;&gt;"",$AB155&lt;&gt;"",COUNTA($J155,$L155,$N155,$P155,$R155,$T155,$V155,$X155,$Z155)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE155" s="67" t="inlineStr">
@@ -14217,7 +14230,7 @@
       <c r="AB156" s="68" t="n"/>
       <c r="AC156" s="69" t="n"/>
       <c r="AD156" s="70">
-        <f>IF(AND(COUNTIF($B$5:B156,B156)=1,$B156&lt;&gt;"",$AB156&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B156,B156)=1,$B156&lt;&gt;"",$AB156&lt;&gt;"",COUNTA($J156,$L156,$N156,$P156,$R156,$T156,$V156,$X156,$Z156)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE156" s="67" t="inlineStr">
@@ -14295,7 +14308,7 @@
       <c r="AB157" s="68" t="n"/>
       <c r="AC157" s="69" t="n"/>
       <c r="AD157" s="70">
-        <f>IF(AND(COUNTIF($B$5:B157,B157)=1,$B157&lt;&gt;"",$AB157&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B157,B157)=1,$B157&lt;&gt;"",$AB157&lt;&gt;"",COUNTA($J157,$L157,$N157,$P157,$R157,$T157,$V157,$X157,$Z157)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE157" s="67" t="inlineStr">
@@ -14373,7 +14386,7 @@
       <c r="AB158" s="68" t="n"/>
       <c r="AC158" s="69" t="n"/>
       <c r="AD158" s="70">
-        <f>IF(AND(COUNTIF($B$5:B158,B158)=1,$B158&lt;&gt;"",$AB158&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B158,B158)=1,$B158&lt;&gt;"",$AB158&lt;&gt;"",COUNTA($J158,$L158,$N158,$P158,$R158,$T158,$V158,$X158,$Z158)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE158" s="67" t="inlineStr">
@@ -14451,7 +14464,7 @@
       <c r="AB159" s="68" t="n"/>
       <c r="AC159" s="69" t="n"/>
       <c r="AD159" s="70">
-        <f>IF(AND(COUNTIF($B$5:B159,B159)=1,$B159&lt;&gt;"",$AB159&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B159,B159)=1,$B159&lt;&gt;"",$AB159&lt;&gt;"",COUNTA($J159,$L159,$N159,$P159,$R159,$T159,$V159,$X159,$Z159)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE159" s="67" t="inlineStr">
@@ -14529,7 +14542,7 @@
       <c r="AB160" s="68" t="n"/>
       <c r="AC160" s="69" t="n"/>
       <c r="AD160" s="70">
-        <f>IF(AND(COUNTIF($B$5:B160,B160)=1,$B160&lt;&gt;"",$AB160&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B160,B160)=1,$B160&lt;&gt;"",$AB160&lt;&gt;"",COUNTA($J160,$L160,$N160,$P160,$R160,$T160,$V160,$X160,$Z160)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE160" s="67" t="inlineStr">
@@ -14607,7 +14620,7 @@
       <c r="AB161" s="68" t="n"/>
       <c r="AC161" s="69" t="n"/>
       <c r="AD161" s="70">
-        <f>IF(AND(COUNTIF($B$5:B161,B161)=1,$B161&lt;&gt;"",$AB161&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B161,B161)=1,$B161&lt;&gt;"",$AB161&lt;&gt;"",COUNTA($J161,$L161,$N161,$P161,$R161,$T161,$V161,$X161,$Z161)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE161" s="67" t="inlineStr">
@@ -14685,7 +14698,7 @@
       <c r="AB162" s="68" t="n"/>
       <c r="AC162" s="69" t="n"/>
       <c r="AD162" s="70">
-        <f>IF(AND(COUNTIF($B$5:B162,B162)=1,$B162&lt;&gt;"",$AB162&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B162,B162)=1,$B162&lt;&gt;"",$AB162&lt;&gt;"",COUNTA($J162,$L162,$N162,$P162,$R162,$T162,$V162,$X162,$Z162)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE162" s="67" t="inlineStr">
@@ -14763,7 +14776,7 @@
       <c r="AB163" s="68" t="n"/>
       <c r="AC163" s="69" t="n"/>
       <c r="AD163" s="70">
-        <f>IF(AND(COUNTIF($B$5:B163,B163)=1,$B163&lt;&gt;"",$AB163&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B163,B163)=1,$B163&lt;&gt;"",$AB163&lt;&gt;"",COUNTA($J163,$L163,$N163,$P163,$R163,$T163,$V163,$X163,$Z163)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE163" s="67" t="inlineStr">
@@ -14837,7 +14850,7 @@
       <c r="AB164" s="68" t="n"/>
       <c r="AC164" s="69" t="n"/>
       <c r="AD164" s="70">
-        <f>IF(AND(COUNTIF($B$5:B164,B164)=1,$B164&lt;&gt;"",$AB164&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B164,B164)=1,$B164&lt;&gt;"",$AB164&lt;&gt;"",COUNTA($J164,$L164,$N164,$P164,$R164,$T164,$V164,$X164,$Z164)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE164" s="67" t="inlineStr">
@@ -14911,7 +14924,7 @@
       <c r="AB165" s="68" t="n"/>
       <c r="AC165" s="69" t="n"/>
       <c r="AD165" s="70">
-        <f>IF(AND(COUNTIF($B$5:B165,B165)=1,$B165&lt;&gt;"",$AB165&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B165,B165)=1,$B165&lt;&gt;"",$AB165&lt;&gt;"",COUNTA($J165,$L165,$N165,$P165,$R165,$T165,$V165,$X165,$Z165)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE165" s="67" t="inlineStr">
@@ -14989,7 +15002,7 @@
       <c r="AB166" s="68" t="n"/>
       <c r="AC166" s="69" t="n"/>
       <c r="AD166" s="70">
-        <f>IF(AND(COUNTIF($B$5:B166,B166)=1,$B166&lt;&gt;"",$AB166&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B166,B166)=1,$B166&lt;&gt;"",$AB166&lt;&gt;"",COUNTA($J166,$L166,$N166,$P166,$R166,$T166,$V166,$X166,$Z166)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE166" s="67" t="inlineStr">
@@ -15067,7 +15080,7 @@
       <c r="AB167" s="68" t="n"/>
       <c r="AC167" s="69" t="n"/>
       <c r="AD167" s="70">
-        <f>IF(AND(COUNTIF($B$5:B167,B167)=1,$B167&lt;&gt;"",$AB167&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B167,B167)=1,$B167&lt;&gt;"",$AB167&lt;&gt;"",COUNTA($J167,$L167,$N167,$P167,$R167,$T167,$V167,$X167,$Z167)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE167" s="67" t="inlineStr">
@@ -15145,7 +15158,7 @@
       <c r="AB168" s="68" t="n"/>
       <c r="AC168" s="69" t="n"/>
       <c r="AD168" s="70">
-        <f>IF(AND(COUNTIF($B$5:B168,B168)=1,$B168&lt;&gt;"",$AB168&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B168,B168)=1,$B168&lt;&gt;"",$AB168&lt;&gt;"",COUNTA($J168,$L168,$N168,$P168,$R168,$T168,$V168,$X168,$Z168)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE168" s="67" t="inlineStr">
@@ -15223,7 +15236,7 @@
       <c r="AB169" s="68" t="n"/>
       <c r="AC169" s="69" t="n"/>
       <c r="AD169" s="70">
-        <f>IF(AND(COUNTIF($B$5:B169,B169)=1,$B169&lt;&gt;"",$AB169&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B169,B169)=1,$B169&lt;&gt;"",$AB169&lt;&gt;"",COUNTA($J169,$L169,$N169,$P169,$R169,$T169,$V169,$X169,$Z169)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE169" s="67" t="inlineStr">
@@ -15297,7 +15310,7 @@
       <c r="AB170" s="68" t="n"/>
       <c r="AC170" s="69" t="n"/>
       <c r="AD170" s="70">
-        <f>IF(AND(COUNTIF($B$5:B170,B170)=1,$B170&lt;&gt;"",$AB170&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B170,B170)=1,$B170&lt;&gt;"",$AB170&lt;&gt;"",COUNTA($J170,$L170,$N170,$P170,$R170,$T170,$V170,$X170,$Z170)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE170" s="67" t="inlineStr">
@@ -15371,7 +15384,7 @@
       <c r="AB171" s="68" t="n"/>
       <c r="AC171" s="69" t="n"/>
       <c r="AD171" s="70">
-        <f>IF(AND(COUNTIF($B$5:B171,B171)=1,$B171&lt;&gt;"",$AB171&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B171,B171)=1,$B171&lt;&gt;"",$AB171&lt;&gt;"",COUNTA($J171,$L171,$N171,$P171,$R171,$T171,$V171,$X171,$Z171)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE171" s="67" t="inlineStr">
@@ -15445,7 +15458,7 @@
       <c r="AB172" s="68" t="n"/>
       <c r="AC172" s="69" t="n"/>
       <c r="AD172" s="70">
-        <f>IF(AND(COUNTIF($B$5:B172,B172)=1,$B172&lt;&gt;"",$AB172&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B172,B172)=1,$B172&lt;&gt;"",$AB172&lt;&gt;"",COUNTA($J172,$L172,$N172,$P172,$R172,$T172,$V172,$X172,$Z172)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE172" s="67" t="inlineStr">
@@ -15519,7 +15532,7 @@
       <c r="AB173" s="68" t="n"/>
       <c r="AC173" s="69" t="n"/>
       <c r="AD173" s="70">
-        <f>IF(AND(COUNTIF($B$5:B173,B173)=1,$B173&lt;&gt;"",$AB173&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B173,B173)=1,$B173&lt;&gt;"",$AB173&lt;&gt;"",COUNTA($J173,$L173,$N173,$P173,$R173,$T173,$V173,$X173,$Z173)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE173" s="67" t="inlineStr">
@@ -15597,7 +15610,7 @@
       <c r="AB174" s="68" t="n"/>
       <c r="AC174" s="69" t="n"/>
       <c r="AD174" s="70">
-        <f>IF(AND(COUNTIF($B$5:B174,B174)=1,$B174&lt;&gt;"",$AB174&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B174,B174)=1,$B174&lt;&gt;"",$AB174&lt;&gt;"",COUNTA($J174,$L174,$N174,$P174,$R174,$T174,$V174,$X174,$Z174)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE174" s="67" t="inlineStr">
@@ -15675,7 +15688,7 @@
       <c r="AB175" s="68" t="n"/>
       <c r="AC175" s="69" t="n"/>
       <c r="AD175" s="70">
-        <f>IF(AND(COUNTIF($B$5:B175,B175)=1,$B175&lt;&gt;"",$AB175&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B175,B175)=1,$B175&lt;&gt;"",$AB175&lt;&gt;"",COUNTA($J175,$L175,$N175,$P175,$R175,$T175,$V175,$X175,$Z175)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE175" s="67" t="inlineStr">
@@ -15753,7 +15766,7 @@
       <c r="AB176" s="68" t="n"/>
       <c r="AC176" s="69" t="n"/>
       <c r="AD176" s="70">
-        <f>IF(AND(COUNTIF($B$5:B176,B176)=1,$B176&lt;&gt;"",$AB176&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B176,B176)=1,$B176&lt;&gt;"",$AB176&lt;&gt;"",COUNTA($J176,$L176,$N176,$P176,$R176,$T176,$V176,$X176,$Z176)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE176" s="67" t="inlineStr">
@@ -15831,7 +15844,7 @@
       <c r="AB177" s="68" t="n"/>
       <c r="AC177" s="69" t="n"/>
       <c r="AD177" s="70">
-        <f>IF(AND(COUNTIF($B$5:B177,B177)=1,$B177&lt;&gt;"",$AB177&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B177,B177)=1,$B177&lt;&gt;"",$AB177&lt;&gt;"",COUNTA($J177,$L177,$N177,$P177,$R177,$T177,$V177,$X177,$Z177)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE177" s="67" t="inlineStr">
@@ -15909,7 +15922,7 @@
       <c r="AB178" s="68" t="n"/>
       <c r="AC178" s="69" t="n"/>
       <c r="AD178" s="70">
-        <f>IF(AND(COUNTIF($B$5:B178,B178)=1,$B178&lt;&gt;"",$AB178&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B178,B178)=1,$B178&lt;&gt;"",$AB178&lt;&gt;"",COUNTA($J178,$L178,$N178,$P178,$R178,$T178,$V178,$X178,$Z178)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE178" s="67" t="inlineStr">
@@ -15987,7 +16000,7 @@
       <c r="AB179" s="68" t="n"/>
       <c r="AC179" s="69" t="n"/>
       <c r="AD179" s="70">
-        <f>IF(AND(COUNTIF($B$5:B179,B179)=1,$B179&lt;&gt;"",$AB179&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B179,B179)=1,$B179&lt;&gt;"",$AB179&lt;&gt;"",COUNTA($J179,$L179,$N179,$P179,$R179,$T179,$V179,$X179,$Z179)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE179" s="67" t="inlineStr">
@@ -16065,7 +16078,7 @@
       <c r="AB180" s="68" t="n"/>
       <c r="AC180" s="69" t="n"/>
       <c r="AD180" s="70">
-        <f>IF(AND(COUNTIF($B$5:B180,B180)=1,$B180&lt;&gt;"",$AB180&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B180,B180)=1,$B180&lt;&gt;"",$AB180&lt;&gt;"",COUNTA($J180,$L180,$N180,$P180,$R180,$T180,$V180,$X180,$Z180)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE180" s="67" t="inlineStr">
@@ -16143,7 +16156,7 @@
       <c r="AB181" s="68" t="n"/>
       <c r="AC181" s="69" t="n"/>
       <c r="AD181" s="70">
-        <f>IF(AND(COUNTIF($B$5:B181,B181)=1,$B181&lt;&gt;"",$AB181&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B181,B181)=1,$B181&lt;&gt;"",$AB181&lt;&gt;"",COUNTA($J181,$L181,$N181,$P181,$R181,$T181,$V181,$X181,$Z181)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE181" s="67" t="inlineStr">
@@ -16221,7 +16234,7 @@
       <c r="AB182" s="68" t="n"/>
       <c r="AC182" s="69" t="n"/>
       <c r="AD182" s="70">
-        <f>IF(AND(COUNTIF($B$5:B182,B182)=1,$B182&lt;&gt;"",$AB182&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B182,B182)=1,$B182&lt;&gt;"",$AB182&lt;&gt;"",COUNTA($J182,$L182,$N182,$P182,$R182,$T182,$V182,$X182,$Z182)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE182" s="67" t="inlineStr">
@@ -16299,7 +16312,7 @@
       <c r="AB183" s="68" t="n"/>
       <c r="AC183" s="69" t="n"/>
       <c r="AD183" s="70">
-        <f>IF(AND(COUNTIF($B$5:B183,B183)=1,$B183&lt;&gt;"",$AB183&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B183,B183)=1,$B183&lt;&gt;"",$AB183&lt;&gt;"",COUNTA($J183,$L183,$N183,$P183,$R183,$T183,$V183,$X183,$Z183)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE183" s="67" t="inlineStr">
@@ -16373,7 +16386,7 @@
       <c r="AB184" s="68" t="n"/>
       <c r="AC184" s="69" t="n"/>
       <c r="AD184" s="70">
-        <f>IF(AND(COUNTIF($B$5:B184,B184)=1,$B184&lt;&gt;"",$AB184&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B184,B184)=1,$B184&lt;&gt;"",$AB184&lt;&gt;"",COUNTA($J184,$L184,$N184,$P184,$R184,$T184,$V184,$X184,$Z184)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE184" s="67" t="inlineStr">
@@ -16447,7 +16460,7 @@
       <c r="AB185" s="68" t="n"/>
       <c r="AC185" s="69" t="n"/>
       <c r="AD185" s="70">
-        <f>IF(AND(COUNTIF($B$5:B185,B185)=1,$B185&lt;&gt;"",$AB185&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B185,B185)=1,$B185&lt;&gt;"",$AB185&lt;&gt;"",COUNTA($J185,$L185,$N185,$P185,$R185,$T185,$V185,$X185,$Z185)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE185" s="67" t="inlineStr">
@@ -16525,7 +16538,7 @@
       <c r="AB186" s="68" t="n"/>
       <c r="AC186" s="69" t="n"/>
       <c r="AD186" s="70">
-        <f>IF(AND(COUNTIF($B$5:B186,B186)=1,$B186&lt;&gt;"",$AB186&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B186,B186)=1,$B186&lt;&gt;"",$AB186&lt;&gt;"",COUNTA($J186,$L186,$N186,$P186,$R186,$T186,$V186,$X186,$Z186)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE186" s="67" t="inlineStr">
@@ -16603,7 +16616,7 @@
       <c r="AB187" s="68" t="n"/>
       <c r="AC187" s="69" t="n"/>
       <c r="AD187" s="70">
-        <f>IF(AND(COUNTIF($B$5:B187,B187)=1,$B187&lt;&gt;"",$AB187&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B187,B187)=1,$B187&lt;&gt;"",$AB187&lt;&gt;"",COUNTA($J187,$L187,$N187,$P187,$R187,$T187,$V187,$X187,$Z187)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE187" s="67" t="inlineStr">
@@ -16681,7 +16694,7 @@
       <c r="AB188" s="68" t="n"/>
       <c r="AC188" s="69" t="n"/>
       <c r="AD188" s="70">
-        <f>IF(AND(COUNTIF($B$5:B188,B188)=1,$B188&lt;&gt;"",$AB188&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B188,B188)=1,$B188&lt;&gt;"",$AB188&lt;&gt;"",COUNTA($J188,$L188,$N188,$P188,$R188,$T188,$V188,$X188,$Z188)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE188" s="67" t="inlineStr">
@@ -16759,7 +16772,7 @@
       <c r="AB189" s="68" t="n"/>
       <c r="AC189" s="69" t="n"/>
       <c r="AD189" s="70">
-        <f>IF(AND(COUNTIF($B$5:B189,B189)=1,$B189&lt;&gt;"",$AB189&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B189,B189)=1,$B189&lt;&gt;"",$AB189&lt;&gt;"",COUNTA($J189,$L189,$N189,$P189,$R189,$T189,$V189,$X189,$Z189)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE189" s="67" t="inlineStr">
@@ -16837,7 +16850,7 @@
       <c r="AB190" s="68" t="n"/>
       <c r="AC190" s="69" t="n"/>
       <c r="AD190" s="70">
-        <f>IF(AND(COUNTIF($B$5:B190,B190)=1,$B190&lt;&gt;"",$AB190&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B190,B190)=1,$B190&lt;&gt;"",$AB190&lt;&gt;"",COUNTA($J190,$L190,$N190,$P190,$R190,$T190,$V190,$X190,$Z190)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE190" s="67" t="inlineStr">
@@ -16915,7 +16928,7 @@
       <c r="AB191" s="68" t="n"/>
       <c r="AC191" s="69" t="n"/>
       <c r="AD191" s="70">
-        <f>IF(AND(COUNTIF($B$5:B191,B191)=1,$B191&lt;&gt;"",$AB191&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B191,B191)=1,$B191&lt;&gt;"",$AB191&lt;&gt;"",COUNTA($J191,$L191,$N191,$P191,$R191,$T191,$V191,$X191,$Z191)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE191" s="67" t="inlineStr">
@@ -16993,7 +17006,7 @@
       <c r="AB192" s="68" t="n"/>
       <c r="AC192" s="69" t="n"/>
       <c r="AD192" s="70">
-        <f>IF(AND(COUNTIF($B$5:B192,B192)=1,$B192&lt;&gt;"",$AB192&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B192,B192)=1,$B192&lt;&gt;"",$AB192&lt;&gt;"",COUNTA($J192,$L192,$N192,$P192,$R192,$T192,$V192,$X192,$Z192)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE192" s="67" t="inlineStr">
@@ -17067,7 +17080,7 @@
       <c r="AB193" s="68" t="n"/>
       <c r="AC193" s="69" t="n"/>
       <c r="AD193" s="70">
-        <f>IF(AND(COUNTIF($B$5:B193,B193)=1,$B193&lt;&gt;"",$AB193&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B193,B193)=1,$B193&lt;&gt;"",$AB193&lt;&gt;"",COUNTA($J193,$L193,$N193,$P193,$R193,$T193,$V193,$X193,$Z193)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE193" s="67" t="inlineStr">
@@ -17137,7 +17150,7 @@
       <c r="AB194" s="68" t="n"/>
       <c r="AC194" s="69" t="n"/>
       <c r="AD194" s="70">
-        <f>IF(AND(COUNTIF($B$5:B194,B194)=1,$B194&lt;&gt;"",$AB194&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B194,B194)=1,$B194&lt;&gt;"",$AB194&lt;&gt;"",COUNTA($J194,$L194,$N194,$P194,$R194,$T194,$V194,$X194,$Z194)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE194" s="67" t="inlineStr">
@@ -17211,7 +17224,7 @@
       <c r="AB195" s="68" t="n"/>
       <c r="AC195" s="69" t="n"/>
       <c r="AD195" s="70">
-        <f>IF(AND(COUNTIF($B$5:B195,B195)=1,$B195&lt;&gt;"",$AB195&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B195,B195)=1,$B195&lt;&gt;"",$AB195&lt;&gt;"",COUNTA($J195,$L195,$N195,$P195,$R195,$T195,$V195,$X195,$Z195)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE195" s="67" t="inlineStr">
@@ -17289,7 +17302,7 @@
       <c r="AB196" s="68" t="n"/>
       <c r="AC196" s="69" t="n"/>
       <c r="AD196" s="70">
-        <f>IF(AND(COUNTIF($B$5:B196,B196)=1,$B196&lt;&gt;"",$AB196&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B196,B196)=1,$B196&lt;&gt;"",$AB196&lt;&gt;"",COUNTA($J196,$L196,$N196,$P196,$R196,$T196,$V196,$X196,$Z196)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE196" s="67" t="inlineStr">
@@ -17367,7 +17380,7 @@
       <c r="AB197" s="68" t="n"/>
       <c r="AC197" s="69" t="n"/>
       <c r="AD197" s="70">
-        <f>IF(AND(COUNTIF($B$5:B197,B197)=1,$B197&lt;&gt;"",$AB197&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B197,B197)=1,$B197&lt;&gt;"",$AB197&lt;&gt;"",COUNTA($J197,$L197,$N197,$P197,$R197,$T197,$V197,$X197,$Z197)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE197" s="67" t="inlineStr">
@@ -17445,7 +17458,7 @@
       <c r="AB198" s="68" t="n"/>
       <c r="AC198" s="69" t="n"/>
       <c r="AD198" s="70">
-        <f>IF(AND(COUNTIF($B$5:B198,B198)=1,$B198&lt;&gt;"",$AB198&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B198,B198)=1,$B198&lt;&gt;"",$AB198&lt;&gt;"",COUNTA($J198,$L198,$N198,$P198,$R198,$T198,$V198,$X198,$Z198)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE198" s="67" t="inlineStr">
@@ -17523,7 +17536,7 @@
       <c r="AB199" s="68" t="n"/>
       <c r="AC199" s="69" t="n"/>
       <c r="AD199" s="70">
-        <f>IF(AND(COUNTIF($B$5:B199,B199)=1,$B199&lt;&gt;"",$AB199&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B199,B199)=1,$B199&lt;&gt;"",$AB199&lt;&gt;"",COUNTA($J199,$L199,$N199,$P199,$R199,$T199,$V199,$X199,$Z199)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE199" s="67" t="inlineStr">
@@ -17601,7 +17614,7 @@
       <c r="AB200" s="68" t="n"/>
       <c r="AC200" s="69" t="n"/>
       <c r="AD200" s="70">
-        <f>IF(AND(COUNTIF($B$5:B200,B200)=1,$B200&lt;&gt;"",$AB200&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B200,B200)=1,$B200&lt;&gt;"",$AB200&lt;&gt;"",COUNTA($J200,$L200,$N200,$P200,$R200,$T200,$V200,$X200,$Z200)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE200" s="67" t="inlineStr">
@@ -17679,7 +17692,7 @@
       <c r="AB201" s="68" t="n"/>
       <c r="AC201" s="69" t="n"/>
       <c r="AD201" s="70">
-        <f>IF(AND(COUNTIF($B$5:B201,B201)=1,$B201&lt;&gt;"",$AB201&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B201,B201)=1,$B201&lt;&gt;"",$AB201&lt;&gt;"",COUNTA($J201,$L201,$N201,$P201,$R201,$T201,$V201,$X201,$Z201)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE201" s="67" t="inlineStr">
@@ -17757,7 +17770,7 @@
       <c r="AB202" s="68" t="n"/>
       <c r="AC202" s="69" t="n"/>
       <c r="AD202" s="70">
-        <f>IF(AND(COUNTIF($B$5:B202,B202)=1,$B202&lt;&gt;"",$AB202&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B202,B202)=1,$B202&lt;&gt;"",$AB202&lt;&gt;"",COUNTA($J202,$L202,$N202,$P202,$R202,$T202,$V202,$X202,$Z202)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE202" s="67" t="inlineStr">
@@ -17835,7 +17848,7 @@
       <c r="AB203" s="68" t="n"/>
       <c r="AC203" s="69" t="n"/>
       <c r="AD203" s="70">
-        <f>IF(AND(COUNTIF($B$5:B203,B203)=1,$B203&lt;&gt;"",$AB203&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B203,B203)=1,$B203&lt;&gt;"",$AB203&lt;&gt;"",COUNTA($J203,$L203,$N203,$P203,$R203,$T203,$V203,$X203,$Z203)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE203" s="67" t="inlineStr">
@@ -17909,7 +17922,7 @@
       <c r="AB204" s="68" t="n"/>
       <c r="AC204" s="69" t="n"/>
       <c r="AD204" s="70">
-        <f>IF(AND(COUNTIF($B$5:B204,B204)=1,$B204&lt;&gt;"",$AB204&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B204,B204)=1,$B204&lt;&gt;"",$AB204&lt;&gt;"",COUNTA($J204,$L204,$N204,$P204,$R204,$T204,$V204,$X204,$Z204)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE204" s="67" t="inlineStr">
@@ -17983,7 +17996,7 @@
       <c r="AB205" s="68" t="n"/>
       <c r="AC205" s="69" t="n"/>
       <c r="AD205" s="70">
-        <f>IF(AND(COUNTIF($B$5:B205,B205)=1,$B205&lt;&gt;"",$AB205&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B205,B205)=1,$B205&lt;&gt;"",$AB205&lt;&gt;"",COUNTA($J205,$L205,$N205,$P205,$R205,$T205,$V205,$X205,$Z205)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE205" s="67" t="inlineStr">
@@ -18061,7 +18074,7 @@
       <c r="AB206" s="68" t="n"/>
       <c r="AC206" s="69" t="n"/>
       <c r="AD206" s="70">
-        <f>IF(AND(COUNTIF($B$5:B206,B206)=1,$B206&lt;&gt;"",$AB206&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B206,B206)=1,$B206&lt;&gt;"",$AB206&lt;&gt;"",COUNTA($J206,$L206,$N206,$P206,$R206,$T206,$V206,$X206,$Z206)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE206" s="67" t="inlineStr">
@@ -18139,7 +18152,7 @@
       <c r="AB207" s="68" t="n"/>
       <c r="AC207" s="69" t="n"/>
       <c r="AD207" s="70">
-        <f>IF(AND(COUNTIF($B$5:B207,B207)=1,$B207&lt;&gt;"",$AB207&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B207,B207)=1,$B207&lt;&gt;"",$AB207&lt;&gt;"",COUNTA($J207,$L207,$N207,$P207,$R207,$T207,$V207,$X207,$Z207)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE207" s="67" t="inlineStr">
@@ -18217,7 +18230,7 @@
       <c r="AB208" s="68" t="n"/>
       <c r="AC208" s="69" t="n"/>
       <c r="AD208" s="70">
-        <f>IF(AND(COUNTIF($B$5:B208,B208)=1,$B208&lt;&gt;"",$AB208&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B208,B208)=1,$B208&lt;&gt;"",$AB208&lt;&gt;"",COUNTA($J208,$L208,$N208,$P208,$R208,$T208,$V208,$X208,$Z208)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE208" s="67" t="inlineStr">
@@ -18295,7 +18308,7 @@
       <c r="AB209" s="68" t="n"/>
       <c r="AC209" s="69" t="n"/>
       <c r="AD209" s="70">
-        <f>IF(AND(COUNTIF($B$5:B209,B209)=1,$B209&lt;&gt;"",$AB209&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B209,B209)=1,$B209&lt;&gt;"",$AB209&lt;&gt;"",COUNTA($J209,$L209,$N209,$P209,$R209,$T209,$V209,$X209,$Z209)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE209" s="67" t="inlineStr">
@@ -18373,7 +18386,7 @@
       <c r="AB210" s="68" t="n"/>
       <c r="AC210" s="69" t="n"/>
       <c r="AD210" s="70">
-        <f>IF(AND(COUNTIF($B$5:B210,B210)=1,$B210&lt;&gt;"",$AB210&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B210,B210)=1,$B210&lt;&gt;"",$AB210&lt;&gt;"",COUNTA($J210,$L210,$N210,$P210,$R210,$T210,$V210,$X210,$Z210)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE210" s="67" t="inlineStr">
@@ -18451,7 +18464,7 @@
       <c r="AB211" s="68" t="n"/>
       <c r="AC211" s="69" t="n"/>
       <c r="AD211" s="70">
-        <f>IF(AND(COUNTIF($B$5:B211,B211)=1,$B211&lt;&gt;"",$AB211&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B211,B211)=1,$B211&lt;&gt;"",$AB211&lt;&gt;"",COUNTA($J211,$L211,$N211,$P211,$R211,$T211,$V211,$X211,$Z211)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE211" s="67" t="inlineStr">
@@ -18529,7 +18542,7 @@
       <c r="AB212" s="68" t="n"/>
       <c r="AC212" s="69" t="n"/>
       <c r="AD212" s="70">
-        <f>IF(AND(COUNTIF($B$5:B212,B212)=1,$B212&lt;&gt;"",$AB212&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B212,B212)=1,$B212&lt;&gt;"",$AB212&lt;&gt;"",COUNTA($J212,$L212,$N212,$P212,$R212,$T212,$V212,$X212,$Z212)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE212" s="67" t="inlineStr">
@@ -18607,7 +18620,7 @@
       <c r="AB213" s="68" t="n"/>
       <c r="AC213" s="69" t="n"/>
       <c r="AD213" s="70">
-        <f>IF(AND(COUNTIF($B$5:B213,B213)=1,$B213&lt;&gt;"",$AB213&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B213,B213)=1,$B213&lt;&gt;"",$AB213&lt;&gt;"",COUNTA($J213,$L213,$N213,$P213,$R213,$T213,$V213,$X213,$Z213)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE213" s="67" t="inlineStr">
@@ -18681,7 +18694,7 @@
       <c r="AB214" s="68" t="n"/>
       <c r="AC214" s="69" t="n"/>
       <c r="AD214" s="70">
-        <f>IF(AND(COUNTIF($B$5:B214,B214)=1,$B214&lt;&gt;"",$AB214&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B214,B214)=1,$B214&lt;&gt;"",$AB214&lt;&gt;"",COUNTA($J214,$L214,$N214,$P214,$R214,$T214,$V214,$X214,$Z214)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE214" s="67" t="inlineStr">
@@ -18755,7 +18768,7 @@
       <c r="AB215" s="68" t="n"/>
       <c r="AC215" s="69" t="n"/>
       <c r="AD215" s="70">
-        <f>IF(AND(COUNTIF($B$5:B215,B215)=1,$B215&lt;&gt;"",$AB215&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B215,B215)=1,$B215&lt;&gt;"",$AB215&lt;&gt;"",COUNTA($J215,$L215,$N215,$P215,$R215,$T215,$V215,$X215,$Z215)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE215" s="67" t="inlineStr">
@@ -18833,7 +18846,7 @@
       <c r="AB216" s="68" t="n"/>
       <c r="AC216" s="69" t="n"/>
       <c r="AD216" s="70">
-        <f>IF(AND(COUNTIF($B$5:B216,B216)=1,$B216&lt;&gt;"",$AB216&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B216,B216)=1,$B216&lt;&gt;"",$AB216&lt;&gt;"",COUNTA($J216,$L216,$N216,$P216,$R216,$T216,$V216,$X216,$Z216)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE216" s="67" t="inlineStr">
@@ -18911,7 +18924,7 @@
       <c r="AB217" s="68" t="n"/>
       <c r="AC217" s="69" t="n"/>
       <c r="AD217" s="70">
-        <f>IF(AND(COUNTIF($B$5:B217,B217)=1,$B217&lt;&gt;"",$AB217&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B217,B217)=1,$B217&lt;&gt;"",$AB217&lt;&gt;"",COUNTA($J217,$L217,$N217,$P217,$R217,$T217,$V217,$X217,$Z217)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE217" s="67" t="inlineStr">
@@ -18989,7 +19002,7 @@
       <c r="AB218" s="68" t="n"/>
       <c r="AC218" s="69" t="n"/>
       <c r="AD218" s="70">
-        <f>IF(AND(COUNTIF($B$5:B218,B218)=1,$B218&lt;&gt;"",$AB218&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B218,B218)=1,$B218&lt;&gt;"",$AB218&lt;&gt;"",COUNTA($J218,$L218,$N218,$P218,$R218,$T218,$V218,$X218,$Z218)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE218" s="67" t="inlineStr">
@@ -19067,7 +19080,7 @@
       <c r="AB219" s="68" t="n"/>
       <c r="AC219" s="69" t="n"/>
       <c r="AD219" s="70">
-        <f>IF(AND(COUNTIF($B$5:B219,B219)=1,$B219&lt;&gt;"",$AB219&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B219,B219)=1,$B219&lt;&gt;"",$AB219&lt;&gt;"",COUNTA($J219,$L219,$N219,$P219,$R219,$T219,$V219,$X219,$Z219)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE219" s="67" t="inlineStr">
@@ -19145,7 +19158,7 @@
       <c r="AB220" s="68" t="n"/>
       <c r="AC220" s="69" t="n"/>
       <c r="AD220" s="70">
-        <f>IF(AND(COUNTIF($B$5:B220,B220)=1,$B220&lt;&gt;"",$AB220&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B220,B220)=1,$B220&lt;&gt;"",$AB220&lt;&gt;"",COUNTA($J220,$L220,$N220,$P220,$R220,$T220,$V220,$X220,$Z220)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE220" s="67" t="inlineStr">
@@ -19223,7 +19236,7 @@
       <c r="AB221" s="68" t="n"/>
       <c r="AC221" s="69" t="n"/>
       <c r="AD221" s="70">
-        <f>IF(AND(COUNTIF($B$5:B221,B221)=1,$B221&lt;&gt;"",$AB221&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B221,B221)=1,$B221&lt;&gt;"",$AB221&lt;&gt;"",COUNTA($J221,$L221,$N221,$P221,$R221,$T221,$V221,$X221,$Z221)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE221" s="67" t="inlineStr">
@@ -19297,7 +19310,7 @@
       <c r="AB222" s="68" t="n"/>
       <c r="AC222" s="69" t="n"/>
       <c r="AD222" s="70">
-        <f>IF(AND(COUNTIF($B$5:B222,B222)=1,$B222&lt;&gt;"",$AB222&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B222,B222)=1,$B222&lt;&gt;"",$AB222&lt;&gt;"",COUNTA($J222,$L222,$N222,$P222,$R222,$T222,$V222,$X222,$Z222)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE222" s="67" t="inlineStr">
@@ -19371,7 +19384,7 @@
       <c r="AB223" s="68" t="n"/>
       <c r="AC223" s="69" t="n"/>
       <c r="AD223" s="70">
-        <f>IF(AND(COUNTIF($B$5:B223,B223)=1,$B223&lt;&gt;"",$AB223&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B223,B223)=1,$B223&lt;&gt;"",$AB223&lt;&gt;"",COUNTA($J223,$L223,$N223,$P223,$R223,$T223,$V223,$X223,$Z223)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE223" s="67" t="inlineStr">
@@ -19445,7 +19458,7 @@
       <c r="AB224" s="68" t="n"/>
       <c r="AC224" s="69" t="n"/>
       <c r="AD224" s="70">
-        <f>IF(AND(COUNTIF($B$5:B224,B224)=1,$B224&lt;&gt;"",$AB224&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B224,B224)=1,$B224&lt;&gt;"",$AB224&lt;&gt;"",COUNTA($J224,$L224,$N224,$P224,$R224,$T224,$V224,$X224,$Z224)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE224" s="67" t="inlineStr">
@@ -19519,7 +19532,7 @@
       <c r="AB225" s="68" t="n"/>
       <c r="AC225" s="69" t="n"/>
       <c r="AD225" s="70">
-        <f>IF(AND(COUNTIF($B$5:B225,B225)=1,$B225&lt;&gt;"",$AB225&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B225,B225)=1,$B225&lt;&gt;"",$AB225&lt;&gt;"",COUNTA($J225,$L225,$N225,$P225,$R225,$T225,$V225,$X225,$Z225)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE225" s="67" t="inlineStr">
@@ -19597,7 +19610,7 @@
       <c r="AB226" s="68" t="n"/>
       <c r="AC226" s="69" t="n"/>
       <c r="AD226" s="70">
-        <f>IF(AND(COUNTIF($B$5:B226,B226)=1,$B226&lt;&gt;"",$AB226&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B226,B226)=1,$B226&lt;&gt;"",$AB226&lt;&gt;"",COUNTA($J226,$L226,$N226,$P226,$R226,$T226,$V226,$X226,$Z226)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE226" s="67" t="inlineStr">
@@ -19675,7 +19688,7 @@
       <c r="AB227" s="68" t="n"/>
       <c r="AC227" s="69" t="n"/>
       <c r="AD227" s="70">
-        <f>IF(AND(COUNTIF($B$5:B227,B227)=1,$B227&lt;&gt;"",$AB227&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B227,B227)=1,$B227&lt;&gt;"",$AB227&lt;&gt;"",COUNTA($J227,$L227,$N227,$P227,$R227,$T227,$V227,$X227,$Z227)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE227" s="67" t="inlineStr">
@@ -19753,7 +19766,7 @@
       <c r="AB228" s="68" t="n"/>
       <c r="AC228" s="69" t="n"/>
       <c r="AD228" s="70">
-        <f>IF(AND(COUNTIF($B$5:B228,B228)=1,$B228&lt;&gt;"",$AB228&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B228,B228)=1,$B228&lt;&gt;"",$AB228&lt;&gt;"",COUNTA($J228,$L228,$N228,$P228,$R228,$T228,$V228,$X228,$Z228)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE228" s="67" t="inlineStr">
@@ -19831,7 +19844,7 @@
       <c r="AB229" s="68" t="n"/>
       <c r="AC229" s="69" t="n"/>
       <c r="AD229" s="70">
-        <f>IF(AND(COUNTIF($B$5:B229,B229)=1,$B229&lt;&gt;"",$AB229&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B229,B229)=1,$B229&lt;&gt;"",$AB229&lt;&gt;"",COUNTA($J229,$L229,$N229,$P229,$R229,$T229,$V229,$X229,$Z229)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE229" s="67" t="inlineStr">
@@ -19909,7 +19922,7 @@
       <c r="AB230" s="68" t="n"/>
       <c r="AC230" s="69" t="n"/>
       <c r="AD230" s="70">
-        <f>IF(AND(COUNTIF($B$5:B230,B230)=1,$B230&lt;&gt;"",$AB230&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B230,B230)=1,$B230&lt;&gt;"",$AB230&lt;&gt;"",COUNTA($J230,$L230,$N230,$P230,$R230,$T230,$V230,$X230,$Z230)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE230" s="67" t="inlineStr">
@@ -19987,7 +20000,7 @@
       <c r="AB231" s="68" t="n"/>
       <c r="AC231" s="69" t="n"/>
       <c r="AD231" s="70">
-        <f>IF(AND(COUNTIF($B$5:B231,B231)=1,$B231&lt;&gt;"",$AB231&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B231,B231)=1,$B231&lt;&gt;"",$AB231&lt;&gt;"",COUNTA($J231,$L231,$N231,$P231,$R231,$T231,$V231,$X231,$Z231)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE231" s="67" t="inlineStr">
@@ -20065,7 +20078,7 @@
       <c r="AB232" s="68" t="n"/>
       <c r="AC232" s="69" t="n"/>
       <c r="AD232" s="70">
-        <f>IF(AND(COUNTIF($B$5:B232,B232)=1,$B232&lt;&gt;"",$AB232&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B232,B232)=1,$B232&lt;&gt;"",$AB232&lt;&gt;"",COUNTA($J232,$L232,$N232,$P232,$R232,$T232,$V232,$X232,$Z232)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE232" s="67" t="inlineStr">
@@ -20143,7 +20156,7 @@
       <c r="AB233" s="68" t="n"/>
       <c r="AC233" s="69" t="n"/>
       <c r="AD233" s="70">
-        <f>IF(AND(COUNTIF($B$5:B233,B233)=1,$B233&lt;&gt;"",$AB233&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B233,B233)=1,$B233&lt;&gt;"",$AB233&lt;&gt;"",COUNTA($J233,$L233,$N233,$P233,$R233,$T233,$V233,$X233,$Z233)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE233" s="67" t="inlineStr">
@@ -20221,7 +20234,7 @@
       <c r="AB234" s="68" t="n"/>
       <c r="AC234" s="69" t="n"/>
       <c r="AD234" s="70">
-        <f>IF(AND(COUNTIF($B$5:B234,B234)=1,$B234&lt;&gt;"",$AB234&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B234,B234)=1,$B234&lt;&gt;"",$AB234&lt;&gt;"",COUNTA($J234,$L234,$N234,$P234,$R234,$T234,$V234,$X234,$Z234)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE234" s="67" t="inlineStr">
@@ -20299,7 +20312,7 @@
       <c r="AB235" s="68" t="n"/>
       <c r="AC235" s="69" t="n"/>
       <c r="AD235" s="70">
-        <f>IF(AND(COUNTIF($B$5:B235,B235)=1,$B235&lt;&gt;"",$AB235&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B235,B235)=1,$B235&lt;&gt;"",$AB235&lt;&gt;"",COUNTA($J235,$L235,$N235,$P235,$R235,$T235,$V235,$X235,$Z235)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE235" s="67" t="inlineStr">
@@ -20373,7 +20386,7 @@
       <c r="AB236" s="68" t="n"/>
       <c r="AC236" s="69" t="n"/>
       <c r="AD236" s="70">
-        <f>IF(AND(COUNTIF($B$5:B236,B236)=1,$B236&lt;&gt;"",$AB236&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B236,B236)=1,$B236&lt;&gt;"",$AB236&lt;&gt;"",COUNTA($J236,$L236,$N236,$P236,$R236,$T236,$V236,$X236,$Z236)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE236" s="67" t="inlineStr">
@@ -20447,7 +20460,7 @@
       <c r="AB237" s="68" t="n"/>
       <c r="AC237" s="69" t="n"/>
       <c r="AD237" s="70">
-        <f>IF(AND(COUNTIF($B$5:B237,B237)=1,$B237&lt;&gt;"",$AB237&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B237,B237)=1,$B237&lt;&gt;"",$AB237&lt;&gt;"",COUNTA($J237,$L237,$N237,$P237,$R237,$T237,$V237,$X237,$Z237)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE237" s="67" t="inlineStr">
@@ -20521,7 +20534,7 @@
       <c r="AB238" s="68" t="n"/>
       <c r="AC238" s="69" t="n"/>
       <c r="AD238" s="70">
-        <f>IF(AND(COUNTIF($B$5:B238,B238)=1,$B238&lt;&gt;"",$AB238&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B238,B238)=1,$B238&lt;&gt;"",$AB238&lt;&gt;"",COUNTA($J238,$L238,$N238,$P238,$R238,$T238,$V238,$X238,$Z238)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE238" s="67" t="inlineStr">
@@ -20595,7 +20608,7 @@
       <c r="AB239" s="68" t="n"/>
       <c r="AC239" s="69" t="n"/>
       <c r="AD239" s="70">
-        <f>IF(AND(COUNTIF($B$5:B239,B239)=1,$B239&lt;&gt;"",$AB239&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B239,B239)=1,$B239&lt;&gt;"",$AB239&lt;&gt;"",COUNTA($J239,$L239,$N239,$P239,$R239,$T239,$V239,$X239,$Z239)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE239" s="67" t="inlineStr">
@@ -20673,7 +20686,7 @@
       <c r="AB240" s="68" t="n"/>
       <c r="AC240" s="69" t="n"/>
       <c r="AD240" s="70">
-        <f>IF(AND(COUNTIF($B$5:B240,B240)=1,$B240&lt;&gt;"",$AB240&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B240,B240)=1,$B240&lt;&gt;"",$AB240&lt;&gt;"",COUNTA($J240,$L240,$N240,$P240,$R240,$T240,$V240,$X240,$Z240)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE240" s="67" t="inlineStr">
@@ -20751,7 +20764,7 @@
       <c r="AB241" s="68" t="n"/>
       <c r="AC241" s="69" t="n"/>
       <c r="AD241" s="70">
-        <f>IF(AND(COUNTIF($B$5:B241,B241)=1,$B241&lt;&gt;"",$AB241&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B241,B241)=1,$B241&lt;&gt;"",$AB241&lt;&gt;"",COUNTA($J241,$L241,$N241,$P241,$R241,$T241,$V241,$X241,$Z241)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE241" s="67" t="inlineStr">
@@ -20829,7 +20842,7 @@
       <c r="AB242" s="68" t="n"/>
       <c r="AC242" s="69" t="n"/>
       <c r="AD242" s="70">
-        <f>IF(AND(COUNTIF($B$5:B242,B242)=1,$B242&lt;&gt;"",$AB242&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B242,B242)=1,$B242&lt;&gt;"",$AB242&lt;&gt;"",COUNTA($J242,$L242,$N242,$P242,$R242,$T242,$V242,$X242,$Z242)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE242" s="67" t="inlineStr">
@@ -20907,7 +20920,7 @@
       <c r="AB243" s="68" t="n"/>
       <c r="AC243" s="69" t="n"/>
       <c r="AD243" s="70">
-        <f>IF(AND(COUNTIF($B$5:B243,B243)=1,$B243&lt;&gt;"",$AB243&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B243,B243)=1,$B243&lt;&gt;"",$AB243&lt;&gt;"",COUNTA($J243,$L243,$N243,$P243,$R243,$T243,$V243,$X243,$Z243)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE243" s="67" t="inlineStr">
@@ -20981,7 +20994,7 @@
       <c r="AB244" s="68" t="n"/>
       <c r="AC244" s="69" t="n"/>
       <c r="AD244" s="70">
-        <f>IF(AND(COUNTIF($B$5:B244,B244)=1,$B244&lt;&gt;"",$AB244&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B244,B244)=1,$B244&lt;&gt;"",$AB244&lt;&gt;"",COUNTA($J244,$L244,$N244,$P244,$R244,$T244,$V244,$X244,$Z244)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE244" s="67" t="inlineStr">
@@ -21055,7 +21068,7 @@
       <c r="AB245" s="68" t="n"/>
       <c r="AC245" s="69" t="n"/>
       <c r="AD245" s="70">
-        <f>IF(AND(COUNTIF($B$5:B245,B245)=1,$B245&lt;&gt;"",$AB245&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B245,B245)=1,$B245&lt;&gt;"",$AB245&lt;&gt;"",COUNTA($J245,$L245,$N245,$P245,$R245,$T245,$V245,$X245,$Z245)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE245" s="67" t="inlineStr">
@@ -21133,7 +21146,7 @@
       <c r="AB246" s="68" t="n"/>
       <c r="AC246" s="69" t="n"/>
       <c r="AD246" s="70">
-        <f>IF(AND(COUNTIF($B$5:B246,B246)=1,$B246&lt;&gt;"",$AB246&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B246,B246)=1,$B246&lt;&gt;"",$AB246&lt;&gt;"",COUNTA($J246,$L246,$N246,$P246,$R246,$T246,$V246,$X246,$Z246)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE246" s="67" t="inlineStr">
@@ -21211,7 +21224,7 @@
       <c r="AB247" s="68" t="n"/>
       <c r="AC247" s="69" t="n"/>
       <c r="AD247" s="70">
-        <f>IF(AND(COUNTIF($B$5:B247,B247)=1,$B247&lt;&gt;"",$AB247&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B247,B247)=1,$B247&lt;&gt;"",$AB247&lt;&gt;"",COUNTA($J247,$L247,$N247,$P247,$R247,$T247,$V247,$X247,$Z247)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE247" s="67" t="inlineStr">
@@ -21289,7 +21302,7 @@
       <c r="AB248" s="68" t="n"/>
       <c r="AC248" s="69" t="n"/>
       <c r="AD248" s="70">
-        <f>IF(AND(COUNTIF($B$5:B248,B248)=1,$B248&lt;&gt;"",$AB248&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B248,B248)=1,$B248&lt;&gt;"",$AB248&lt;&gt;"",COUNTA($J248,$L248,$N248,$P248,$R248,$T248,$V248,$X248,$Z248)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE248" s="67" t="inlineStr">
@@ -21367,7 +21380,7 @@
       <c r="AB249" s="68" t="n"/>
       <c r="AC249" s="69" t="n"/>
       <c r="AD249" s="70">
-        <f>IF(AND(COUNTIF($B$5:B249,B249)=1,$B249&lt;&gt;"",$AB249&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B249,B249)=1,$B249&lt;&gt;"",$AB249&lt;&gt;"",COUNTA($J249,$L249,$N249,$P249,$R249,$T249,$V249,$X249,$Z249)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE249" s="67" t="inlineStr">
@@ -21441,7 +21454,7 @@
       <c r="AB250" s="68" t="n"/>
       <c r="AC250" s="69" t="n"/>
       <c r="AD250" s="70">
-        <f>IF(AND(COUNTIF($B$5:B250,B250)=1,$B250&lt;&gt;"",$AB250&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B250,B250)=1,$B250&lt;&gt;"",$AB250&lt;&gt;"",COUNTA($J250,$L250,$N250,$P250,$R250,$T250,$V250,$X250,$Z250)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE250" s="67" t="inlineStr">
@@ -21515,7 +21528,7 @@
       <c r="AB251" s="68" t="n"/>
       <c r="AC251" s="69" t="n"/>
       <c r="AD251" s="70">
-        <f>IF(AND(COUNTIF($B$5:B251,B251)=1,$B251&lt;&gt;"",$AB251&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B251,B251)=1,$B251&lt;&gt;"",$AB251&lt;&gt;"",COUNTA($J251,$L251,$N251,$P251,$R251,$T251,$V251,$X251,$Z251)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE251" s="67" t="inlineStr">
@@ -21593,7 +21606,7 @@
       <c r="AB252" s="68" t="n"/>
       <c r="AC252" s="69" t="n"/>
       <c r="AD252" s="70">
-        <f>IF(AND(COUNTIF($B$5:B252,B252)=1,$B252&lt;&gt;"",$AB252&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B252,B252)=1,$B252&lt;&gt;"",$AB252&lt;&gt;"",COUNTA($J252,$L252,$N252,$P252,$R252,$T252,$V252,$X252,$Z252)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE252" s="67" t="inlineStr">
@@ -21671,7 +21684,7 @@
       <c r="AB253" s="68" t="n"/>
       <c r="AC253" s="69" t="n"/>
       <c r="AD253" s="70">
-        <f>IF(AND(COUNTIF($B$5:B253,B253)=1,$B253&lt;&gt;"",$AB253&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B253,B253)=1,$B253&lt;&gt;"",$AB253&lt;&gt;"",COUNTA($J253,$L253,$N253,$P253,$R253,$T253,$V253,$X253,$Z253)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE253" s="67" t="inlineStr">
@@ -21749,7 +21762,7 @@
       <c r="AB254" s="68" t="n"/>
       <c r="AC254" s="69" t="n"/>
       <c r="AD254" s="70">
-        <f>IF(AND(COUNTIF($B$5:B254,B254)=1,$B254&lt;&gt;"",$AB254&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B254,B254)=1,$B254&lt;&gt;"",$AB254&lt;&gt;"",COUNTA($J254,$L254,$N254,$P254,$R254,$T254,$V254,$X254,$Z254)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE254" s="67" t="inlineStr">
@@ -21827,7 +21840,7 @@
       <c r="AB255" s="68" t="n"/>
       <c r="AC255" s="69" t="n"/>
       <c r="AD255" s="70">
-        <f>IF(AND(COUNTIF($B$5:B255,B255)=1,$B255&lt;&gt;"",$AB255&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B255,B255)=1,$B255&lt;&gt;"",$AB255&lt;&gt;"",COUNTA($J255,$L255,$N255,$P255,$R255,$T255,$V255,$X255,$Z255)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE255" s="67" t="inlineStr">
@@ -21905,7 +21918,7 @@
       <c r="AB256" s="68" t="n"/>
       <c r="AC256" s="69" t="n"/>
       <c r="AD256" s="70">
-        <f>IF(AND(COUNTIF($B$5:B256,B256)=1,$B256&lt;&gt;"",$AB256&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B256,B256)=1,$B256&lt;&gt;"",$AB256&lt;&gt;"",COUNTA($J256,$L256,$N256,$P256,$R256,$T256,$V256,$X256,$Z256)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE256" s="67" t="inlineStr">
@@ -21983,7 +21996,7 @@
       <c r="AB257" s="68" t="n"/>
       <c r="AC257" s="69" t="n"/>
       <c r="AD257" s="70">
-        <f>IF(AND(COUNTIF($B$5:B257,B257)=1,$B257&lt;&gt;"",$AB257&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B257,B257)=1,$B257&lt;&gt;"",$AB257&lt;&gt;"",COUNTA($J257,$L257,$N257,$P257,$R257,$T257,$V257,$X257,$Z257)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE257" s="67" t="inlineStr">
@@ -22061,7 +22074,7 @@
       <c r="AB258" s="68" t="n"/>
       <c r="AC258" s="69" t="n"/>
       <c r="AD258" s="70">
-        <f>IF(AND(COUNTIF($B$5:B258,B258)=1,$B258&lt;&gt;"",$AB258&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B258,B258)=1,$B258&lt;&gt;"",$AB258&lt;&gt;"",COUNTA($J258,$L258,$N258,$P258,$R258,$T258,$V258,$X258,$Z258)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE258" s="67" t="inlineStr">
@@ -22139,7 +22152,7 @@
       <c r="AB259" s="68" t="n"/>
       <c r="AC259" s="69" t="n"/>
       <c r="AD259" s="70">
-        <f>IF(AND(COUNTIF($B$5:B259,B259)=1,$B259&lt;&gt;"",$AB259&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B259,B259)=1,$B259&lt;&gt;"",$AB259&lt;&gt;"",COUNTA($J259,$L259,$N259,$P259,$R259,$T259,$V259,$X259,$Z259)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE259" s="67" t="inlineStr">
@@ -22217,7 +22230,7 @@
       <c r="AB260" s="68" t="n"/>
       <c r="AC260" s="69" t="n"/>
       <c r="AD260" s="70">
-        <f>IF(AND(COUNTIF($B$5:B260,B260)=1,$B260&lt;&gt;"",$AB260&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B260,B260)=1,$B260&lt;&gt;"",$AB260&lt;&gt;"",COUNTA($J260,$L260,$N260,$P260,$R260,$T260,$V260,$X260,$Z260)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE260" s="67" t="inlineStr">
@@ -22295,7 +22308,7 @@
       <c r="AB261" s="68" t="n"/>
       <c r="AC261" s="69" t="n"/>
       <c r="AD261" s="70">
-        <f>IF(AND(COUNTIF($B$5:B261,B261)=1,$B261&lt;&gt;"",$AB261&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B261,B261)=1,$B261&lt;&gt;"",$AB261&lt;&gt;"",COUNTA($J261,$L261,$N261,$P261,$R261,$T261,$V261,$X261,$Z261)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE261" s="67" t="inlineStr">
@@ -22373,7 +22386,7 @@
       <c r="AB262" s="68" t="n"/>
       <c r="AC262" s="69" t="n"/>
       <c r="AD262" s="70">
-        <f>IF(AND(COUNTIF($B$5:B262,B262)=1,$B262&lt;&gt;"",$AB262&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B262,B262)=1,$B262&lt;&gt;"",$AB262&lt;&gt;"",COUNTA($J262,$L262,$N262,$P262,$R262,$T262,$V262,$X262,$Z262)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE262" s="67" t="inlineStr">
@@ -22451,7 +22464,7 @@
       <c r="AB263" s="68" t="n"/>
       <c r="AC263" s="69" t="n"/>
       <c r="AD263" s="70">
-        <f>IF(AND(COUNTIF($B$5:B263,B263)=1,$B263&lt;&gt;"",$AB263&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B263,B263)=1,$B263&lt;&gt;"",$AB263&lt;&gt;"",COUNTA($J263,$L263,$N263,$P263,$R263,$T263,$V263,$X263,$Z263)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE263" s="67" t="inlineStr">
@@ -22525,7 +22538,7 @@
       <c r="AB264" s="68" t="n"/>
       <c r="AC264" s="69" t="n"/>
       <c r="AD264" s="70">
-        <f>IF(AND(COUNTIF($B$5:B264,B264)=1,$B264&lt;&gt;"",$AB264&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B264,B264)=1,$B264&lt;&gt;"",$AB264&lt;&gt;"",COUNTA($J264,$L264,$N264,$P264,$R264,$T264,$V264,$X264,$Z264)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE264" s="67" t="inlineStr">
@@ -22599,7 +22612,7 @@
       <c r="AB265" s="68" t="n"/>
       <c r="AC265" s="69" t="n"/>
       <c r="AD265" s="70">
-        <f>IF(AND(COUNTIF($B$5:B265,B265)=1,$B265&lt;&gt;"",$AB265&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B265,B265)=1,$B265&lt;&gt;"",$AB265&lt;&gt;"",COUNTA($J265,$L265,$N265,$P265,$R265,$T265,$V265,$X265,$Z265)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE265" s="67" t="inlineStr">
@@ -22677,7 +22690,7 @@
       <c r="AB266" s="68" t="n"/>
       <c r="AC266" s="69" t="n"/>
       <c r="AD266" s="70">
-        <f>IF(AND(COUNTIF($B$5:B266,B266)=1,$B266&lt;&gt;"",$AB266&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B266,B266)=1,$B266&lt;&gt;"",$AB266&lt;&gt;"",COUNTA($J266,$L266,$N266,$P266,$R266,$T266,$V266,$X266,$Z266)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE266" s="67" t="inlineStr">
@@ -22755,7 +22768,7 @@
       <c r="AB267" s="68" t="n"/>
       <c r="AC267" s="69" t="n"/>
       <c r="AD267" s="70">
-        <f>IF(AND(COUNTIF($B$5:B267,B267)=1,$B267&lt;&gt;"",$AB267&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B267,B267)=1,$B267&lt;&gt;"",$AB267&lt;&gt;"",COUNTA($J267,$L267,$N267,$P267,$R267,$T267,$V267,$X267,$Z267)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE267" s="67" t="inlineStr">
@@ -22833,7 +22846,7 @@
       <c r="AB268" s="68" t="n"/>
       <c r="AC268" s="69" t="n"/>
       <c r="AD268" s="70">
-        <f>IF(AND(COUNTIF($B$5:B268,B268)=1,$B268&lt;&gt;"",$AB268&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B268,B268)=1,$B268&lt;&gt;"",$AB268&lt;&gt;"",COUNTA($J268,$L268,$N268,$P268,$R268,$T268,$V268,$X268,$Z268)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE268" s="67" t="inlineStr">
@@ -22911,7 +22924,7 @@
       <c r="AB269" s="68" t="n"/>
       <c r="AC269" s="69" t="n"/>
       <c r="AD269" s="70">
-        <f>IF(AND(COUNTIF($B$5:B269,B269)=1,$B269&lt;&gt;"",$AB269&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B269,B269)=1,$B269&lt;&gt;"",$AB269&lt;&gt;"",COUNTA($J269,$L269,$N269,$P269,$R269,$T269,$V269,$X269,$Z269)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE269" s="67" t="inlineStr">
@@ -22989,7 +23002,7 @@
       <c r="AB270" s="68" t="n"/>
       <c r="AC270" s="69" t="n"/>
       <c r="AD270" s="70">
-        <f>IF(AND(COUNTIF($B$5:B270,B270)=1,$B270&lt;&gt;"",$AB270&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B270,B270)=1,$B270&lt;&gt;"",$AB270&lt;&gt;"",COUNTA($J270,$L270,$N270,$P270,$R270,$T270,$V270,$X270,$Z270)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE270" s="67" t="inlineStr">
@@ -23067,7 +23080,7 @@
       <c r="AB271" s="68" t="n"/>
       <c r="AC271" s="69" t="n"/>
       <c r="AD271" s="70">
-        <f>IF(AND(COUNTIF($B$5:B271,B271)=1,$B271&lt;&gt;"",$AB271&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B271,B271)=1,$B271&lt;&gt;"",$AB271&lt;&gt;"",COUNTA($J271,$L271,$N271,$P271,$R271,$T271,$V271,$X271,$Z271)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE271" s="67" t="inlineStr">
@@ -23141,7 +23154,7 @@
       <c r="AB272" s="68" t="n"/>
       <c r="AC272" s="69" t="n"/>
       <c r="AD272" s="70">
-        <f>IF(AND(COUNTIF($B$5:B272,B272)=1,$B272&lt;&gt;"",$AB272&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B272,B272)=1,$B272&lt;&gt;"",$AB272&lt;&gt;"",COUNTA($J272,$L272,$N272,$P272,$R272,$T272,$V272,$X272,$Z272)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE272" s="67" t="inlineStr">
@@ -23215,7 +23228,7 @@
       <c r="AB273" s="68" t="n"/>
       <c r="AC273" s="69" t="n"/>
       <c r="AD273" s="70">
-        <f>IF(AND(COUNTIF($B$5:B273,B273)=1,$B273&lt;&gt;"",$AB273&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B273,B273)=1,$B273&lt;&gt;"",$AB273&lt;&gt;"",COUNTA($J273,$L273,$N273,$P273,$R273,$T273,$V273,$X273,$Z273)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE273" s="67" t="inlineStr">
@@ -23293,7 +23306,7 @@
       <c r="AB274" s="68" t="n"/>
       <c r="AC274" s="69" t="n"/>
       <c r="AD274" s="70">
-        <f>IF(AND(COUNTIF($B$5:B274,B274)=1,$B274&lt;&gt;"",$AB274&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B274,B274)=1,$B274&lt;&gt;"",$AB274&lt;&gt;"",COUNTA($J274,$L274,$N274,$P274,$R274,$T274,$V274,$X274,$Z274)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE274" s="67" t="inlineStr">
@@ -23371,7 +23384,7 @@
       <c r="AB275" s="68" t="n"/>
       <c r="AC275" s="69" t="n"/>
       <c r="AD275" s="70">
-        <f>IF(AND(COUNTIF($B$5:B275,B275)=1,$B275&lt;&gt;"",$AB275&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B275,B275)=1,$B275&lt;&gt;"",$AB275&lt;&gt;"",COUNTA($J275,$L275,$N275,$P275,$R275,$T275,$V275,$X275,$Z275)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE275" s="67" t="inlineStr">
@@ -23449,7 +23462,7 @@
       <c r="AB276" s="68" t="n"/>
       <c r="AC276" s="69" t="n"/>
       <c r="AD276" s="70">
-        <f>IF(AND(COUNTIF($B$5:B276,B276)=1,$B276&lt;&gt;"",$AB276&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B276,B276)=1,$B276&lt;&gt;"",$AB276&lt;&gt;"",COUNTA($J276,$L276,$N276,$P276,$R276,$T276,$V276,$X276,$Z276)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE276" s="67" t="inlineStr">
@@ -23527,7 +23540,7 @@
       <c r="AB277" s="68" t="n"/>
       <c r="AC277" s="69" t="n"/>
       <c r="AD277" s="70">
-        <f>IF(AND(COUNTIF($B$5:B277,B277)=1,$B277&lt;&gt;"",$AB277&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B277,B277)=1,$B277&lt;&gt;"",$AB277&lt;&gt;"",COUNTA($J277,$L277,$N277,$P277,$R277,$T277,$V277,$X277,$Z277)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE277" s="67" t="inlineStr">
@@ -23605,7 +23618,7 @@
       <c r="AB278" s="68" t="n"/>
       <c r="AC278" s="69" t="n"/>
       <c r="AD278" s="70">
-        <f>IF(AND(COUNTIF($B$5:B278,B278)=1,$B278&lt;&gt;"",$AB278&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B278,B278)=1,$B278&lt;&gt;"",$AB278&lt;&gt;"",COUNTA($J278,$L278,$N278,$P278,$R278,$T278,$V278,$X278,$Z278)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE278" s="67" t="inlineStr">
@@ -23683,7 +23696,7 @@
       <c r="AB279" s="68" t="n"/>
       <c r="AC279" s="69" t="n"/>
       <c r="AD279" s="70">
-        <f>IF(AND(COUNTIF($B$5:B279,B279)=1,$B279&lt;&gt;"",$AB279&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B279,B279)=1,$B279&lt;&gt;"",$AB279&lt;&gt;"",COUNTA($J279,$L279,$N279,$P279,$R279,$T279,$V279,$X279,$Z279)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE279" s="67" t="inlineStr">
@@ -23761,7 +23774,7 @@
       <c r="AB280" s="68" t="n"/>
       <c r="AC280" s="69" t="n"/>
       <c r="AD280" s="70">
-        <f>IF(AND(COUNTIF($B$5:B280,B280)=1,$B280&lt;&gt;"",$AB280&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B280,B280)=1,$B280&lt;&gt;"",$AB280&lt;&gt;"",COUNTA($J280,$L280,$N280,$P280,$R280,$T280,$V280,$X280,$Z280)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE280" s="67" t="inlineStr">
@@ -23839,7 +23852,7 @@
       <c r="AB281" s="68" t="n"/>
       <c r="AC281" s="69" t="n"/>
       <c r="AD281" s="70">
-        <f>IF(AND(COUNTIF($B$5:B281,B281)=1,$B281&lt;&gt;"",$AB281&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B281,B281)=1,$B281&lt;&gt;"",$AB281&lt;&gt;"",COUNTA($J281,$L281,$N281,$P281,$R281,$T281,$V281,$X281,$Z281)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE281" s="67" t="inlineStr">
@@ -23917,7 +23930,7 @@
       <c r="AB282" s="68" t="n"/>
       <c r="AC282" s="69" t="n"/>
       <c r="AD282" s="70">
-        <f>IF(AND(COUNTIF($B$5:B282,B282)=1,$B282&lt;&gt;"",$AB282&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B282,B282)=1,$B282&lt;&gt;"",$AB282&lt;&gt;"",COUNTA($J282,$L282,$N282,$P282,$R282,$T282,$V282,$X282,$Z282)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE282" s="67" t="inlineStr">
@@ -23995,7 +24008,7 @@
       <c r="AB283" s="68" t="n"/>
       <c r="AC283" s="69" t="n"/>
       <c r="AD283" s="70">
-        <f>IF(AND(COUNTIF($B$5:B283,B283)=1,$B283&lt;&gt;"",$AB283&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B283,B283)=1,$B283&lt;&gt;"",$AB283&lt;&gt;"",COUNTA($J283,$L283,$N283,$P283,$R283,$T283,$V283,$X283,$Z283)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE283" s="67" t="inlineStr">
@@ -24069,7 +24082,7 @@
       <c r="AB284" s="68" t="n"/>
       <c r="AC284" s="69" t="n"/>
       <c r="AD284" s="70">
-        <f>IF(AND(COUNTIF($B$5:B284,B284)=1,$B284&lt;&gt;"",$AB284&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B284,B284)=1,$B284&lt;&gt;"",$AB284&lt;&gt;"",COUNTA($J284,$L284,$N284,$P284,$R284,$T284,$V284,$X284,$Z284)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE284" s="67" t="inlineStr">
@@ -24143,7 +24156,7 @@
       <c r="AB285" s="68" t="n"/>
       <c r="AC285" s="69" t="n"/>
       <c r="AD285" s="70">
-        <f>IF(AND(COUNTIF($B$5:B285,B285)=1,$B285&lt;&gt;"",$AB285&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B285,B285)=1,$B285&lt;&gt;"",$AB285&lt;&gt;"",COUNTA($J285,$L285,$N285,$P285,$R285,$T285,$V285,$X285,$Z285)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE285" s="67" t="inlineStr">
@@ -24221,7 +24234,7 @@
       <c r="AB286" s="68" t="n"/>
       <c r="AC286" s="69" t="n"/>
       <c r="AD286" s="70">
-        <f>IF(AND(COUNTIF($B$5:B286,B286)=1,$B286&lt;&gt;"",$AB286&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B286,B286)=1,$B286&lt;&gt;"",$AB286&lt;&gt;"",COUNTA($J286,$L286,$N286,$P286,$R286,$T286,$V286,$X286,$Z286)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE286" s="67" t="inlineStr">
@@ -24299,7 +24312,7 @@
       <c r="AB287" s="68" t="n"/>
       <c r="AC287" s="69" t="n"/>
       <c r="AD287" s="70">
-        <f>IF(AND(COUNTIF($B$5:B287,B287)=1,$B287&lt;&gt;"",$AB287&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B287,B287)=1,$B287&lt;&gt;"",$AB287&lt;&gt;"",COUNTA($J287,$L287,$N287,$P287,$R287,$T287,$V287,$X287,$Z287)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE287" s="67" t="inlineStr">
@@ -24377,7 +24390,7 @@
       <c r="AB288" s="68" t="n"/>
       <c r="AC288" s="69" t="n"/>
       <c r="AD288" s="70">
-        <f>IF(AND(COUNTIF($B$5:B288,B288)=1,$B288&lt;&gt;"",$AB288&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B288,B288)=1,$B288&lt;&gt;"",$AB288&lt;&gt;"",COUNTA($J288,$L288,$N288,$P288,$R288,$T288,$V288,$X288,$Z288)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE288" s="67" t="inlineStr">
@@ -24455,7 +24468,7 @@
       <c r="AB289" s="68" t="n"/>
       <c r="AC289" s="69" t="n"/>
       <c r="AD289" s="70">
-        <f>IF(AND(COUNTIF($B$5:B289,B289)=1,$B289&lt;&gt;"",$AB289&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B289,B289)=1,$B289&lt;&gt;"",$AB289&lt;&gt;"",COUNTA($J289,$L289,$N289,$P289,$R289,$T289,$V289,$X289,$Z289)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE289" s="67" t="inlineStr">
@@ -24533,7 +24546,7 @@
       <c r="AB290" s="68" t="n"/>
       <c r="AC290" s="69" t="n"/>
       <c r="AD290" s="70">
-        <f>IF(AND(COUNTIF($B$5:B290,B290)=1,$B290&lt;&gt;"",$AB290&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B290,B290)=1,$B290&lt;&gt;"",$AB290&lt;&gt;"",COUNTA($J290,$L290,$N290,$P290,$R290,$T290,$V290,$X290,$Z290)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE290" s="67" t="inlineStr">
@@ -24611,7 +24624,7 @@
       <c r="AB291" s="68" t="n"/>
       <c r="AC291" s="69" t="n"/>
       <c r="AD291" s="70">
-        <f>IF(AND(COUNTIF($B$5:B291,B291)=1,$B291&lt;&gt;"",$AB291&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B291,B291)=1,$B291&lt;&gt;"",$AB291&lt;&gt;"",COUNTA($J291,$L291,$N291,$P291,$R291,$T291,$V291,$X291,$Z291)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE291" s="67" t="inlineStr">
@@ -24689,7 +24702,7 @@
       <c r="AB292" s="68" t="n"/>
       <c r="AC292" s="69" t="n"/>
       <c r="AD292" s="70">
-        <f>IF(AND(COUNTIF($B$5:B292,B292)=1,$B292&lt;&gt;"",$AB292&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B292,B292)=1,$B292&lt;&gt;"",$AB292&lt;&gt;"",COUNTA($J292,$L292,$N292,$P292,$R292,$T292,$V292,$X292,$Z292)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE292" s="67" t="inlineStr">
@@ -24767,7 +24780,7 @@
       <c r="AB293" s="68" t="n"/>
       <c r="AC293" s="69" t="n"/>
       <c r="AD293" s="70">
-        <f>IF(AND(COUNTIF($B$5:B293,B293)=1,$B293&lt;&gt;"",$AB293&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B293,B293)=1,$B293&lt;&gt;"",$AB293&lt;&gt;"",COUNTA($J293,$L293,$N293,$P293,$R293,$T293,$V293,$X293,$Z293)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE293" s="67" t="inlineStr">
@@ -24841,7 +24854,7 @@
       <c r="AB294" s="68" t="n"/>
       <c r="AC294" s="69" t="n"/>
       <c r="AD294" s="70">
-        <f>IF(AND(COUNTIF($B$5:B294,B294)=1,$B294&lt;&gt;"",$AB294&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B294,B294)=1,$B294&lt;&gt;"",$AB294&lt;&gt;"",COUNTA($J294,$L294,$N294,$P294,$R294,$T294,$V294,$X294,$Z294)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE294" s="67" t="inlineStr">
@@ -24915,7 +24928,7 @@
       <c r="AB295" s="68" t="n"/>
       <c r="AC295" s="69" t="n"/>
       <c r="AD295" s="70">
-        <f>IF(AND(COUNTIF($B$5:B295,B295)=1,$B295&lt;&gt;"",$AB295&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B295,B295)=1,$B295&lt;&gt;"",$AB295&lt;&gt;"",COUNTA($J295,$L295,$N295,$P295,$R295,$T295,$V295,$X295,$Z295)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE295" s="67" t="inlineStr">
@@ -24993,7 +25006,7 @@
       <c r="AB296" s="68" t="n"/>
       <c r="AC296" s="69" t="n"/>
       <c r="AD296" s="70">
-        <f>IF(AND(COUNTIF($B$5:B296,B296)=1,$B296&lt;&gt;"",$AB296&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B296,B296)=1,$B296&lt;&gt;"",$AB296&lt;&gt;"",COUNTA($J296,$L296,$N296,$P296,$R296,$T296,$V296,$X296,$Z296)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE296" s="67" t="inlineStr">
@@ -25071,7 +25084,7 @@
       <c r="AB297" s="68" t="n"/>
       <c r="AC297" s="69" t="n"/>
       <c r="AD297" s="70">
-        <f>IF(AND(COUNTIF($B$5:B297,B297)=1,$B297&lt;&gt;"",$AB297&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B297,B297)=1,$B297&lt;&gt;"",$AB297&lt;&gt;"",COUNTA($J297,$L297,$N297,$P297,$R297,$T297,$V297,$X297,$Z297)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE297" s="67" t="inlineStr">
@@ -25149,7 +25162,7 @@
       <c r="AB298" s="68" t="n"/>
       <c r="AC298" s="69" t="n"/>
       <c r="AD298" s="70">
-        <f>IF(AND(COUNTIF($B$5:B298,B298)=1,$B298&lt;&gt;"",$AB298&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B298,B298)=1,$B298&lt;&gt;"",$AB298&lt;&gt;"",COUNTA($J298,$L298,$N298,$P298,$R298,$T298,$V298,$X298,$Z298)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE298" s="67" t="inlineStr">
@@ -25227,7 +25240,7 @@
       <c r="AB299" s="68" t="n"/>
       <c r="AC299" s="69" t="n"/>
       <c r="AD299" s="70">
-        <f>IF(AND(COUNTIF($B$5:B299,B299)=1,$B299&lt;&gt;"",$AB299&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B299,B299)=1,$B299&lt;&gt;"",$AB299&lt;&gt;"",COUNTA($J299,$L299,$N299,$P299,$R299,$T299,$V299,$X299,$Z299)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE299" s="67" t="inlineStr">
@@ -25305,7 +25318,7 @@
       <c r="AB300" s="68" t="n"/>
       <c r="AC300" s="69" t="n"/>
       <c r="AD300" s="70">
-        <f>IF(AND(COUNTIF($B$5:B300,B300)=1,$B300&lt;&gt;"",$AB300&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B300,B300)=1,$B300&lt;&gt;"",$AB300&lt;&gt;"",COUNTA($J300,$L300,$N300,$P300,$R300,$T300,$V300,$X300,$Z300)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE300" s="67" t="inlineStr">
@@ -25383,7 +25396,7 @@
       <c r="AB301" s="68" t="n"/>
       <c r="AC301" s="69" t="n"/>
       <c r="AD301" s="70">
-        <f>IF(AND(COUNTIF($B$5:B301,B301)=1,$B301&lt;&gt;"",$AB301&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B301,B301)=1,$B301&lt;&gt;"",$AB301&lt;&gt;"",COUNTA($J301,$L301,$N301,$P301,$R301,$T301,$V301,$X301,$Z301)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE301" s="67" t="inlineStr">
@@ -25461,7 +25474,7 @@
       <c r="AB302" s="68" t="n"/>
       <c r="AC302" s="69" t="n"/>
       <c r="AD302" s="70">
-        <f>IF(AND(COUNTIF($B$5:B302,B302)=1,$B302&lt;&gt;"",$AB302&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B302,B302)=1,$B302&lt;&gt;"",$AB302&lt;&gt;"",COUNTA($J302,$L302,$N302,$P302,$R302,$T302,$V302,$X302,$Z302)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE302" s="67" t="inlineStr">
@@ -25539,7 +25552,7 @@
       <c r="AB303" s="68" t="n"/>
       <c r="AC303" s="69" t="n"/>
       <c r="AD303" s="70">
-        <f>IF(AND(COUNTIF($B$5:B303,B303)=1,$B303&lt;&gt;"",$AB303&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B303,B303)=1,$B303&lt;&gt;"",$AB303&lt;&gt;"",COUNTA($J303,$L303,$N303,$P303,$R303,$T303,$V303,$X303,$Z303)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE303" s="67" t="inlineStr">
@@ -25613,7 +25626,7 @@
       <c r="AB304" s="68" t="n"/>
       <c r="AC304" s="69" t="n"/>
       <c r="AD304" s="70">
-        <f>IF(AND(COUNTIF($B$5:B304,B304)=1,$B304&lt;&gt;"",$AB304&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B304,B304)=1,$B304&lt;&gt;"",$AB304&lt;&gt;"",COUNTA($J304,$L304,$N304,$P304,$R304,$T304,$V304,$X304,$Z304)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE304" s="67" t="inlineStr">
@@ -25687,7 +25700,7 @@
       <c r="AB305" s="68" t="n"/>
       <c r="AC305" s="69" t="n"/>
       <c r="AD305" s="70">
-        <f>IF(AND(COUNTIF($B$5:B305,B305)=1,$B305&lt;&gt;"",$AB305&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B305,B305)=1,$B305&lt;&gt;"",$AB305&lt;&gt;"",COUNTA($J305,$L305,$N305,$P305,$R305,$T305,$V305,$X305,$Z305)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE305" s="67" t="inlineStr">
@@ -25765,7 +25778,7 @@
       <c r="AB306" s="68" t="n"/>
       <c r="AC306" s="69" t="n"/>
       <c r="AD306" s="70">
-        <f>IF(AND(COUNTIF($B$5:B306,B306)=1,$B306&lt;&gt;"",$AB306&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B306,B306)=1,$B306&lt;&gt;"",$AB306&lt;&gt;"",COUNTA($J306,$L306,$N306,$P306,$R306,$T306,$V306,$X306,$Z306)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE306" s="67" t="inlineStr">
@@ -25843,7 +25856,7 @@
       <c r="AB307" s="68" t="n"/>
       <c r="AC307" s="69" t="n"/>
       <c r="AD307" s="70">
-        <f>IF(AND(COUNTIF($B$5:B307,B307)=1,$B307&lt;&gt;"",$AB307&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B307,B307)=1,$B307&lt;&gt;"",$AB307&lt;&gt;"",COUNTA($J307,$L307,$N307,$P307,$R307,$T307,$V307,$X307,$Z307)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE307" s="67" t="inlineStr">
@@ -25921,7 +25934,7 @@
       <c r="AB308" s="68" t="n"/>
       <c r="AC308" s="69" t="n"/>
       <c r="AD308" s="70">
-        <f>IF(AND(COUNTIF($B$5:B308,B308)=1,$B308&lt;&gt;"",$AB308&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B308,B308)=1,$B308&lt;&gt;"",$AB308&lt;&gt;"",COUNTA($J308,$L308,$N308,$P308,$R308,$T308,$V308,$X308,$Z308)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE308" s="67" t="inlineStr">
@@ -25999,7 +26012,7 @@
       <c r="AB309" s="68" t="n"/>
       <c r="AC309" s="69" t="n"/>
       <c r="AD309" s="70">
-        <f>IF(AND(COUNTIF($B$5:B309,B309)=1,$B309&lt;&gt;"",$AB309&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B309,B309)=1,$B309&lt;&gt;"",$AB309&lt;&gt;"",COUNTA($J309,$L309,$N309,$P309,$R309,$T309,$V309,$X309,$Z309)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE309" s="67" t="inlineStr">
@@ -26077,7 +26090,7 @@
       <c r="AB310" s="68" t="n"/>
       <c r="AC310" s="69" t="n"/>
       <c r="AD310" s="70">
-        <f>IF(AND(COUNTIF($B$5:B310,B310)=1,$B310&lt;&gt;"",$AB310&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B310,B310)=1,$B310&lt;&gt;"",$AB310&lt;&gt;"",COUNTA($J310,$L310,$N310,$P310,$R310,$T310,$V310,$X310,$Z310)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE310" s="67" t="inlineStr">
@@ -26155,7 +26168,7 @@
       <c r="AB311" s="68" t="n"/>
       <c r="AC311" s="69" t="n"/>
       <c r="AD311" s="70">
-        <f>IF(AND(COUNTIF($B$5:B311,B311)=1,$B311&lt;&gt;"",$AB311&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B311,B311)=1,$B311&lt;&gt;"",$AB311&lt;&gt;"",COUNTA($J311,$L311,$N311,$P311,$R311,$T311,$V311,$X311,$Z311)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE311" s="67" t="inlineStr">
@@ -26233,7 +26246,7 @@
       <c r="AB312" s="68" t="n"/>
       <c r="AC312" s="69" t="n"/>
       <c r="AD312" s="70">
-        <f>IF(AND(COUNTIF($B$5:B312,B312)=1,$B312&lt;&gt;"",$AB312&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B312,B312)=1,$B312&lt;&gt;"",$AB312&lt;&gt;"",COUNTA($J312,$L312,$N312,$P312,$R312,$T312,$V312,$X312,$Z312)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE312" s="67" t="inlineStr">
@@ -26311,7 +26324,7 @@
       <c r="AB313" s="68" t="n"/>
       <c r="AC313" s="69" t="n"/>
       <c r="AD313" s="70">
-        <f>IF(AND(COUNTIF($B$5:B313,B313)=1,$B313&lt;&gt;"",$AB313&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B313,B313)=1,$B313&lt;&gt;"",$AB313&lt;&gt;"",COUNTA($J313,$L313,$N313,$P313,$R313,$T313,$V313,$X313,$Z313)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE313" s="67" t="inlineStr">
@@ -26389,7 +26402,7 @@
       <c r="AB314" s="68" t="n"/>
       <c r="AC314" s="69" t="n"/>
       <c r="AD314" s="70">
-        <f>IF(AND(COUNTIF($B$5:B314,B314)=1,$B314&lt;&gt;"",$AB314&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B314,B314)=1,$B314&lt;&gt;"",$AB314&lt;&gt;"",COUNTA($J314,$L314,$N314,$P314,$R314,$T314,$V314,$X314,$Z314)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE314" s="67" t="inlineStr">
@@ -26467,7 +26480,7 @@
       <c r="AB315" s="68" t="n"/>
       <c r="AC315" s="69" t="n"/>
       <c r="AD315" s="70">
-        <f>IF(AND(COUNTIF($B$5:B315,B315)=1,$B315&lt;&gt;"",$AB315&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B315,B315)=1,$B315&lt;&gt;"",$AB315&lt;&gt;"",COUNTA($J315,$L315,$N315,$P315,$R315,$T315,$V315,$X315,$Z315)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE315" s="67" t="inlineStr">
@@ -26541,7 +26554,7 @@
       <c r="AB316" s="68" t="n"/>
       <c r="AC316" s="69" t="n"/>
       <c r="AD316" s="70">
-        <f>IF(AND(COUNTIF($B$5:B316,B316)=1,$B316&lt;&gt;"",$AB316&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B316,B316)=1,$B316&lt;&gt;"",$AB316&lt;&gt;"",COUNTA($J316,$L316,$N316,$P316,$R316,$T316,$V316,$X316,$Z316)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE316" s="67" t="inlineStr">
@@ -26615,7 +26628,7 @@
       <c r="AB317" s="68" t="n"/>
       <c r="AC317" s="69" t="n"/>
       <c r="AD317" s="70">
-        <f>IF(AND(COUNTIF($B$5:B317,B317)=1,$B317&lt;&gt;"",$AB317&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B317,B317)=1,$B317&lt;&gt;"",$AB317&lt;&gt;"",COUNTA($J317,$L317,$N317,$P317,$R317,$T317,$V317,$X317,$Z317)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE317" s="67" t="inlineStr">
@@ -26693,7 +26706,7 @@
       <c r="AB318" s="68" t="n"/>
       <c r="AC318" s="69" t="n"/>
       <c r="AD318" s="70">
-        <f>IF(AND(COUNTIF($B$5:B318,B318)=1,$B318&lt;&gt;"",$AB318&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B318,B318)=1,$B318&lt;&gt;"",$AB318&lt;&gt;"",COUNTA($J318,$L318,$N318,$P318,$R318,$T318,$V318,$X318,$Z318)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE318" s="67" t="inlineStr">
@@ -26771,7 +26784,7 @@
       <c r="AB319" s="68" t="n"/>
       <c r="AC319" s="69" t="n"/>
       <c r="AD319" s="70">
-        <f>IF(AND(COUNTIF($B$5:B319,B319)=1,$B319&lt;&gt;"",$AB319&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B319,B319)=1,$B319&lt;&gt;"",$AB319&lt;&gt;"",COUNTA($J319,$L319,$N319,$P319,$R319,$T319,$V319,$X319,$Z319)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE319" s="67" t="inlineStr">
@@ -26849,7 +26862,7 @@
       <c r="AB320" s="68" t="n"/>
       <c r="AC320" s="69" t="n"/>
       <c r="AD320" s="70">
-        <f>IF(AND(COUNTIF($B$5:B320,B320)=1,$B320&lt;&gt;"",$AB320&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B320,B320)=1,$B320&lt;&gt;"",$AB320&lt;&gt;"",COUNTA($J320,$L320,$N320,$P320,$R320,$T320,$V320,$X320,$Z320)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE320" s="67" t="inlineStr">
@@ -26927,7 +26940,7 @@
       <c r="AB321" s="68" t="n"/>
       <c r="AC321" s="69" t="n"/>
       <c r="AD321" s="70">
-        <f>IF(AND(COUNTIF($B$5:B321,B321)=1,$B321&lt;&gt;"",$AB321&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B321,B321)=1,$B321&lt;&gt;"",$AB321&lt;&gt;"",COUNTA($J321,$L321,$N321,$P321,$R321,$T321,$V321,$X321,$Z321)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE321" s="67" t="inlineStr">
@@ -27005,7 +27018,7 @@
       <c r="AB322" s="68" t="n"/>
       <c r="AC322" s="69" t="n"/>
       <c r="AD322" s="70">
-        <f>IF(AND(COUNTIF($B$5:B322,B322)=1,$B322&lt;&gt;"",$AB322&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B322,B322)=1,$B322&lt;&gt;"",$AB322&lt;&gt;"",COUNTA($J322,$L322,$N322,$P322,$R322,$T322,$V322,$X322,$Z322)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE322" s="67" t="inlineStr">
@@ -27083,7 +27096,7 @@
       <c r="AB323" s="68" t="n"/>
       <c r="AC323" s="69" t="n"/>
       <c r="AD323" s="70">
-        <f>IF(AND(COUNTIF($B$5:B323,B323)=1,$B323&lt;&gt;"",$AB323&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B323,B323)=1,$B323&lt;&gt;"",$AB323&lt;&gt;"",COUNTA($J323,$L323,$N323,$P323,$R323,$T323,$V323,$X323,$Z323)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE323" s="67" t="inlineStr">
@@ -27157,7 +27170,7 @@
       <c r="AB324" s="68" t="n"/>
       <c r="AC324" s="69" t="n"/>
       <c r="AD324" s="70">
-        <f>IF(AND(COUNTIF($B$5:B324,B324)=1,$B324&lt;&gt;"",$AB324&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B324,B324)=1,$B324&lt;&gt;"",$AB324&lt;&gt;"",COUNTA($J324,$L324,$N324,$P324,$R324,$T324,$V324,$X324,$Z324)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE324" s="67" t="inlineStr">
@@ -27231,7 +27244,7 @@
       <c r="AB325" s="68" t="n"/>
       <c r="AC325" s="69" t="n"/>
       <c r="AD325" s="70">
-        <f>IF(AND(COUNTIF($B$5:B325,B325)=1,$B325&lt;&gt;"",$AB325&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B325,B325)=1,$B325&lt;&gt;"",$AB325&lt;&gt;"",COUNTA($J325,$L325,$N325,$P325,$R325,$T325,$V325,$X325,$Z325)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE325" s="67" t="inlineStr">
@@ -27309,7 +27322,7 @@
       <c r="AB326" s="68" t="n"/>
       <c r="AC326" s="69" t="n"/>
       <c r="AD326" s="70">
-        <f>IF(AND(COUNTIF($B$5:B326,B326)=1,$B326&lt;&gt;"",$AB326&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B326,B326)=1,$B326&lt;&gt;"",$AB326&lt;&gt;"",COUNTA($J326,$L326,$N326,$P326,$R326,$T326,$V326,$X326,$Z326)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE326" s="67" t="inlineStr">
@@ -27387,7 +27400,7 @@
       <c r="AB327" s="68" t="n"/>
       <c r="AC327" s="69" t="n"/>
       <c r="AD327" s="70">
-        <f>IF(AND(COUNTIF($B$5:B327,B327)=1,$B327&lt;&gt;"",$AB327&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B327,B327)=1,$B327&lt;&gt;"",$AB327&lt;&gt;"",COUNTA($J327,$L327,$N327,$P327,$R327,$T327,$V327,$X327,$Z327)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE327" s="67" t="inlineStr">
@@ -27465,7 +27478,7 @@
       <c r="AB328" s="68" t="n"/>
       <c r="AC328" s="69" t="n"/>
       <c r="AD328" s="70">
-        <f>IF(AND(COUNTIF($B$5:B328,B328)=1,$B328&lt;&gt;"",$AB328&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B328,B328)=1,$B328&lt;&gt;"",$AB328&lt;&gt;"",COUNTA($J328,$L328,$N328,$P328,$R328,$T328,$V328,$X328,$Z328)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE328" s="67" t="inlineStr">
@@ -27543,7 +27556,7 @@
       <c r="AB329" s="68" t="n"/>
       <c r="AC329" s="69" t="n"/>
       <c r="AD329" s="70">
-        <f>IF(AND(COUNTIF($B$5:B329,B329)=1,$B329&lt;&gt;"",$AB329&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B329,B329)=1,$B329&lt;&gt;"",$AB329&lt;&gt;"",COUNTA($J329,$L329,$N329,$P329,$R329,$T329,$V329,$X329,$Z329)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE329" s="67" t="inlineStr">
@@ -27621,7 +27634,7 @@
       <c r="AB330" s="68" t="n"/>
       <c r="AC330" s="69" t="n"/>
       <c r="AD330" s="70">
-        <f>IF(AND(COUNTIF($B$5:B330,B330)=1,$B330&lt;&gt;"",$AB330&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B330,B330)=1,$B330&lt;&gt;"",$AB330&lt;&gt;"",COUNTA($J330,$L330,$N330,$P330,$R330,$T330,$V330,$X330,$Z330)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE330" s="67" t="inlineStr">
@@ -27699,7 +27712,7 @@
       <c r="AB331" s="68" t="n"/>
       <c r="AC331" s="69" t="n"/>
       <c r="AD331" s="70">
-        <f>IF(AND(COUNTIF($B$5:B331,B331)=1,$B331&lt;&gt;"",$AB331&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B331,B331)=1,$B331&lt;&gt;"",$AB331&lt;&gt;"",COUNTA($J331,$L331,$N331,$P331,$R331,$T331,$V331,$X331,$Z331)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE331" s="67" t="inlineStr">
@@ -27777,7 +27790,7 @@
       <c r="AB332" s="68" t="n"/>
       <c r="AC332" s="69" t="n"/>
       <c r="AD332" s="70">
-        <f>IF(AND(COUNTIF($B$5:B332,B332)=1,$B332&lt;&gt;"",$AB332&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B332,B332)=1,$B332&lt;&gt;"",$AB332&lt;&gt;"",COUNTA($J332,$L332,$N332,$P332,$R332,$T332,$V332,$X332,$Z332)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE332" s="67" t="inlineStr">
@@ -27855,7 +27868,7 @@
       <c r="AB333" s="68" t="n"/>
       <c r="AC333" s="69" t="n"/>
       <c r="AD333" s="70">
-        <f>IF(AND(COUNTIF($B$5:B333,B333)=1,$B333&lt;&gt;"",$AB333&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B333,B333)=1,$B333&lt;&gt;"",$AB333&lt;&gt;"",COUNTA($J333,$L333,$N333,$P333,$R333,$T333,$V333,$X333,$Z333)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE333" s="67" t="inlineStr">
@@ -27933,7 +27946,7 @@
       <c r="AB334" s="68" t="n"/>
       <c r="AC334" s="69" t="n"/>
       <c r="AD334" s="70">
-        <f>IF(AND(COUNTIF($B$5:B334,B334)=1,$B334&lt;&gt;"",$AB334&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B334,B334)=1,$B334&lt;&gt;"",$AB334&lt;&gt;"",COUNTA($J334,$L334,$N334,$P334,$R334,$T334,$V334,$X334,$Z334)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE334" s="67" t="inlineStr">
@@ -28007,7 +28020,7 @@
       <c r="AB335" s="68" t="n"/>
       <c r="AC335" s="69" t="n"/>
       <c r="AD335" s="70">
-        <f>IF(AND(COUNTIF($B$5:B335,B335)=1,$B335&lt;&gt;"",$AB335&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B335,B335)=1,$B335&lt;&gt;"",$AB335&lt;&gt;"",COUNTA($J335,$L335,$N335,$P335,$R335,$T335,$V335,$X335,$Z335)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE335" s="67" t="inlineStr">
@@ -28081,7 +28094,7 @@
       <c r="AB336" s="68" t="n"/>
       <c r="AC336" s="69" t="n"/>
       <c r="AD336" s="70">
-        <f>IF(AND(COUNTIF($B$5:B336,B336)=1,$B336&lt;&gt;"",$AB336&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B336,B336)=1,$B336&lt;&gt;"",$AB336&lt;&gt;"",COUNTA($J336,$L336,$N336,$P336,$R336,$T336,$V336,$X336,$Z336)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE336" s="67" t="inlineStr">
@@ -28155,7 +28168,7 @@
       <c r="AB337" s="68" t="n"/>
       <c r="AC337" s="69" t="n"/>
       <c r="AD337" s="70">
-        <f>IF(AND(COUNTIF($B$5:B337,B337)=1,$B337&lt;&gt;"",$AB337&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B337,B337)=1,$B337&lt;&gt;"",$AB337&lt;&gt;"",COUNTA($J337,$L337,$N337,$P337,$R337,$T337,$V337,$X337,$Z337)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE337" s="67" t="inlineStr">
@@ -28225,7 +28238,7 @@
       <c r="AB338" s="68" t="n"/>
       <c r="AC338" s="69" t="n"/>
       <c r="AD338" s="70">
-        <f>IF(AND(COUNTIF($B$5:B338,B338)=1,$B338&lt;&gt;"",$AB338&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B338,B338)=1,$B338&lt;&gt;"",$AB338&lt;&gt;"",COUNTA($J338,$L338,$N338,$P338,$R338,$T338,$V338,$X338,$Z338)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE338" s="67" t="inlineStr">
@@ -28299,7 +28312,7 @@
       <c r="AB339" s="68" t="n"/>
       <c r="AC339" s="69" t="n"/>
       <c r="AD339" s="70">
-        <f>IF(AND(COUNTIF($B$5:B339,B339)=1,$B339&lt;&gt;"",$AB339&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B339,B339)=1,$B339&lt;&gt;"",$AB339&lt;&gt;"",COUNTA($J339,$L339,$N339,$P339,$R339,$T339,$V339,$X339,$Z339)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE339" s="67" t="inlineStr">
@@ -28377,7 +28390,7 @@
       <c r="AB340" s="68" t="n"/>
       <c r="AC340" s="69" t="n"/>
       <c r="AD340" s="70">
-        <f>IF(AND(COUNTIF($B$5:B340,B340)=1,$B340&lt;&gt;"",$AB340&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B340,B340)=1,$B340&lt;&gt;"",$AB340&lt;&gt;"",COUNTA($J340,$L340,$N340,$P340,$R340,$T340,$V340,$X340,$Z340)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE340" s="67" t="inlineStr">
@@ -28455,7 +28468,7 @@
       <c r="AB341" s="68" t="n"/>
       <c r="AC341" s="69" t="n"/>
       <c r="AD341" s="70">
-        <f>IF(AND(COUNTIF($B$5:B341,B341)=1,$B341&lt;&gt;"",$AB341&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B341,B341)=1,$B341&lt;&gt;"",$AB341&lt;&gt;"",COUNTA($J341,$L341,$N341,$P341,$R341,$T341,$V341,$X341,$Z341)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE341" s="67" t="inlineStr">
@@ -28533,7 +28546,7 @@
       <c r="AB342" s="68" t="n"/>
       <c r="AC342" s="69" t="n"/>
       <c r="AD342" s="70">
-        <f>IF(AND(COUNTIF($B$5:B342,B342)=1,$B342&lt;&gt;"",$AB342&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B342,B342)=1,$B342&lt;&gt;"",$AB342&lt;&gt;"",COUNTA($J342,$L342,$N342,$P342,$R342,$T342,$V342,$X342,$Z342)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE342" s="67" t="inlineStr">
@@ -28611,7 +28624,7 @@
       <c r="AB343" s="68" t="n"/>
       <c r="AC343" s="69" t="n"/>
       <c r="AD343" s="70">
-        <f>IF(AND(COUNTIF($B$5:B343,B343)=1,$B343&lt;&gt;"",$AB343&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B343,B343)=1,$B343&lt;&gt;"",$AB343&lt;&gt;"",COUNTA($J343,$L343,$N343,$P343,$R343,$T343,$V343,$X343,$Z343)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE343" s="67" t="inlineStr">
@@ -28685,7 +28698,7 @@
       <c r="AB344" s="68" t="n"/>
       <c r="AC344" s="69" t="n"/>
       <c r="AD344" s="70">
-        <f>IF(AND(COUNTIF($B$5:B344,B344)=1,$B344&lt;&gt;"",$AB344&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B344,B344)=1,$B344&lt;&gt;"",$AB344&lt;&gt;"",COUNTA($J344,$L344,$N344,$P344,$R344,$T344,$V344,$X344,$Z344)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE344" s="67" t="inlineStr">
@@ -28759,7 +28772,7 @@
       <c r="AB345" s="68" t="n"/>
       <c r="AC345" s="69" t="n"/>
       <c r="AD345" s="70">
-        <f>IF(AND(COUNTIF($B$5:B345,B345)=1,$B345&lt;&gt;"",$AB345&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B345,B345)=1,$B345&lt;&gt;"",$AB345&lt;&gt;"",COUNTA($J345,$L345,$N345,$P345,$R345,$T345,$V345,$X345,$Z345)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE345" s="67" t="inlineStr">
@@ -28837,7 +28850,7 @@
       <c r="AB346" s="68" t="n"/>
       <c r="AC346" s="69" t="n"/>
       <c r="AD346" s="70">
-        <f>IF(AND(COUNTIF($B$5:B346,B346)=1,$B346&lt;&gt;"",$AB346&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B346,B346)=1,$B346&lt;&gt;"",$AB346&lt;&gt;"",COUNTA($J346,$L346,$N346,$P346,$R346,$T346,$V346,$X346,$Z346)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE346" s="67" t="inlineStr">
@@ -28915,7 +28928,7 @@
       <c r="AB347" s="68" t="n"/>
       <c r="AC347" s="69" t="n"/>
       <c r="AD347" s="70">
-        <f>IF(AND(COUNTIF($B$5:B347,B347)=1,$B347&lt;&gt;"",$AB347&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B347,B347)=1,$B347&lt;&gt;"",$AB347&lt;&gt;"",COUNTA($J347,$L347,$N347,$P347,$R347,$T347,$V347,$X347,$Z347)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE347" s="67" t="inlineStr">
@@ -28993,7 +29006,7 @@
       <c r="AB348" s="68" t="n"/>
       <c r="AC348" s="69" t="n"/>
       <c r="AD348" s="70">
-        <f>IF(AND(COUNTIF($B$5:B348,B348)=1,$B348&lt;&gt;"",$AB348&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B348,B348)=1,$B348&lt;&gt;"",$AB348&lt;&gt;"",COUNTA($J348,$L348,$N348,$P348,$R348,$T348,$V348,$X348,$Z348)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE348" s="67" t="inlineStr">
@@ -29071,7 +29084,7 @@
       <c r="AB349" s="68" t="n"/>
       <c r="AC349" s="69" t="n"/>
       <c r="AD349" s="70">
-        <f>IF(AND(COUNTIF($B$5:B349,B349)=1,$B349&lt;&gt;"",$AB349&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B349,B349)=1,$B349&lt;&gt;"",$AB349&lt;&gt;"",COUNTA($J349,$L349,$N349,$P349,$R349,$T349,$V349,$X349,$Z349)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE349" s="67" t="inlineStr">
@@ -29145,7 +29158,7 @@
       <c r="AB350" s="68" t="n"/>
       <c r="AC350" s="69" t="n"/>
       <c r="AD350" s="70">
-        <f>IF(AND(COUNTIF($B$5:B350,B350)=1,$B350&lt;&gt;"",$AB350&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B350,B350)=1,$B350&lt;&gt;"",$AB350&lt;&gt;"",COUNTA($J350,$L350,$N350,$P350,$R350,$T350,$V350,$X350,$Z350)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE350" s="67" t="inlineStr">
@@ -29219,7 +29232,7 @@
       <c r="AB351" s="68" t="n"/>
       <c r="AC351" s="69" t="n"/>
       <c r="AD351" s="70">
-        <f>IF(AND(COUNTIF($B$5:B351,B351)=1,$B351&lt;&gt;"",$AB351&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B351,B351)=1,$B351&lt;&gt;"",$AB351&lt;&gt;"",COUNTA($J351,$L351,$N351,$P351,$R351,$T351,$V351,$X351,$Z351)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE351" s="67" t="inlineStr">
@@ -29297,7 +29310,7 @@
       <c r="AB352" s="68" t="n"/>
       <c r="AC352" s="69" t="n"/>
       <c r="AD352" s="70">
-        <f>IF(AND(COUNTIF($B$5:B352,B352)=1,$B352&lt;&gt;"",$AB352&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B352,B352)=1,$B352&lt;&gt;"",$AB352&lt;&gt;"",COUNTA($J352,$L352,$N352,$P352,$R352,$T352,$V352,$X352,$Z352)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE352" s="67" t="inlineStr">
@@ -29375,7 +29388,7 @@
       <c r="AB353" s="68" t="n"/>
       <c r="AC353" s="69" t="n"/>
       <c r="AD353" s="70">
-        <f>IF(AND(COUNTIF($B$5:B353,B353)=1,$B353&lt;&gt;"",$AB353&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B353,B353)=1,$B353&lt;&gt;"",$AB353&lt;&gt;"",COUNTA($J353,$L353,$N353,$P353,$R353,$T353,$V353,$X353,$Z353)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE353" s="67" t="inlineStr">
@@ -29453,7 +29466,7 @@
       <c r="AB354" s="68" t="n"/>
       <c r="AC354" s="69" t="n"/>
       <c r="AD354" s="70">
-        <f>IF(AND(COUNTIF($B$5:B354,B354)=1,$B354&lt;&gt;"",$AB354&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B354,B354)=1,$B354&lt;&gt;"",$AB354&lt;&gt;"",COUNTA($J354,$L354,$N354,$P354,$R354,$T354,$V354,$X354,$Z354)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE354" s="67" t="inlineStr">
@@ -29531,7 +29544,7 @@
       <c r="AB355" s="68" t="n"/>
       <c r="AC355" s="69" t="n"/>
       <c r="AD355" s="70">
-        <f>IF(AND(COUNTIF($B$5:B355,B355)=1,$B355&lt;&gt;"",$AB355&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B355,B355)=1,$B355&lt;&gt;"",$AB355&lt;&gt;"",COUNTA($J355,$L355,$N355,$P355,$R355,$T355,$V355,$X355,$Z355)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE355" s="67" t="inlineStr">
@@ -29609,7 +29622,7 @@
       <c r="AB356" s="68" t="n"/>
       <c r="AC356" s="69" t="n"/>
       <c r="AD356" s="70">
-        <f>IF(AND(COUNTIF($B$5:B356,B356)=1,$B356&lt;&gt;"",$AB356&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B356,B356)=1,$B356&lt;&gt;"",$AB356&lt;&gt;"",COUNTA($J356,$L356,$N356,$P356,$R356,$T356,$V356,$X356,$Z356)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE356" s="67" t="inlineStr">
@@ -29687,7 +29700,7 @@
       <c r="AB357" s="68" t="n"/>
       <c r="AC357" s="69" t="n"/>
       <c r="AD357" s="70">
-        <f>IF(AND(COUNTIF($B$5:B357,B357)=1,$B357&lt;&gt;"",$AB357&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B357,B357)=1,$B357&lt;&gt;"",$AB357&lt;&gt;"",COUNTA($J357,$L357,$N357,$P357,$R357,$T357,$V357,$X357,$Z357)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE357" s="67" t="inlineStr">
@@ -29765,7 +29778,7 @@
       <c r="AB358" s="68" t="n"/>
       <c r="AC358" s="69" t="n"/>
       <c r="AD358" s="70">
-        <f>IF(AND(COUNTIF($B$5:B358,B358)=1,$B358&lt;&gt;"",$AB358&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B358,B358)=1,$B358&lt;&gt;"",$AB358&lt;&gt;"",COUNTA($J358,$L358,$N358,$P358,$R358,$T358,$V358,$X358,$Z358)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE358" s="67" t="inlineStr">
@@ -29843,7 +29856,7 @@
       <c r="AB359" s="68" t="n"/>
       <c r="AC359" s="69" t="n"/>
       <c r="AD359" s="70">
-        <f>IF(AND(COUNTIF($B$5:B359,B359)=1,$B359&lt;&gt;"",$AB359&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B359,B359)=1,$B359&lt;&gt;"",$AB359&lt;&gt;"",COUNTA($J359,$L359,$N359,$P359,$R359,$T359,$V359,$X359,$Z359)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE359" s="67" t="inlineStr">
@@ -29921,7 +29934,7 @@
       <c r="AB360" s="68" t="n"/>
       <c r="AC360" s="69" t="n"/>
       <c r="AD360" s="70">
-        <f>IF(AND(COUNTIF($B$5:B360,B360)=1,$B360&lt;&gt;"",$AB360&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B360,B360)=1,$B360&lt;&gt;"",$AB360&lt;&gt;"",COUNTA($J360,$L360,$N360,$P360,$R360,$T360,$V360,$X360,$Z360)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE360" s="67" t="inlineStr">
@@ -29999,7 +30012,7 @@
       <c r="AB361" s="68" t="n"/>
       <c r="AC361" s="69" t="n"/>
       <c r="AD361" s="70">
-        <f>IF(AND(COUNTIF($B$5:B361,B361)=1,$B361&lt;&gt;"",$AB361&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B361,B361)=1,$B361&lt;&gt;"",$AB361&lt;&gt;"",COUNTA($J361,$L361,$N361,$P361,$R361,$T361,$V361,$X361,$Z361)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE361" s="67" t="inlineStr">
@@ -30077,7 +30090,7 @@
       <c r="AB362" s="68" t="n"/>
       <c r="AC362" s="69" t="n"/>
       <c r="AD362" s="70">
-        <f>IF(AND(COUNTIF($B$5:B362,B362)=1,$B362&lt;&gt;"",$AB362&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B362,B362)=1,$B362&lt;&gt;"",$AB362&lt;&gt;"",COUNTA($J362,$L362,$N362,$P362,$R362,$T362,$V362,$X362,$Z362)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE362" s="67" t="inlineStr">
@@ -30155,7 +30168,7 @@
       <c r="AB363" s="68" t="n"/>
       <c r="AC363" s="69" t="n"/>
       <c r="AD363" s="70">
-        <f>IF(AND(COUNTIF($B$5:B363,B363)=1,$B363&lt;&gt;"",$AB363&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B363,B363)=1,$B363&lt;&gt;"",$AB363&lt;&gt;"",COUNTA($J363,$L363,$N363,$P363,$R363,$T363,$V363,$X363,$Z363)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE363" s="67" t="inlineStr">
@@ -30229,7 +30242,7 @@
       <c r="AB364" s="68" t="n"/>
       <c r="AC364" s="69" t="n"/>
       <c r="AD364" s="70">
-        <f>IF(AND(COUNTIF($B$5:B364,B364)=1,$B364&lt;&gt;"",$AB364&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B364,B364)=1,$B364&lt;&gt;"",$AB364&lt;&gt;"",COUNTA($J364,$L364,$N364,$P364,$R364,$T364,$V364,$X364,$Z364)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE364" s="67" t="inlineStr">
@@ -30303,7 +30316,7 @@
       <c r="AB365" s="68" t="n"/>
       <c r="AC365" s="69" t="n"/>
       <c r="AD365" s="70">
-        <f>IF(AND(COUNTIF($B$5:B365,B365)=1,$B365&lt;&gt;"",$AB365&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B365,B365)=1,$B365&lt;&gt;"",$AB365&lt;&gt;"",COUNTA($J365,$L365,$N365,$P365,$R365,$T365,$V365,$X365,$Z365)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE365" s="67" t="inlineStr">
@@ -30381,7 +30394,7 @@
       <c r="AB366" s="68" t="n"/>
       <c r="AC366" s="69" t="n"/>
       <c r="AD366" s="70">
-        <f>IF(AND(COUNTIF($B$5:B366,B366)=1,$B366&lt;&gt;"",$AB366&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B366,B366)=1,$B366&lt;&gt;"",$AB366&lt;&gt;"",COUNTA($J366,$L366,$N366,$P366,$R366,$T366,$V366,$X366,$Z366)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE366" s="67" t="inlineStr">
@@ -30459,7 +30472,7 @@
       <c r="AB367" s="68" t="n"/>
       <c r="AC367" s="69" t="n"/>
       <c r="AD367" s="70">
-        <f>IF(AND(COUNTIF($B$5:B367,B367)=1,$B367&lt;&gt;"",$AB367&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B367,B367)=1,$B367&lt;&gt;"",$AB367&lt;&gt;"",COUNTA($J367,$L367,$N367,$P367,$R367,$T367,$V367,$X367,$Z367)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE367" s="67" t="inlineStr">
@@ -30537,7 +30550,7 @@
       <c r="AB368" s="68" t="n"/>
       <c r="AC368" s="69" t="n"/>
       <c r="AD368" s="70">
-        <f>IF(AND(COUNTIF($B$5:B368,B368)=1,$B368&lt;&gt;"",$AB368&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B368,B368)=1,$B368&lt;&gt;"",$AB368&lt;&gt;"",COUNTA($J368,$L368,$N368,$P368,$R368,$T368,$V368,$X368,$Z368)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE368" s="67" t="inlineStr">
@@ -30615,7 +30628,7 @@
       <c r="AB369" s="68" t="n"/>
       <c r="AC369" s="69" t="n"/>
       <c r="AD369" s="70">
-        <f>IF(AND(COUNTIF($B$5:B369,B369)=1,$B369&lt;&gt;"",$AB369&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B369,B369)=1,$B369&lt;&gt;"",$AB369&lt;&gt;"",COUNTA($J369,$L369,$N369,$P369,$R369,$T369,$V369,$X369,$Z369)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE369" s="67" t="inlineStr">
@@ -30693,7 +30706,7 @@
       <c r="AB370" s="68" t="n"/>
       <c r="AC370" s="69" t="n"/>
       <c r="AD370" s="70">
-        <f>IF(AND(COUNTIF($B$5:B370,B370)=1,$B370&lt;&gt;"",$AB370&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B370,B370)=1,$B370&lt;&gt;"",$AB370&lt;&gt;"",COUNTA($J370,$L370,$N370,$P370,$R370,$T370,$V370,$X370,$Z370)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE370" s="67" t="inlineStr">
@@ -30767,7 +30780,7 @@
       <c r="AB371" s="68" t="n"/>
       <c r="AC371" s="69" t="n"/>
       <c r="AD371" s="70">
-        <f>IF(AND(COUNTIF($B$5:B371,B371)=1,$B371&lt;&gt;"",$AB371&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B371,B371)=1,$B371&lt;&gt;"",$AB371&lt;&gt;"",COUNTA($J371,$L371,$N371,$P371,$R371,$T371,$V371,$X371,$Z371)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE371" s="67" t="inlineStr">
@@ -30837,7 +30850,7 @@
       <c r="AB372" s="68" t="n"/>
       <c r="AC372" s="69" t="n"/>
       <c r="AD372" s="70">
-        <f>IF(AND(COUNTIF($B$5:B372,B372)=1,$B372&lt;&gt;"",$AB372&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B372,B372)=1,$B372&lt;&gt;"",$AB372&lt;&gt;"",COUNTA($J372,$L372,$N372,$P372,$R372,$T372,$V372,$X372,$Z372)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE372" s="67" t="inlineStr">
@@ -30911,7 +30924,7 @@
       <c r="AB373" s="68" t="n"/>
       <c r="AC373" s="69" t="n"/>
       <c r="AD373" s="70">
-        <f>IF(AND(COUNTIF($B$5:B373,B373)=1,$B373&lt;&gt;"",$AB373&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B373,B373)=1,$B373&lt;&gt;"",$AB373&lt;&gt;"",COUNTA($J373,$L373,$N373,$P373,$R373,$T373,$V373,$X373,$Z373)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE373" s="67" t="inlineStr">
@@ -30989,7 +31002,7 @@
       <c r="AB374" s="68" t="n"/>
       <c r="AC374" s="69" t="n"/>
       <c r="AD374" s="70">
-        <f>IF(AND(COUNTIF($B$5:B374,B374)=1,$B374&lt;&gt;"",$AB374&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B374,B374)=1,$B374&lt;&gt;"",$AB374&lt;&gt;"",COUNTA($J374,$L374,$N374,$P374,$R374,$T374,$V374,$X374,$Z374)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE374" s="67" t="inlineStr">
@@ -31067,7 +31080,7 @@
       <c r="AB375" s="68" t="n"/>
       <c r="AC375" s="69" t="n"/>
       <c r="AD375" s="70">
-        <f>IF(AND(COUNTIF($B$5:B375,B375)=1,$B375&lt;&gt;"",$AB375&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B375,B375)=1,$B375&lt;&gt;"",$AB375&lt;&gt;"",COUNTA($J375,$L375,$N375,$P375,$R375,$T375,$V375,$X375,$Z375)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE375" s="67" t="inlineStr">
@@ -31145,7 +31158,7 @@
       <c r="AB376" s="68" t="n"/>
       <c r="AC376" s="69" t="n"/>
       <c r="AD376" s="70">
-        <f>IF(AND(COUNTIF($B$5:B376,B376)=1,$B376&lt;&gt;"",$AB376&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B376,B376)=1,$B376&lt;&gt;"",$AB376&lt;&gt;"",COUNTA($J376,$L376,$N376,$P376,$R376,$T376,$V376,$X376,$Z376)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE376" s="67" t="inlineStr">
@@ -31223,7 +31236,7 @@
       <c r="AB377" s="68" t="n"/>
       <c r="AC377" s="69" t="n"/>
       <c r="AD377" s="70">
-        <f>IF(AND(COUNTIF($B$5:B377,B377)=1,$B377&lt;&gt;"",$AB377&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B377,B377)=1,$B377&lt;&gt;"",$AB377&lt;&gt;"",COUNTA($J377,$L377,$N377,$P377,$R377,$T377,$V377,$X377,$Z377)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE377" s="67" t="inlineStr">
@@ -31301,7 +31314,7 @@
       <c r="AB378" s="68" t="n"/>
       <c r="AC378" s="69" t="n"/>
       <c r="AD378" s="70">
-        <f>IF(AND(COUNTIF($B$5:B378,B378)=1,$B378&lt;&gt;"",$AB378&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B378,B378)=1,$B378&lt;&gt;"",$AB378&lt;&gt;"",COUNTA($J378,$L378,$N378,$P378,$R378,$T378,$V378,$X378,$Z378)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE378" s="67" t="inlineStr">
@@ -31379,7 +31392,7 @@
       <c r="AB379" s="68" t="n"/>
       <c r="AC379" s="69" t="n"/>
       <c r="AD379" s="70">
-        <f>IF(AND(COUNTIF($B$5:B379,B379)=1,$B379&lt;&gt;"",$AB379&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B379,B379)=1,$B379&lt;&gt;"",$AB379&lt;&gt;"",COUNTA($J379,$L379,$N379,$P379,$R379,$T379,$V379,$X379,$Z379)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE379" s="67" t="inlineStr">
@@ -31457,7 +31470,7 @@
       <c r="AB380" s="68" t="n"/>
       <c r="AC380" s="69" t="n"/>
       <c r="AD380" s="70">
-        <f>IF(AND(COUNTIF($B$5:B380,B380)=1,$B380&lt;&gt;"",$AB380&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B380,B380)=1,$B380&lt;&gt;"",$AB380&lt;&gt;"",COUNTA($J380,$L380,$N380,$P380,$R380,$T380,$V380,$X380,$Z380)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE380" s="67" t="inlineStr">
@@ -31535,7 +31548,7 @@
       <c r="AB381" s="68" t="n"/>
       <c r="AC381" s="69" t="n"/>
       <c r="AD381" s="70">
-        <f>IF(AND(COUNTIF($B$5:B381,B381)=1,$B381&lt;&gt;"",$AB381&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B381,B381)=1,$B381&lt;&gt;"",$AB381&lt;&gt;"",COUNTA($J381,$L381,$N381,$P381,$R381,$T381,$V381,$X381,$Z381)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE381" s="67" t="inlineStr">
@@ -31613,7 +31626,7 @@
       <c r="AB382" s="68" t="n"/>
       <c r="AC382" s="69" t="n"/>
       <c r="AD382" s="70">
-        <f>IF(AND(COUNTIF($B$5:B382,B382)=1,$B382&lt;&gt;"",$AB382&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B382,B382)=1,$B382&lt;&gt;"",$AB382&lt;&gt;"",COUNTA($J382,$L382,$N382,$P382,$R382,$T382,$V382,$X382,$Z382)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE382" s="67" t="inlineStr">
@@ -31687,7 +31700,7 @@
       <c r="AB383" s="68" t="n"/>
       <c r="AC383" s="69" t="n"/>
       <c r="AD383" s="70">
-        <f>IF(AND(COUNTIF($B$5:B383,B383)=1,$B383&lt;&gt;"",$AB383&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B383,B383)=1,$B383&lt;&gt;"",$AB383&lt;&gt;"",COUNTA($J383,$L383,$N383,$P383,$R383,$T383,$V383,$X383,$Z383)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE383" s="67" t="inlineStr">
@@ -31757,7 +31770,7 @@
       <c r="AB384" s="68" t="n"/>
       <c r="AC384" s="69" t="n"/>
       <c r="AD384" s="70">
-        <f>IF(AND(COUNTIF($B$5:B384,B384)=1,$B384&lt;&gt;"",$AB384&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B384,B384)=1,$B384&lt;&gt;"",$AB384&lt;&gt;"",COUNTA($J384,$L384,$N384,$P384,$R384,$T384,$V384,$X384,$Z384)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE384" s="67" t="inlineStr">
@@ -31831,7 +31844,7 @@
       <c r="AB385" s="68" t="n"/>
       <c r="AC385" s="69" t="n"/>
       <c r="AD385" s="70">
-        <f>IF(AND(COUNTIF($B$5:B385,B385)=1,$B385&lt;&gt;"",$AB385&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B385,B385)=1,$B385&lt;&gt;"",$AB385&lt;&gt;"",COUNTA($J385,$L385,$N385,$P385,$R385,$T385,$V385,$X385,$Z385)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE385" s="67" t="inlineStr">
@@ -31909,7 +31922,7 @@
       <c r="AB386" s="68" t="n"/>
       <c r="AC386" s="69" t="n"/>
       <c r="AD386" s="70">
-        <f>IF(AND(COUNTIF($B$5:B386,B386)=1,$B386&lt;&gt;"",$AB386&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B386,B386)=1,$B386&lt;&gt;"",$AB386&lt;&gt;"",COUNTA($J386,$L386,$N386,$P386,$R386,$T386,$V386,$X386,$Z386)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE386" s="67" t="inlineStr">
@@ -31987,7 +32000,7 @@
       <c r="AB387" s="68" t="n"/>
       <c r="AC387" s="69" t="n"/>
       <c r="AD387" s="70">
-        <f>IF(AND(COUNTIF($B$5:B387,B387)=1,$B387&lt;&gt;"",$AB387&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B387,B387)=1,$B387&lt;&gt;"",$AB387&lt;&gt;"",COUNTA($J387,$L387,$N387,$P387,$R387,$T387,$V387,$X387,$Z387)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE387" s="67" t="inlineStr">
@@ -32065,7 +32078,7 @@
       <c r="AB388" s="68" t="n"/>
       <c r="AC388" s="69" t="n"/>
       <c r="AD388" s="70">
-        <f>IF(AND(COUNTIF($B$5:B388,B388)=1,$B388&lt;&gt;"",$AB388&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B388,B388)=1,$B388&lt;&gt;"",$AB388&lt;&gt;"",COUNTA($J388,$L388,$N388,$P388,$R388,$T388,$V388,$X388,$Z388)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE388" s="67" t="inlineStr">
@@ -32143,7 +32156,7 @@
       <c r="AB389" s="68" t="n"/>
       <c r="AC389" s="69" t="n"/>
       <c r="AD389" s="70">
-        <f>IF(AND(COUNTIF($B$5:B389,B389)=1,$B389&lt;&gt;"",$AB389&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B389,B389)=1,$B389&lt;&gt;"",$AB389&lt;&gt;"",COUNTA($J389,$L389,$N389,$P389,$R389,$T389,$V389,$X389,$Z389)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE389" s="67" t="inlineStr">
@@ -32221,7 +32234,7 @@
       <c r="AB390" s="68" t="n"/>
       <c r="AC390" s="69" t="n"/>
       <c r="AD390" s="70">
-        <f>IF(AND(COUNTIF($B$5:B390,B390)=1,$B390&lt;&gt;"",$AB390&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B390,B390)=1,$B390&lt;&gt;"",$AB390&lt;&gt;"",COUNTA($J390,$L390,$N390,$P390,$R390,$T390,$V390,$X390,$Z390)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE390" s="67" t="inlineStr">
@@ -32299,7 +32312,7 @@
       <c r="AB391" s="68" t="n"/>
       <c r="AC391" s="69" t="n"/>
       <c r="AD391" s="70">
-        <f>IF(AND(COUNTIF($B$5:B391,B391)=1,$B391&lt;&gt;"",$AB391&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B391,B391)=1,$B391&lt;&gt;"",$AB391&lt;&gt;"",COUNTA($J391,$L391,$N391,$P391,$R391,$T391,$V391,$X391,$Z391)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE391" s="67" t="inlineStr">
@@ -32377,7 +32390,7 @@
       <c r="AB392" s="68" t="n"/>
       <c r="AC392" s="69" t="n"/>
       <c r="AD392" s="70">
-        <f>IF(AND(COUNTIF($B$5:B392,B392)=1,$B392&lt;&gt;"",$AB392&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B392,B392)=1,$B392&lt;&gt;"",$AB392&lt;&gt;"",COUNTA($J392,$L392,$N392,$P392,$R392,$T392,$V392,$X392,$Z392)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE392" s="67" t="inlineStr">
@@ -32455,7 +32468,7 @@
       <c r="AB393" s="68" t="n"/>
       <c r="AC393" s="69" t="n"/>
       <c r="AD393" s="70">
-        <f>IF(AND(COUNTIF($B$5:B393,B393)=1,$B393&lt;&gt;"",$AB393&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B393,B393)=1,$B393&lt;&gt;"",$AB393&lt;&gt;"",COUNTA($J393,$L393,$N393,$P393,$R393,$T393,$V393,$X393,$Z393)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE393" s="67" t="inlineStr">
@@ -32529,7 +32542,7 @@
       <c r="AB394" s="68" t="n"/>
       <c r="AC394" s="69" t="n"/>
       <c r="AD394" s="70">
-        <f>IF(AND(COUNTIF($B$5:B394,B394)=1,$B394&lt;&gt;"",$AB394&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B394,B394)=1,$B394&lt;&gt;"",$AB394&lt;&gt;"",COUNTA($J394,$L394,$N394,$P394,$R394,$T394,$V394,$X394,$Z394)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE394" s="67" t="inlineStr">
@@ -32603,7 +32616,7 @@
       <c r="AB395" s="68" t="n"/>
       <c r="AC395" s="69" t="n"/>
       <c r="AD395" s="70">
-        <f>IF(AND(COUNTIF($B$5:B395,B395)=1,$B395&lt;&gt;"",$AB395&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B395,B395)=1,$B395&lt;&gt;"",$AB395&lt;&gt;"",COUNTA($J395,$L395,$N395,$P395,$R395,$T395,$V395,$X395,$Z395)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE395" s="67" t="inlineStr">
@@ -32681,7 +32694,7 @@
       <c r="AB396" s="68" t="n"/>
       <c r="AC396" s="69" t="n"/>
       <c r="AD396" s="70">
-        <f>IF(AND(COUNTIF($B$5:B396,B396)=1,$B396&lt;&gt;"",$AB396&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B396,B396)=1,$B396&lt;&gt;"",$AB396&lt;&gt;"",COUNTA($J396,$L396,$N396,$P396,$R396,$T396,$V396,$X396,$Z396)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE396" s="67" t="inlineStr">
@@ -32759,7 +32772,7 @@
       <c r="AB397" s="68" t="n"/>
       <c r="AC397" s="69" t="n"/>
       <c r="AD397" s="70">
-        <f>IF(AND(COUNTIF($B$5:B397,B397)=1,$B397&lt;&gt;"",$AB397&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B397,B397)=1,$B397&lt;&gt;"",$AB397&lt;&gt;"",COUNTA($J397,$L397,$N397,$P397,$R397,$T397,$V397,$X397,$Z397)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE397" s="67" t="inlineStr">
@@ -32837,7 +32850,7 @@
       <c r="AB398" s="68" t="n"/>
       <c r="AC398" s="69" t="n"/>
       <c r="AD398" s="70">
-        <f>IF(AND(COUNTIF($B$5:B398,B398)=1,$B398&lt;&gt;"",$AB398&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B398,B398)=1,$B398&lt;&gt;"",$AB398&lt;&gt;"",COUNTA($J398,$L398,$N398,$P398,$R398,$T398,$V398,$X398,$Z398)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE398" s="67" t="inlineStr">
@@ -32915,7 +32928,7 @@
       <c r="AB399" s="68" t="n"/>
       <c r="AC399" s="69" t="n"/>
       <c r="AD399" s="70">
-        <f>IF(AND(COUNTIF($B$5:B399,B399)=1,$B399&lt;&gt;"",$AB399&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B399,B399)=1,$B399&lt;&gt;"",$AB399&lt;&gt;"",COUNTA($J399,$L399,$N399,$P399,$R399,$T399,$V399,$X399,$Z399)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE399" s="67" t="inlineStr">
@@ -32993,7 +33006,7 @@
       <c r="AB400" s="68" t="n"/>
       <c r="AC400" s="69" t="n"/>
       <c r="AD400" s="70">
-        <f>IF(AND(COUNTIF($B$5:B400,B400)=1,$B400&lt;&gt;"",$AB400&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B400,B400)=1,$B400&lt;&gt;"",$AB400&lt;&gt;"",COUNTA($J400,$L400,$N400,$P400,$R400,$T400,$V400,$X400,$Z400)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE400" s="67" t="inlineStr">
@@ -33071,7 +33084,7 @@
       <c r="AB401" s="68" t="n"/>
       <c r="AC401" s="69" t="n"/>
       <c r="AD401" s="70">
-        <f>IF(AND(COUNTIF($B$5:B401,B401)=1,$B401&lt;&gt;"",$AB401&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B401,B401)=1,$B401&lt;&gt;"",$AB401&lt;&gt;"",COUNTA($J401,$L401,$N401,$P401,$R401,$T401,$V401,$X401,$Z401)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE401" s="67" t="inlineStr">
@@ -33149,7 +33162,7 @@
       <c r="AB402" s="68" t="n"/>
       <c r="AC402" s="69" t="n"/>
       <c r="AD402" s="70">
-        <f>IF(AND(COUNTIF($B$5:B402,B402)=1,$B402&lt;&gt;"",$AB402&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B402,B402)=1,$B402&lt;&gt;"",$AB402&lt;&gt;"",COUNTA($J402,$L402,$N402,$P402,$R402,$T402,$V402,$X402,$Z402)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE402" s="67" t="inlineStr">
@@ -33227,7 +33240,7 @@
       <c r="AB403" s="68" t="n"/>
       <c r="AC403" s="69" t="n"/>
       <c r="AD403" s="70">
-        <f>IF(AND(COUNTIF($B$5:B403,B403)=1,$B403&lt;&gt;"",$AB403&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B403,B403)=1,$B403&lt;&gt;"",$AB403&lt;&gt;"",COUNTA($J403,$L403,$N403,$P403,$R403,$T403,$V403,$X403,$Z403)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE403" s="67" t="inlineStr">
@@ -33301,7 +33314,7 @@
       <c r="AB404" s="68" t="n"/>
       <c r="AC404" s="69" t="n"/>
       <c r="AD404" s="70">
-        <f>IF(AND(COUNTIF($B$5:B404,B404)=1,$B404&lt;&gt;"",$AB404&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B404,B404)=1,$B404&lt;&gt;"",$AB404&lt;&gt;"",COUNTA($J404,$L404,$N404,$P404,$R404,$T404,$V404,$X404,$Z404)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE404" s="67" t="inlineStr">
@@ -33375,7 +33388,7 @@
       <c r="AB405" s="68" t="n"/>
       <c r="AC405" s="69" t="n"/>
       <c r="AD405" s="70">
-        <f>IF(AND(COUNTIF($B$5:B405,B405)=1,$B405&lt;&gt;"",$AB405&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B405,B405)=1,$B405&lt;&gt;"",$AB405&lt;&gt;"",COUNTA($J405,$L405,$N405,$P405,$R405,$T405,$V405,$X405,$Z405)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE405" s="67" t="inlineStr">
@@ -33453,7 +33466,7 @@
       <c r="AB406" s="68" t="n"/>
       <c r="AC406" s="69" t="n"/>
       <c r="AD406" s="70">
-        <f>IF(AND(COUNTIF($B$5:B406,B406)=1,$B406&lt;&gt;"",$AB406&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B406,B406)=1,$B406&lt;&gt;"",$AB406&lt;&gt;"",COUNTA($J406,$L406,$N406,$P406,$R406,$T406,$V406,$X406,$Z406)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE406" s="67" t="inlineStr">
@@ -33531,7 +33544,7 @@
       <c r="AB407" s="68" t="n"/>
       <c r="AC407" s="69" t="n"/>
       <c r="AD407" s="70">
-        <f>IF(AND(COUNTIF($B$5:B407,B407)=1,$B407&lt;&gt;"",$AB407&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B407,B407)=1,$B407&lt;&gt;"",$AB407&lt;&gt;"",COUNTA($J407,$L407,$N407,$P407,$R407,$T407,$V407,$X407,$Z407)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE407" s="67" t="inlineStr">
@@ -33609,7 +33622,7 @@
       <c r="AB408" s="68" t="n"/>
       <c r="AC408" s="69" t="n"/>
       <c r="AD408" s="70">
-        <f>IF(AND(COUNTIF($B$5:B408,B408)=1,$B408&lt;&gt;"",$AB408&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B408,B408)=1,$B408&lt;&gt;"",$AB408&lt;&gt;"",COUNTA($J408,$L408,$N408,$P408,$R408,$T408,$V408,$X408,$Z408)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE408" s="67" t="inlineStr">
@@ -33687,7 +33700,7 @@
       <c r="AB409" s="68" t="n"/>
       <c r="AC409" s="69" t="n"/>
       <c r="AD409" s="70">
-        <f>IF(AND(COUNTIF($B$5:B409,B409)=1,$B409&lt;&gt;"",$AB409&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B409,B409)=1,$B409&lt;&gt;"",$AB409&lt;&gt;"",COUNTA($J409,$L409,$N409,$P409,$R409,$T409,$V409,$X409,$Z409)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE409" s="67" t="inlineStr">
@@ -33765,7 +33778,7 @@
       <c r="AB410" s="68" t="n"/>
       <c r="AC410" s="69" t="n"/>
       <c r="AD410" s="70">
-        <f>IF(AND(COUNTIF($B$5:B410,B410)=1,$B410&lt;&gt;"",$AB410&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B410,B410)=1,$B410&lt;&gt;"",$AB410&lt;&gt;"",COUNTA($J410,$L410,$N410,$P410,$R410,$T410,$V410,$X410,$Z410)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE410" s="67" t="inlineStr">
@@ -33843,7 +33856,7 @@
       <c r="AB411" s="68" t="n"/>
       <c r="AC411" s="69" t="n"/>
       <c r="AD411" s="70">
-        <f>IF(AND(COUNTIF($B$5:B411,B411)=1,$B411&lt;&gt;"",$AB411&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B411,B411)=1,$B411&lt;&gt;"",$AB411&lt;&gt;"",COUNTA($J411,$L411,$N411,$P411,$R411,$T411,$V411,$X411,$Z411)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE411" s="67" t="inlineStr">
@@ -33921,7 +33934,7 @@
       <c r="AB412" s="68" t="n"/>
       <c r="AC412" s="69" t="n"/>
       <c r="AD412" s="70">
-        <f>IF(AND(COUNTIF($B$5:B412,B412)=1,$B412&lt;&gt;"",$AB412&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B412,B412)=1,$B412&lt;&gt;"",$AB412&lt;&gt;"",COUNTA($J412,$L412,$N412,$P412,$R412,$T412,$V412,$X412,$Z412)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE412" s="67" t="inlineStr">
@@ -33999,7 +34012,7 @@
       <c r="AB413" s="68" t="n"/>
       <c r="AC413" s="69" t="n"/>
       <c r="AD413" s="70">
-        <f>IF(AND(COUNTIF($B$5:B413,B413)=1,$B413&lt;&gt;"",$AB413&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B413,B413)=1,$B413&lt;&gt;"",$AB413&lt;&gt;"",COUNTA($J413,$L413,$N413,$P413,$R413,$T413,$V413,$X413,$Z413)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE413" s="67" t="inlineStr">
@@ -34073,7 +34086,7 @@
       <c r="AB414" s="68" t="n"/>
       <c r="AC414" s="69" t="n"/>
       <c r="AD414" s="70">
-        <f>IF(AND(COUNTIF($B$5:B414,B414)=1,$B414&lt;&gt;"",$AB414&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B414,B414)=1,$B414&lt;&gt;"",$AB414&lt;&gt;"",COUNTA($J414,$L414,$N414,$P414,$R414,$T414,$V414,$X414,$Z414)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE414" s="67" t="inlineStr">
@@ -34147,7 +34160,7 @@
       <c r="AB415" s="68" t="n"/>
       <c r="AC415" s="69" t="n"/>
       <c r="AD415" s="70">
-        <f>IF(AND(COUNTIF($B$5:B415,B415)=1,$B415&lt;&gt;"",$AB415&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B415,B415)=1,$B415&lt;&gt;"",$AB415&lt;&gt;"",COUNTA($J415,$L415,$N415,$P415,$R415,$T415,$V415,$X415,$Z415)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE415" s="67" t="inlineStr">
@@ -34225,7 +34238,7 @@
       <c r="AB416" s="68" t="n"/>
       <c r="AC416" s="69" t="n"/>
       <c r="AD416" s="70">
-        <f>IF(AND(COUNTIF($B$5:B416,B416)=1,$B416&lt;&gt;"",$AB416&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B416,B416)=1,$B416&lt;&gt;"",$AB416&lt;&gt;"",COUNTA($J416,$L416,$N416,$P416,$R416,$T416,$V416,$X416,$Z416)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE416" s="67" t="inlineStr">
@@ -34303,7 +34316,7 @@
       <c r="AB417" s="68" t="n"/>
       <c r="AC417" s="69" t="n"/>
       <c r="AD417" s="70">
-        <f>IF(AND(COUNTIF($B$5:B417,B417)=1,$B417&lt;&gt;"",$AB417&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B417,B417)=1,$B417&lt;&gt;"",$AB417&lt;&gt;"",COUNTA($J417,$L417,$N417,$P417,$R417,$T417,$V417,$X417,$Z417)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE417" s="67" t="inlineStr">
@@ -34381,7 +34394,7 @@
       <c r="AB418" s="68" t="n"/>
       <c r="AC418" s="69" t="n"/>
       <c r="AD418" s="70">
-        <f>IF(AND(COUNTIF($B$5:B418,B418)=1,$B418&lt;&gt;"",$AB418&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B418,B418)=1,$B418&lt;&gt;"",$AB418&lt;&gt;"",COUNTA($J418,$L418,$N418,$P418,$R418,$T418,$V418,$X418,$Z418)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE418" s="67" t="inlineStr">
@@ -34459,7 +34472,7 @@
       <c r="AB419" s="68" t="n"/>
       <c r="AC419" s="69" t="n"/>
       <c r="AD419" s="70">
-        <f>IF(AND(COUNTIF($B$5:B419,B419)=1,$B419&lt;&gt;"",$AB419&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B419,B419)=1,$B419&lt;&gt;"",$AB419&lt;&gt;"",COUNTA($J419,$L419,$N419,$P419,$R419,$T419,$V419,$X419,$Z419)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE419" s="67" t="inlineStr">
@@ -34537,7 +34550,7 @@
       <c r="AB420" s="68" t="n"/>
       <c r="AC420" s="69" t="n"/>
       <c r="AD420" s="70">
-        <f>IF(AND(COUNTIF($B$5:B420,B420)=1,$B420&lt;&gt;"",$AB420&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B420,B420)=1,$B420&lt;&gt;"",$AB420&lt;&gt;"",COUNTA($J420,$L420,$N420,$P420,$R420,$T420,$V420,$X420,$Z420)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE420" s="67" t="inlineStr">
@@ -34615,7 +34628,7 @@
       <c r="AB421" s="68" t="n"/>
       <c r="AC421" s="69" t="n"/>
       <c r="AD421" s="70">
-        <f>IF(AND(COUNTIF($B$5:B421,B421)=1,$B421&lt;&gt;"",$AB421&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B421,B421)=1,$B421&lt;&gt;"",$AB421&lt;&gt;"",COUNTA($J421,$L421,$N421,$P421,$R421,$T421,$V421,$X421,$Z421)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE421" s="67" t="inlineStr">
@@ -34693,7 +34706,7 @@
       <c r="AB422" s="68" t="n"/>
       <c r="AC422" s="69" t="n"/>
       <c r="AD422" s="70">
-        <f>IF(AND(COUNTIF($B$5:B422,B422)=1,$B422&lt;&gt;"",$AB422&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B422,B422)=1,$B422&lt;&gt;"",$AB422&lt;&gt;"",COUNTA($J422,$L422,$N422,$P422,$R422,$T422,$V422,$X422,$Z422)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE422" s="67" t="inlineStr">
@@ -34771,7 +34784,7 @@
       <c r="AB423" s="68" t="n"/>
       <c r="AC423" s="69" t="n"/>
       <c r="AD423" s="70">
-        <f>IF(AND(COUNTIF($B$5:B423,B423)=1,$B423&lt;&gt;"",$AB423&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B423,B423)=1,$B423&lt;&gt;"",$AB423&lt;&gt;"",COUNTA($J423,$L423,$N423,$P423,$R423,$T423,$V423,$X423,$Z423)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE423" s="67" t="inlineStr">
@@ -34849,7 +34862,7 @@
       <c r="AB424" s="68" t="n"/>
       <c r="AC424" s="69" t="n"/>
       <c r="AD424" s="70">
-        <f>IF(AND(COUNTIF($B$5:B424,B424)=1,$B424&lt;&gt;"",$AB424&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B424,B424)=1,$B424&lt;&gt;"",$AB424&lt;&gt;"",COUNTA($J424,$L424,$N424,$P424,$R424,$T424,$V424,$X424,$Z424)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE424" s="67" t="inlineStr">
@@ -34923,7 +34936,7 @@
       <c r="AB425" s="68" t="n"/>
       <c r="AC425" s="69" t="n"/>
       <c r="AD425" s="70">
-        <f>IF(AND(COUNTIF($B$5:B425,B425)=1,$B425&lt;&gt;"",$AB425&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B425,B425)=1,$B425&lt;&gt;"",$AB425&lt;&gt;"",COUNTA($J425,$L425,$N425,$P425,$R425,$T425,$V425,$X425,$Z425)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE425" s="67" t="inlineStr">
@@ -34993,7 +35006,7 @@
       <c r="AB426" s="68" t="n"/>
       <c r="AC426" s="69" t="n"/>
       <c r="AD426" s="70">
-        <f>IF(AND(COUNTIF($B$5:B426,B426)=1,$B426&lt;&gt;"",$AB426&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B426,B426)=1,$B426&lt;&gt;"",$AB426&lt;&gt;"",COUNTA($J426,$L426,$N426,$P426,$R426,$T426,$V426,$X426,$Z426)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE426" s="67" t="inlineStr">
@@ -35067,7 +35080,7 @@
       <c r="AB427" s="68" t="n"/>
       <c r="AC427" s="69" t="n"/>
       <c r="AD427" s="70">
-        <f>IF(AND(COUNTIF($B$5:B427,B427)=1,$B427&lt;&gt;"",$AB427&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B427,B427)=1,$B427&lt;&gt;"",$AB427&lt;&gt;"",COUNTA($J427,$L427,$N427,$P427,$R427,$T427,$V427,$X427,$Z427)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE427" s="67" t="inlineStr">
@@ -35141,7 +35154,7 @@
       <c r="AB428" s="68" t="n"/>
       <c r="AC428" s="69" t="n"/>
       <c r="AD428" s="70">
-        <f>IF(AND(COUNTIF($B$5:B428,B428)=1,$B428&lt;&gt;"",$AB428&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B428,B428)=1,$B428&lt;&gt;"",$AB428&lt;&gt;"",COUNTA($J428,$L428,$N428,$P428,$R428,$T428,$V428,$X428,$Z428)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE428" s="67" t="inlineStr">
@@ -35211,7 +35224,7 @@
       <c r="AB429" s="68" t="n"/>
       <c r="AC429" s="69" t="n"/>
       <c r="AD429" s="70">
-        <f>IF(AND(COUNTIF($B$5:B429,B429)=1,$B429&lt;&gt;"",$AB429&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B429,B429)=1,$B429&lt;&gt;"",$AB429&lt;&gt;"",COUNTA($J429,$L429,$N429,$P429,$R429,$T429,$V429,$X429,$Z429)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE429" s="67" t="inlineStr">
@@ -35285,7 +35298,7 @@
       <c r="AB430" s="68" t="n"/>
       <c r="AC430" s="69" t="n"/>
       <c r="AD430" s="70">
-        <f>IF(AND(COUNTIF($B$5:B430,B430)=1,$B430&lt;&gt;"",$AB430&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B430,B430)=1,$B430&lt;&gt;"",$AB430&lt;&gt;"",COUNTA($J430,$L430,$N430,$P430,$R430,$T430,$V430,$X430,$Z430)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE430" s="67" t="inlineStr">
@@ -35363,7 +35376,7 @@
       <c r="AB431" s="68" t="n"/>
       <c r="AC431" s="69" t="n"/>
       <c r="AD431" s="70">
-        <f>IF(AND(COUNTIF($B$5:B431,B431)=1,$B431&lt;&gt;"",$AB431&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B431,B431)=1,$B431&lt;&gt;"",$AB431&lt;&gt;"",COUNTA($J431,$L431,$N431,$P431,$R431,$T431,$V431,$X431,$Z431)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE431" s="67" t="inlineStr">
@@ -35441,7 +35454,7 @@
       <c r="AB432" s="68" t="n"/>
       <c r="AC432" s="69" t="n"/>
       <c r="AD432" s="70">
-        <f>IF(AND(COUNTIF($B$5:B432,B432)=1,$B432&lt;&gt;"",$AB432&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B432,B432)=1,$B432&lt;&gt;"",$AB432&lt;&gt;"",COUNTA($J432,$L432,$N432,$P432,$R432,$T432,$V432,$X432,$Z432)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE432" s="67" t="inlineStr">
@@ -35519,7 +35532,7 @@
       <c r="AB433" s="68" t="n"/>
       <c r="AC433" s="69" t="n"/>
       <c r="AD433" s="70">
-        <f>IF(AND(COUNTIF($B$5:B433,B433)=1,$B433&lt;&gt;"",$AB433&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B433,B433)=1,$B433&lt;&gt;"",$AB433&lt;&gt;"",COUNTA($J433,$L433,$N433,$P433,$R433,$T433,$V433,$X433,$Z433)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE433" s="67" t="inlineStr">
@@ -35597,7 +35610,7 @@
       <c r="AB434" s="68" t="n"/>
       <c r="AC434" s="69" t="n"/>
       <c r="AD434" s="70">
-        <f>IF(AND(COUNTIF($B$5:B434,B434)=1,$B434&lt;&gt;"",$AB434&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B434,B434)=1,$B434&lt;&gt;"",$AB434&lt;&gt;"",COUNTA($J434,$L434,$N434,$P434,$R434,$T434,$V434,$X434,$Z434)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE434" s="67" t="inlineStr">
@@ -35675,7 +35688,7 @@
       <c r="AB435" s="68" t="n"/>
       <c r="AC435" s="69" t="n"/>
       <c r="AD435" s="70">
-        <f>IF(AND(COUNTIF($B$5:B435,B435)=1,$B435&lt;&gt;"",$AB435&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B435,B435)=1,$B435&lt;&gt;"",$AB435&lt;&gt;"",COUNTA($J435,$L435,$N435,$P435,$R435,$T435,$V435,$X435,$Z435)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE435" s="67" t="inlineStr">
@@ -35753,7 +35766,7 @@
       <c r="AB436" s="68" t="n"/>
       <c r="AC436" s="69" t="n"/>
       <c r="AD436" s="70">
-        <f>IF(AND(COUNTIF($B$5:B436,B436)=1,$B436&lt;&gt;"",$AB436&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B436,B436)=1,$B436&lt;&gt;"",$AB436&lt;&gt;"",COUNTA($J436,$L436,$N436,$P436,$R436,$T436,$V436,$X436,$Z436)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE436" s="67" t="inlineStr">
@@ -35831,7 +35844,7 @@
       <c r="AB437" s="68" t="n"/>
       <c r="AC437" s="69" t="n"/>
       <c r="AD437" s="70">
-        <f>IF(AND(COUNTIF($B$5:B437,B437)=1,$B437&lt;&gt;"",$AB437&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B437,B437)=1,$B437&lt;&gt;"",$AB437&lt;&gt;"",COUNTA($J437,$L437,$N437,$P437,$R437,$T437,$V437,$X437,$Z437)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE437" s="67" t="inlineStr">
@@ -35909,7 +35922,7 @@
       <c r="AB438" s="68" t="n"/>
       <c r="AC438" s="69" t="n"/>
       <c r="AD438" s="70">
-        <f>IF(AND(COUNTIF($B$5:B438,B438)=1,$B438&lt;&gt;"",$AB438&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B438,B438)=1,$B438&lt;&gt;"",$AB438&lt;&gt;"",COUNTA($J438,$L438,$N438,$P438,$R438,$T438,$V438,$X438,$Z438)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE438" s="67" t="inlineStr">
@@ -35987,7 +36000,7 @@
       <c r="AB439" s="68" t="n"/>
       <c r="AC439" s="69" t="n"/>
       <c r="AD439" s="70">
-        <f>IF(AND(COUNTIF($B$5:B439,B439)=1,$B439&lt;&gt;"",$AB439&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B439,B439)=1,$B439&lt;&gt;"",$AB439&lt;&gt;"",COUNTA($J439,$L439,$N439,$P439,$R439,$T439,$V439,$X439,$Z439)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE439" s="67" t="inlineStr">
@@ -36061,7 +36074,7 @@
       <c r="AB440" s="68" t="n"/>
       <c r="AC440" s="69" t="n"/>
       <c r="AD440" s="70">
-        <f>IF(AND(COUNTIF($B$5:B440,B440)=1,$B440&lt;&gt;"",$AB440&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B440,B440)=1,$B440&lt;&gt;"",$AB440&lt;&gt;"",COUNTA($J440,$L440,$N440,$P440,$R440,$T440,$V440,$X440,$Z440)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE440" s="67" t="inlineStr">
@@ -36135,7 +36148,7 @@
       <c r="AB441" s="68" t="n"/>
       <c r="AC441" s="69" t="n"/>
       <c r="AD441" s="70">
-        <f>IF(AND(COUNTIF($B$5:B441,B441)=1,$B441&lt;&gt;"",$AB441&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B441,B441)=1,$B441&lt;&gt;"",$AB441&lt;&gt;"",COUNTA($J441,$L441,$N441,$P441,$R441,$T441,$V441,$X441,$Z441)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE441" s="67" t="inlineStr">
@@ -36213,7 +36226,7 @@
       <c r="AB442" s="68" t="n"/>
       <c r="AC442" s="69" t="n"/>
       <c r="AD442" s="70">
-        <f>IF(AND(COUNTIF($B$5:B442,B442)=1,$B442&lt;&gt;"",$AB442&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B442,B442)=1,$B442&lt;&gt;"",$AB442&lt;&gt;"",COUNTA($J442,$L442,$N442,$P442,$R442,$T442,$V442,$X442,$Z442)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE442" s="67" t="inlineStr">
@@ -36291,7 +36304,7 @@
       <c r="AB443" s="68" t="n"/>
       <c r="AC443" s="69" t="n"/>
       <c r="AD443" s="70">
-        <f>IF(AND(COUNTIF($B$5:B443,B443)=1,$B443&lt;&gt;"",$AB443&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B443,B443)=1,$B443&lt;&gt;"",$AB443&lt;&gt;"",COUNTA($J443,$L443,$N443,$P443,$R443,$T443,$V443,$X443,$Z443)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE443" s="67" t="inlineStr">
@@ -36369,7 +36382,7 @@
       <c r="AB444" s="68" t="n"/>
       <c r="AC444" s="69" t="n"/>
       <c r="AD444" s="70">
-        <f>IF(AND(COUNTIF($B$5:B444,B444)=1,$B444&lt;&gt;"",$AB444&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B444,B444)=1,$B444&lt;&gt;"",$AB444&lt;&gt;"",COUNTA($J444,$L444,$N444,$P444,$R444,$T444,$V444,$X444,$Z444)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE444" s="67" t="inlineStr">
@@ -36443,7 +36456,7 @@
       <c r="AB445" s="68" t="n"/>
       <c r="AC445" s="69" t="n"/>
       <c r="AD445" s="70">
-        <f>IF(AND(COUNTIF($B$5:B445,B445)=1,$B445&lt;&gt;"",$AB445&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B445,B445)=1,$B445&lt;&gt;"",$AB445&lt;&gt;"",COUNTA($J445,$L445,$N445,$P445,$R445,$T445,$V445,$X445,$Z445)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE445" s="67" t="inlineStr">
@@ -36513,7 +36526,7 @@
       <c r="AB446" s="68" t="n"/>
       <c r="AC446" s="69" t="n"/>
       <c r="AD446" s="70">
-        <f>IF(AND(COUNTIF($B$5:B446,B446)=1,$B446&lt;&gt;"",$AB446&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B446,B446)=1,$B446&lt;&gt;"",$AB446&lt;&gt;"",COUNTA($J446,$L446,$N446,$P446,$R446,$T446,$V446,$X446,$Z446)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE446" s="67" t="inlineStr">
@@ -36587,7 +36600,7 @@
       <c r="AB447" s="68" t="n"/>
       <c r="AC447" s="69" t="n"/>
       <c r="AD447" s="70">
-        <f>IF(AND(COUNTIF($B$5:B447,B447)=1,$B447&lt;&gt;"",$AB447&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B447,B447)=1,$B447&lt;&gt;"",$AB447&lt;&gt;"",COUNTA($J447,$L447,$N447,$P447,$R447,$T447,$V447,$X447,$Z447)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE447" s="67" t="inlineStr">
@@ -36665,7 +36678,7 @@
       <c r="AB448" s="68" t="n"/>
       <c r="AC448" s="69" t="n"/>
       <c r="AD448" s="70">
-        <f>IF(AND(COUNTIF($B$5:B448,B448)=1,$B448&lt;&gt;"",$AB448&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B448,B448)=1,$B448&lt;&gt;"",$AB448&lt;&gt;"",COUNTA($J448,$L448,$N448,$P448,$R448,$T448,$V448,$X448,$Z448)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE448" s="67" t="inlineStr">
@@ -36743,7 +36756,7 @@
       <c r="AB449" s="68" t="n"/>
       <c r="AC449" s="69" t="n"/>
       <c r="AD449" s="70">
-        <f>IF(AND(COUNTIF($B$5:B449,B449)=1,$B449&lt;&gt;"",$AB449&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B449,B449)=1,$B449&lt;&gt;"",$AB449&lt;&gt;"",COUNTA($J449,$L449,$N449,$P449,$R449,$T449,$V449,$X449,$Z449)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE449" s="67" t="inlineStr">
@@ -36821,7 +36834,7 @@
       <c r="AB450" s="68" t="n"/>
       <c r="AC450" s="69" t="n"/>
       <c r="AD450" s="70">
-        <f>IF(AND(COUNTIF($B$5:B450,B450)=1,$B450&lt;&gt;"",$AB450&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B450,B450)=1,$B450&lt;&gt;"",$AB450&lt;&gt;"",COUNTA($J450,$L450,$N450,$P450,$R450,$T450,$V450,$X450,$Z450)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE450" s="67" t="inlineStr">
@@ -36899,7 +36912,7 @@
       <c r="AB451" s="68" t="n"/>
       <c r="AC451" s="69" t="n"/>
       <c r="AD451" s="70">
-        <f>IF(AND(COUNTIF($B$5:B451,B451)=1,$B451&lt;&gt;"",$AB451&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B451,B451)=1,$B451&lt;&gt;"",$AB451&lt;&gt;"",COUNTA($J451,$L451,$N451,$P451,$R451,$T451,$V451,$X451,$Z451)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE451" s="67" t="inlineStr">
@@ -36977,7 +36990,7 @@
       <c r="AB452" s="68" t="n"/>
       <c r="AC452" s="69" t="n"/>
       <c r="AD452" s="70">
-        <f>IF(AND(COUNTIF($B$5:B452,B452)=1,$B452&lt;&gt;"",$AB452&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B452,B452)=1,$B452&lt;&gt;"",$AB452&lt;&gt;"",COUNTA($J452,$L452,$N452,$P452,$R452,$T452,$V452,$X452,$Z452)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE452" s="67" t="inlineStr">
@@ -37055,7 +37068,7 @@
       <c r="AB453" s="68" t="n"/>
       <c r="AC453" s="69" t="n"/>
       <c r="AD453" s="70">
-        <f>IF(AND(COUNTIF($B$5:B453,B453)=1,$B453&lt;&gt;"",$AB453&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B453,B453)=1,$B453&lt;&gt;"",$AB453&lt;&gt;"",COUNTA($J453,$L453,$N453,$P453,$R453,$T453,$V453,$X453,$Z453)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE453" s="67" t="inlineStr">
@@ -37129,7 +37142,7 @@
       <c r="AB454" s="68" t="n"/>
       <c r="AC454" s="69" t="n"/>
       <c r="AD454" s="70">
-        <f>IF(AND(COUNTIF($B$5:B454,B454)=1,$B454&lt;&gt;"",$AB454&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B454,B454)=1,$B454&lt;&gt;"",$AB454&lt;&gt;"",COUNTA($J454,$L454,$N454,$P454,$R454,$T454,$V454,$X454,$Z454)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE454" s="67" t="inlineStr">
@@ -37203,7 +37216,7 @@
       <c r="AB455" s="68" t="n"/>
       <c r="AC455" s="69" t="n"/>
       <c r="AD455" s="70">
-        <f>IF(AND(COUNTIF($B$5:B455,B455)=1,$B455&lt;&gt;"",$AB455&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B455,B455)=1,$B455&lt;&gt;"",$AB455&lt;&gt;"",COUNTA($J455,$L455,$N455,$P455,$R455,$T455,$V455,$X455,$Z455)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE455" s="67" t="inlineStr">
@@ -37281,7 +37294,7 @@
       <c r="AB456" s="68" t="n"/>
       <c r="AC456" s="69" t="n"/>
       <c r="AD456" s="70">
-        <f>IF(AND(COUNTIF($B$5:B456,B456)=1,$B456&lt;&gt;"",$AB456&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B456,B456)=1,$B456&lt;&gt;"",$AB456&lt;&gt;"",COUNTA($J456,$L456,$N456,$P456,$R456,$T456,$V456,$X456,$Z456)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE456" s="67" t="inlineStr">
@@ -37359,7 +37372,7 @@
       <c r="AB457" s="68" t="n"/>
       <c r="AC457" s="69" t="n"/>
       <c r="AD457" s="70">
-        <f>IF(AND(COUNTIF($B$5:B457,B457)=1,$B457&lt;&gt;"",$AB457&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B457,B457)=1,$B457&lt;&gt;"",$AB457&lt;&gt;"",COUNTA($J457,$L457,$N457,$P457,$R457,$T457,$V457,$X457,$Z457)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE457" s="67" t="inlineStr">
@@ -37437,7 +37450,7 @@
       <c r="AB458" s="68" t="n"/>
       <c r="AC458" s="69" t="n"/>
       <c r="AD458" s="70">
-        <f>IF(AND(COUNTIF($B$5:B458,B458)=1,$B458&lt;&gt;"",$AB458&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B458,B458)=1,$B458&lt;&gt;"",$AB458&lt;&gt;"",COUNTA($J458,$L458,$N458,$P458,$R458,$T458,$V458,$X458,$Z458)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE458" s="67" t="inlineStr">
@@ -37515,7 +37528,7 @@
       <c r="AB459" s="68" t="n"/>
       <c r="AC459" s="69" t="n"/>
       <c r="AD459" s="70">
-        <f>IF(AND(COUNTIF($B$5:B459,B459)=1,$B459&lt;&gt;"",$AB459&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B459,B459)=1,$B459&lt;&gt;"",$AB459&lt;&gt;"",COUNTA($J459,$L459,$N459,$P459,$R459,$T459,$V459,$X459,$Z459)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE459" s="67" t="inlineStr">
@@ -37589,7 +37602,7 @@
       <c r="AB460" s="68" t="n"/>
       <c r="AC460" s="69" t="n"/>
       <c r="AD460" s="70">
-        <f>IF(AND(COUNTIF($B$5:B460,B460)=1,$B460&lt;&gt;"",$AB460&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B460,B460)=1,$B460&lt;&gt;"",$AB460&lt;&gt;"",COUNTA($J460,$L460,$N460,$P460,$R460,$T460,$V460,$X460,$Z460)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE460" s="67" t="inlineStr">
@@ -37663,7 +37676,7 @@
       <c r="AB461" s="68" t="n"/>
       <c r="AC461" s="69" t="n"/>
       <c r="AD461" s="70">
-        <f>IF(AND(COUNTIF($B$5:B461,B461)=1,$B461&lt;&gt;"",$AB461&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B461,B461)=1,$B461&lt;&gt;"",$AB461&lt;&gt;"",COUNTA($J461,$L461,$N461,$P461,$R461,$T461,$V461,$X461,$Z461)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE461" s="67" t="inlineStr">
@@ -37741,7 +37754,7 @@
       <c r="AB462" s="68" t="n"/>
       <c r="AC462" s="69" t="n"/>
       <c r="AD462" s="70">
-        <f>IF(AND(COUNTIF($B$5:B462,B462)=1,$B462&lt;&gt;"",$AB462&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B462,B462)=1,$B462&lt;&gt;"",$AB462&lt;&gt;"",COUNTA($J462,$L462,$N462,$P462,$R462,$T462,$V462,$X462,$Z462)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE462" s="67" t="inlineStr">
@@ -37819,7 +37832,7 @@
       <c r="AB463" s="68" t="n"/>
       <c r="AC463" s="69" t="n"/>
       <c r="AD463" s="70">
-        <f>IF(AND(COUNTIF($B$5:B463,B463)=1,$B463&lt;&gt;"",$AB463&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B463,B463)=1,$B463&lt;&gt;"",$AB463&lt;&gt;"",COUNTA($J463,$L463,$N463,$P463,$R463,$T463,$V463,$X463,$Z463)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE463" s="67" t="inlineStr">
@@ -37897,7 +37910,7 @@
       <c r="AB464" s="68" t="n"/>
       <c r="AC464" s="69" t="n"/>
       <c r="AD464" s="70">
-        <f>IF(AND(COUNTIF($B$5:B464,B464)=1,$B464&lt;&gt;"",$AB464&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B464,B464)=1,$B464&lt;&gt;"",$AB464&lt;&gt;"",COUNTA($J464,$L464,$N464,$P464,$R464,$T464,$V464,$X464,$Z464)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE464" s="67" t="inlineStr">
@@ -37975,7 +37988,7 @@
       <c r="AB465" s="68" t="n"/>
       <c r="AC465" s="69" t="n"/>
       <c r="AD465" s="70">
-        <f>IF(AND(COUNTIF($B$5:B465,B465)=1,$B465&lt;&gt;"",$AB465&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B465,B465)=1,$B465&lt;&gt;"",$AB465&lt;&gt;"",COUNTA($J465,$L465,$N465,$P465,$R465,$T465,$V465,$X465,$Z465)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE465" s="67" t="inlineStr">
@@ -38049,7 +38062,7 @@
       <c r="AB466" s="68" t="n"/>
       <c r="AC466" s="69" t="n"/>
       <c r="AD466" s="70">
-        <f>IF(AND(COUNTIF($B$5:B466,B466)=1,$B466&lt;&gt;"",$AB466&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B466,B466)=1,$B466&lt;&gt;"",$AB466&lt;&gt;"",COUNTA($J466,$L466,$N466,$P466,$R466,$T466,$V466,$X466,$Z466)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE466" s="67" t="inlineStr">
@@ -38123,7 +38136,7 @@
       <c r="AB467" s="68" t="n"/>
       <c r="AC467" s="69" t="n"/>
       <c r="AD467" s="70">
-        <f>IF(AND(COUNTIF($B$5:B467,B467)=1,$B467&lt;&gt;"",$AB467&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B467,B467)=1,$B467&lt;&gt;"",$AB467&lt;&gt;"",COUNTA($J467,$L467,$N467,$P467,$R467,$T467,$V467,$X467,$Z467)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE467" s="67" t="inlineStr">
@@ -38197,7 +38210,7 @@
       <c r="AB468" s="68" t="n"/>
       <c r="AC468" s="69" t="n"/>
       <c r="AD468" s="70">
-        <f>IF(AND(COUNTIF($B$5:B468,B468)=1,$B468&lt;&gt;"",$AB468&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B468,B468)=1,$B468&lt;&gt;"",$AB468&lt;&gt;"",COUNTA($J468,$L468,$N468,$P468,$R468,$T468,$V468,$X468,$Z468)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE468" s="67" t="inlineStr">
@@ -38271,7 +38284,7 @@
       <c r="AB469" s="68" t="n"/>
       <c r="AC469" s="69" t="n"/>
       <c r="AD469" s="70">
-        <f>IF(AND(COUNTIF($B$5:B469,B469)=1,$B469&lt;&gt;"",$AB469&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B469,B469)=1,$B469&lt;&gt;"",$AB469&lt;&gt;"",COUNTA($J469,$L469,$N469,$P469,$R469,$T469,$V469,$X469,$Z469)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE469" s="67" t="inlineStr">
@@ -38349,7 +38362,7 @@
       <c r="AB470" s="68" t="n"/>
       <c r="AC470" s="69" t="n"/>
       <c r="AD470" s="70">
-        <f>IF(AND(COUNTIF($B$5:B470,B470)=1,$B470&lt;&gt;"",$AB470&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B470,B470)=1,$B470&lt;&gt;"",$AB470&lt;&gt;"",COUNTA($J470,$L470,$N470,$P470,$R470,$T470,$V470,$X470,$Z470)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE470" s="67" t="inlineStr">
@@ -38427,7 +38440,7 @@
       <c r="AB471" s="68" t="n"/>
       <c r="AC471" s="69" t="n"/>
       <c r="AD471" s="70">
-        <f>IF(AND(COUNTIF($B$5:B471,B471)=1,$B471&lt;&gt;"",$AB471&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B471,B471)=1,$B471&lt;&gt;"",$AB471&lt;&gt;"",COUNTA($J471,$L471,$N471,$P471,$R471,$T471,$V471,$X471,$Z471)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE471" s="67" t="inlineStr">
@@ -38505,7 +38518,7 @@
       <c r="AB472" s="68" t="n"/>
       <c r="AC472" s="69" t="n"/>
       <c r="AD472" s="70">
-        <f>IF(AND(COUNTIF($B$5:B472,B472)=1,$B472&lt;&gt;"",$AB472&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B472,B472)=1,$B472&lt;&gt;"",$AB472&lt;&gt;"",COUNTA($J472,$L472,$N472,$P472,$R472,$T472,$V472,$X472,$Z472)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE472" s="67" t="inlineStr">
@@ -38583,7 +38596,7 @@
       <c r="AB473" s="68" t="n"/>
       <c r="AC473" s="69" t="n"/>
       <c r="AD473" s="70">
-        <f>IF(AND(COUNTIF($B$5:B473,B473)=1,$B473&lt;&gt;"",$AB473&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B473,B473)=1,$B473&lt;&gt;"",$AB473&lt;&gt;"",COUNTA($J473,$L473,$N473,$P473,$R473,$T473,$V473,$X473,$Z473)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE473" s="67" t="inlineStr">
@@ -38661,7 +38674,7 @@
       <c r="AB474" s="68" t="n"/>
       <c r="AC474" s="69" t="n"/>
       <c r="AD474" s="70">
-        <f>IF(AND(COUNTIF($B$5:B474,B474)=1,$B474&lt;&gt;"",$AB474&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B474,B474)=1,$B474&lt;&gt;"",$AB474&lt;&gt;"",COUNTA($J474,$L474,$N474,$P474,$R474,$T474,$V474,$X474,$Z474)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE474" s="67" t="inlineStr">
@@ -38739,7 +38752,7 @@
       <c r="AB475" s="68" t="n"/>
       <c r="AC475" s="69" t="n"/>
       <c r="AD475" s="70">
-        <f>IF(AND(COUNTIF($B$5:B475,B475)=1,$B475&lt;&gt;"",$AB475&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B475,B475)=1,$B475&lt;&gt;"",$AB475&lt;&gt;"",COUNTA($J475,$L475,$N475,$P475,$R475,$T475,$V475,$X475,$Z475)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE475" s="67" t="inlineStr">
@@ -38817,7 +38830,7 @@
       <c r="AB476" s="68" t="n"/>
       <c r="AC476" s="69" t="n"/>
       <c r="AD476" s="70">
-        <f>IF(AND(COUNTIF($B$5:B476,B476)=1,$B476&lt;&gt;"",$AB476&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B476,B476)=1,$B476&lt;&gt;"",$AB476&lt;&gt;"",COUNTA($J476,$L476,$N476,$P476,$R476,$T476,$V476,$X476,$Z476)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE476" s="67" t="inlineStr">
@@ -38895,7 +38908,7 @@
       <c r="AB477" s="68" t="n"/>
       <c r="AC477" s="69" t="n"/>
       <c r="AD477" s="70">
-        <f>IF(AND(COUNTIF($B$5:B477,B477)=1,$B477&lt;&gt;"",$AB477&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B477,B477)=1,$B477&lt;&gt;"",$AB477&lt;&gt;"",COUNTA($J477,$L477,$N477,$P477,$R477,$T477,$V477,$X477,$Z477)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE477" s="67" t="inlineStr">
@@ -38973,7 +38986,7 @@
       <c r="AB478" s="68" t="n"/>
       <c r="AC478" s="69" t="n"/>
       <c r="AD478" s="70">
-        <f>IF(AND(COUNTIF($B$5:B478,B478)=1,$B478&lt;&gt;"",$AB478&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B478,B478)=1,$B478&lt;&gt;"",$AB478&lt;&gt;"",COUNTA($J478,$L478,$N478,$P478,$R478,$T478,$V478,$X478,$Z478)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE478" s="67" t="inlineStr">
@@ -39051,7 +39064,7 @@
       <c r="AB479" s="68" t="n"/>
       <c r="AC479" s="69" t="n"/>
       <c r="AD479" s="70">
-        <f>IF(AND(COUNTIF($B$5:B479,B479)=1,$B479&lt;&gt;"",$AB479&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B479,B479)=1,$B479&lt;&gt;"",$AB479&lt;&gt;"",COUNTA($J479,$L479,$N479,$P479,$R479,$T479,$V479,$X479,$Z479)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE479" s="67" t="inlineStr">
@@ -39129,7 +39142,7 @@
       <c r="AB480" s="68" t="n"/>
       <c r="AC480" s="69" t="n"/>
       <c r="AD480" s="70">
-        <f>IF(AND(COUNTIF($B$5:B480,B480)=1,$B480&lt;&gt;"",$AB480&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B480,B480)=1,$B480&lt;&gt;"",$AB480&lt;&gt;"",COUNTA($J480,$L480,$N480,$P480,$R480,$T480,$V480,$X480,$Z480)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE480" s="67" t="inlineStr">
@@ -39207,7 +39220,7 @@
       <c r="AB481" s="68" t="n"/>
       <c r="AC481" s="69" t="n"/>
       <c r="AD481" s="70">
-        <f>IF(AND(COUNTIF($B$5:B481,B481)=1,$B481&lt;&gt;"",$AB481&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B481,B481)=1,$B481&lt;&gt;"",$AB481&lt;&gt;"",COUNTA($J481,$L481,$N481,$P481,$R481,$T481,$V481,$X481,$Z481)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE481" s="67" t="inlineStr">
@@ -39285,7 +39298,7 @@
       <c r="AB482" s="68" t="n"/>
       <c r="AC482" s="69" t="n"/>
       <c r="AD482" s="70">
-        <f>IF(AND(COUNTIF($B$5:B482,B482)=1,$B482&lt;&gt;"",$AB482&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B482,B482)=1,$B482&lt;&gt;"",$AB482&lt;&gt;"",COUNTA($J482,$L482,$N482,$P482,$R482,$T482,$V482,$X482,$Z482)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE482" s="67" t="inlineStr">
@@ -39363,7 +39376,7 @@
       <c r="AB483" s="68" t="n"/>
       <c r="AC483" s="69" t="n"/>
       <c r="AD483" s="70">
-        <f>IF(AND(COUNTIF($B$5:B483,B483)=1,$B483&lt;&gt;"",$AB483&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B483,B483)=1,$B483&lt;&gt;"",$AB483&lt;&gt;"",COUNTA($J483,$L483,$N483,$P483,$R483,$T483,$V483,$X483,$Z483)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE483" s="67" t="inlineStr">
@@ -39437,7 +39450,7 @@
       <c r="AB484" s="68" t="n"/>
       <c r="AC484" s="69" t="n"/>
       <c r="AD484" s="70">
-        <f>IF(AND(COUNTIF($B$5:B484,B484)=1,$B484&lt;&gt;"",$AB484&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B484,B484)=1,$B484&lt;&gt;"",$AB484&lt;&gt;"",COUNTA($J484,$L484,$N484,$P484,$R484,$T484,$V484,$X484,$Z484)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE484" s="67" t="inlineStr">
@@ -39511,7 +39524,7 @@
       <c r="AB485" s="68" t="n"/>
       <c r="AC485" s="69" t="n"/>
       <c r="AD485" s="70">
-        <f>IF(AND(COUNTIF($B$5:B485,B485)=1,$B485&lt;&gt;"",$AB485&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B485,B485)=1,$B485&lt;&gt;"",$AB485&lt;&gt;"",COUNTA($J485,$L485,$N485,$P485,$R485,$T485,$V485,$X485,$Z485)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE485" s="67" t="inlineStr">
@@ -39589,7 +39602,7 @@
       <c r="AB486" s="68" t="n"/>
       <c r="AC486" s="69" t="n"/>
       <c r="AD486" s="70">
-        <f>IF(AND(COUNTIF($B$5:B486,B486)=1,$B486&lt;&gt;"",$AB486&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B486,B486)=1,$B486&lt;&gt;"",$AB486&lt;&gt;"",COUNTA($J486,$L486,$N486,$P486,$R486,$T486,$V486,$X486,$Z486)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE486" s="67" t="inlineStr">
@@ -39667,7 +39680,7 @@
       <c r="AB487" s="68" t="n"/>
       <c r="AC487" s="69" t="n"/>
       <c r="AD487" s="70">
-        <f>IF(AND(COUNTIF($B$5:B487,B487)=1,$B487&lt;&gt;"",$AB487&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B487,B487)=1,$B487&lt;&gt;"",$AB487&lt;&gt;"",COUNTA($J487,$L487,$N487,$P487,$R487,$T487,$V487,$X487,$Z487)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE487" s="67" t="inlineStr">
@@ -39745,7 +39758,7 @@
       <c r="AB488" s="68" t="n"/>
       <c r="AC488" s="69" t="n"/>
       <c r="AD488" s="70">
-        <f>IF(AND(COUNTIF($B$5:B488,B488)=1,$B488&lt;&gt;"",$AB488&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B488,B488)=1,$B488&lt;&gt;"",$AB488&lt;&gt;"",COUNTA($J488,$L488,$N488,$P488,$R488,$T488,$V488,$X488,$Z488)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE488" s="67" t="inlineStr">
@@ -39819,7 +39832,7 @@
       <c r="AB489" s="68" t="n"/>
       <c r="AC489" s="69" t="n"/>
       <c r="AD489" s="70">
-        <f>IF(AND(COUNTIF($B$5:B489,B489)=1,$B489&lt;&gt;"",$AB489&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B489,B489)=1,$B489&lt;&gt;"",$AB489&lt;&gt;"",COUNTA($J489,$L489,$N489,$P489,$R489,$T489,$V489,$X489,$Z489)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE489" s="67" t="inlineStr">
@@ -39893,7 +39906,7 @@
       <c r="AB490" s="68" t="n"/>
       <c r="AC490" s="69" t="n"/>
       <c r="AD490" s="70">
-        <f>IF(AND(COUNTIF($B$5:B490,B490)=1,$B490&lt;&gt;"",$AB490&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B490,B490)=1,$B490&lt;&gt;"",$AB490&lt;&gt;"",COUNTA($J490,$L490,$N490,$P490,$R490,$T490,$V490,$X490,$Z490)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE490" s="67" t="inlineStr">
@@ -39967,7 +39980,7 @@
       <c r="AB491" s="68" t="n"/>
       <c r="AC491" s="69" t="n"/>
       <c r="AD491" s="70">
-        <f>IF(AND(COUNTIF($B$5:B491,B491)=1,$B491&lt;&gt;"",$AB491&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B491,B491)=1,$B491&lt;&gt;"",$AB491&lt;&gt;"",COUNTA($J491,$L491,$N491,$P491,$R491,$T491,$V491,$X491,$Z491)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE491" s="67" t="inlineStr">
@@ -40041,7 +40054,7 @@
       <c r="AB492" s="68" t="n"/>
       <c r="AC492" s="69" t="n"/>
       <c r="AD492" s="70">
-        <f>IF(AND(COUNTIF($B$5:B492,B492)=1,$B492&lt;&gt;"",$AB492&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B492,B492)=1,$B492&lt;&gt;"",$AB492&lt;&gt;"",COUNTA($J492,$L492,$N492,$P492,$R492,$T492,$V492,$X492,$Z492)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE492" s="67" t="inlineStr">
@@ -40119,7 +40132,7 @@
       <c r="AB493" s="68" t="n"/>
       <c r="AC493" s="69" t="n"/>
       <c r="AD493" s="70">
-        <f>IF(AND(COUNTIF($B$5:B493,B493)=1,$B493&lt;&gt;"",$AB493&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B493,B493)=1,$B493&lt;&gt;"",$AB493&lt;&gt;"",COUNTA($J493,$L493,$N493,$P493,$R493,$T493,$V493,$X493,$Z493)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE493" s="67" t="inlineStr">
@@ -40197,7 +40210,7 @@
       <c r="AB494" s="68" t="n"/>
       <c r="AC494" s="69" t="n"/>
       <c r="AD494" s="70">
-        <f>IF(AND(COUNTIF($B$5:B494,B494)=1,$B494&lt;&gt;"",$AB494&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B494,B494)=1,$B494&lt;&gt;"",$AB494&lt;&gt;"",COUNTA($J494,$L494,$N494,$P494,$R494,$T494,$V494,$X494,$Z494)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE494" s="67" t="inlineStr">
@@ -40275,7 +40288,7 @@
       <c r="AB495" s="68" t="n"/>
       <c r="AC495" s="69" t="n"/>
       <c r="AD495" s="70">
-        <f>IF(AND(COUNTIF($B$5:B495,B495)=1,$B495&lt;&gt;"",$AB495&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B495,B495)=1,$B495&lt;&gt;"",$AB495&lt;&gt;"",COUNTA($J495,$L495,$N495,$P495,$R495,$T495,$V495,$X495,$Z495)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE495" s="67" t="inlineStr">
@@ -40353,7 +40366,7 @@
       <c r="AB496" s="68" t="n"/>
       <c r="AC496" s="69" t="n"/>
       <c r="AD496" s="70">
-        <f>IF(AND(COUNTIF($B$5:B496,B496)=1,$B496&lt;&gt;"",$AB496&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B496,B496)=1,$B496&lt;&gt;"",$AB496&lt;&gt;"",COUNTA($J496,$L496,$N496,$P496,$R496,$T496,$V496,$X496,$Z496)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE496" s="67" t="inlineStr">
@@ -40431,7 +40444,7 @@
       <c r="AB497" s="68" t="n"/>
       <c r="AC497" s="69" t="n"/>
       <c r="AD497" s="70">
-        <f>IF(AND(COUNTIF($B$5:B497,B497)=1,$B497&lt;&gt;"",$AB497&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B497,B497)=1,$B497&lt;&gt;"",$AB497&lt;&gt;"",COUNTA($J497,$L497,$N497,$P497,$R497,$T497,$V497,$X497,$Z497)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE497" s="67" t="inlineStr">
@@ -40509,7 +40522,7 @@
       <c r="AB498" s="68" t="n"/>
       <c r="AC498" s="69" t="n"/>
       <c r="AD498" s="70">
-        <f>IF(AND(COUNTIF($B$5:B498,B498)=1,$B498&lt;&gt;"",$AB498&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B498,B498)=1,$B498&lt;&gt;"",$AB498&lt;&gt;"",COUNTA($J498,$L498,$N498,$P498,$R498,$T498,$V498,$X498,$Z498)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE498" s="67" t="inlineStr">
@@ -40587,7 +40600,7 @@
       <c r="AB499" s="68" t="n"/>
       <c r="AC499" s="69" t="n"/>
       <c r="AD499" s="70">
-        <f>IF(AND(COUNTIF($B$5:B499,B499)=1,$B499&lt;&gt;"",$AB499&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B499,B499)=1,$B499&lt;&gt;"",$AB499&lt;&gt;"",COUNTA($J499,$L499,$N499,$P499,$R499,$T499,$V499,$X499,$Z499)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE499" s="67" t="inlineStr">
@@ -40665,7 +40678,7 @@
       <c r="AB500" s="68" t="n"/>
       <c r="AC500" s="69" t="n"/>
       <c r="AD500" s="70">
-        <f>IF(AND(COUNTIF($B$5:B500,B500)=1,$B500&lt;&gt;"",$AB500&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B500,B500)=1,$B500&lt;&gt;"",$AB500&lt;&gt;"",COUNTA($J500,$L500,$N500,$P500,$R500,$T500,$V500,$X500,$Z500)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE500" s="67" t="inlineStr">
@@ -40743,7 +40756,7 @@
       <c r="AB501" s="68" t="n"/>
       <c r="AC501" s="69" t="n"/>
       <c r="AD501" s="70">
-        <f>IF(AND(COUNTIF($B$5:B501,B501)=1,$B501&lt;&gt;"",$AB501&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B501,B501)=1,$B501&lt;&gt;"",$AB501&lt;&gt;"",COUNTA($J501,$L501,$N501,$P501,$R501,$T501,$V501,$X501,$Z501)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE501" s="67" t="inlineStr">
@@ -40821,7 +40834,7 @@
       <c r="AB502" s="68" t="n"/>
       <c r="AC502" s="69" t="n"/>
       <c r="AD502" s="70">
-        <f>IF(AND(COUNTIF($B$5:B502,B502)=1,$B502&lt;&gt;"",$AB502&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B502,B502)=1,$B502&lt;&gt;"",$AB502&lt;&gt;"",COUNTA($J502,$L502,$N502,$P502,$R502,$T502,$V502,$X502,$Z502)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE502" s="67" t="inlineStr">
@@ -40895,7 +40908,7 @@
       <c r="AB503" s="68" t="n"/>
       <c r="AC503" s="69" t="n"/>
       <c r="AD503" s="70">
-        <f>IF(AND(COUNTIF($B$5:B503,B503)=1,$B503&lt;&gt;"",$AB503&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B503,B503)=1,$B503&lt;&gt;"",$AB503&lt;&gt;"",COUNTA($J503,$L503,$N503,$P503,$R503,$T503,$V503,$X503,$Z503)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE503" s="67" t="inlineStr">
@@ -40965,7 +40978,7 @@
       <c r="AB504" s="68" t="n"/>
       <c r="AC504" s="69" t="n"/>
       <c r="AD504" s="70">
-        <f>IF(AND(COUNTIF($B$5:B504,B504)=1,$B504&lt;&gt;"",$AB504&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B504,B504)=1,$B504&lt;&gt;"",$AB504&lt;&gt;"",COUNTA($J504,$L504,$N504,$P504,$R504,$T504,$V504,$X504,$Z504)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE504" s="67" t="inlineStr">
@@ -41007,7 +41020,7 @@
       <c r="AB505" s="68" t="n"/>
       <c r="AC505" s="69" t="n"/>
       <c r="AD505" s="70">
-        <f>IF(AND(COUNTIF($B$5:B505,B505)=1,$B505&lt;&gt;"",$AB505&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B505,B505)=1,$B505&lt;&gt;"",$AB505&lt;&gt;"",COUNTA($J505,$L505,$N505,$P505,$R505,$T505,$V505,$X505,$Z505)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE505" s="67" t="n"/>
@@ -41045,7 +41058,7 @@
       <c r="AB506" s="68" t="n"/>
       <c r="AC506" s="69" t="n"/>
       <c r="AD506" s="70">
-        <f>IF(AND(COUNTIF($B$5:B506,B506)=1,$B506&lt;&gt;"",$AB506&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B506,B506)=1,$B506&lt;&gt;"",$AB506&lt;&gt;"",COUNTA($J506,$L506,$N506,$P506,$R506,$T506,$V506,$X506,$Z506)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE506" s="67" t="n"/>
@@ -41083,7 +41096,7 @@
       <c r="AB507" s="68" t="n"/>
       <c r="AC507" s="69" t="n"/>
       <c r="AD507" s="70">
-        <f>IF(AND(COUNTIF($B$5:B507,B507)=1,$B507&lt;&gt;"",$AB507&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B507,B507)=1,$B507&lt;&gt;"",$AB507&lt;&gt;"",COUNTA($J507,$L507,$N507,$P507,$R507,$T507,$V507,$X507,$Z507)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE507" s="67" t="n"/>
@@ -41121,7 +41134,7 @@
       <c r="AB508" s="68" t="n"/>
       <c r="AC508" s="69" t="n"/>
       <c r="AD508" s="70">
-        <f>IF(AND(COUNTIF($B$5:B508,B508)=1,$B508&lt;&gt;"",$AB508&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B508,B508)=1,$B508&lt;&gt;"",$AB508&lt;&gt;"",COUNTA($J508,$L508,$N508,$P508,$R508,$T508,$V508,$X508,$Z508)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE508" s="67" t="n"/>
@@ -41159,7 +41172,7 @@
       <c r="AB509" s="68" t="n"/>
       <c r="AC509" s="69" t="n"/>
       <c r="AD509" s="70">
-        <f>IF(AND(COUNTIF($B$5:B509,B509)=1,$B509&lt;&gt;"",$AB509&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B509,B509)=1,$B509&lt;&gt;"",$AB509&lt;&gt;"",COUNTA($J509,$L509,$N509,$P509,$R509,$T509,$V509,$X509,$Z509)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE509" s="67" t="n"/>
@@ -41197,7 +41210,7 @@
       <c r="AB510" s="68" t="n"/>
       <c r="AC510" s="69" t="n"/>
       <c r="AD510" s="70">
-        <f>IF(AND(COUNTIF($B$5:B510,B510)=1,$B510&lt;&gt;"",$AB510&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B510,B510)=1,$B510&lt;&gt;"",$AB510&lt;&gt;"",COUNTA($J510,$L510,$N510,$P510,$R510,$T510,$V510,$X510,$Z510)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE510" s="67" t="n"/>
@@ -41235,7 +41248,7 @@
       <c r="AB511" s="68" t="n"/>
       <c r="AC511" s="69" t="n"/>
       <c r="AD511" s="70">
-        <f>IF(AND(COUNTIF($B$5:B511,B511)=1,$B511&lt;&gt;"",$AB511&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B511,B511)=1,$B511&lt;&gt;"",$AB511&lt;&gt;"",COUNTA($J511,$L511,$N511,$P511,$R511,$T511,$V511,$X511,$Z511)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE511" s="67" t="n"/>
@@ -41273,7 +41286,7 @@
       <c r="AB512" s="68" t="n"/>
       <c r="AC512" s="69" t="n"/>
       <c r="AD512" s="70">
-        <f>IF(AND(COUNTIF($B$5:B512,B512)=1,$B512&lt;&gt;"",$AB512&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B512,B512)=1,$B512&lt;&gt;"",$AB512&lt;&gt;"",COUNTA($J512,$L512,$N512,$P512,$R512,$T512,$V512,$X512,$Z512)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE512" s="67" t="n"/>
@@ -41311,7 +41324,7 @@
       <c r="AB513" s="68" t="n"/>
       <c r="AC513" s="69" t="n"/>
       <c r="AD513" s="70">
-        <f>IF(AND(COUNTIF($B$5:B513,B513)=1,$B513&lt;&gt;"",$AB513&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B513,B513)=1,$B513&lt;&gt;"",$AB513&lt;&gt;"",COUNTA($J513,$L513,$N513,$P513,$R513,$T513,$V513,$X513,$Z513)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE513" s="67" t="n"/>
@@ -41349,7 +41362,7 @@
       <c r="AB514" s="68" t="n"/>
       <c r="AC514" s="69" t="n"/>
       <c r="AD514" s="70">
-        <f>IF(AND(COUNTIF($B$5:B514,B514)=1,$B514&lt;&gt;"",$AB514&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B514,B514)=1,$B514&lt;&gt;"",$AB514&lt;&gt;"",COUNTA($J514,$L514,$N514,$P514,$R514,$T514,$V514,$X514,$Z514)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE514" s="67" t="n"/>
@@ -41387,7 +41400,7 @@
       <c r="AB515" s="68" t="n"/>
       <c r="AC515" s="69" t="n"/>
       <c r="AD515" s="70">
-        <f>IF(AND(COUNTIF($B$5:B515,B515)=1,$B515&lt;&gt;"",$AB515&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B515,B515)=1,$B515&lt;&gt;"",$AB515&lt;&gt;"",COUNTA($J515,$L515,$N515,$P515,$R515,$T515,$V515,$X515,$Z515)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE515" s="67" t="n"/>
@@ -41425,7 +41438,7 @@
       <c r="AB516" s="68" t="n"/>
       <c r="AC516" s="69" t="n"/>
       <c r="AD516" s="70">
-        <f>IF(AND(COUNTIF($B$5:B516,B516)=1,$B516&lt;&gt;"",$AB516&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B516,B516)=1,$B516&lt;&gt;"",$AB516&lt;&gt;"",COUNTA($J516,$L516,$N516,$P516,$R516,$T516,$V516,$X516,$Z516)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE516" s="67" t="n"/>
@@ -41463,7 +41476,7 @@
       <c r="AB517" s="68" t="n"/>
       <c r="AC517" s="69" t="n"/>
       <c r="AD517" s="70">
-        <f>IF(AND(COUNTIF($B$5:B517,B517)=1,$B517&lt;&gt;"",$AB517&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B517,B517)=1,$B517&lt;&gt;"",$AB517&lt;&gt;"",COUNTA($J517,$L517,$N517,$P517,$R517,$T517,$V517,$X517,$Z517)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE517" s="67" t="n"/>
@@ -41501,7 +41514,7 @@
       <c r="AB518" s="68" t="n"/>
       <c r="AC518" s="69" t="n"/>
       <c r="AD518" s="70">
-        <f>IF(AND(COUNTIF($B$5:B518,B518)=1,$B518&lt;&gt;"",$AB518&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B518,B518)=1,$B518&lt;&gt;"",$AB518&lt;&gt;"",COUNTA($J518,$L518,$N518,$P518,$R518,$T518,$V518,$X518,$Z518)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE518" s="67" t="n"/>
@@ -41539,7 +41552,7 @@
       <c r="AB519" s="68" t="n"/>
       <c r="AC519" s="69" t="n"/>
       <c r="AD519" s="70">
-        <f>IF(AND(COUNTIF($B$5:B519,B519)=1,$B519&lt;&gt;"",$AB519&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B519,B519)=1,$B519&lt;&gt;"",$AB519&lt;&gt;"",COUNTA($J519,$L519,$N519,$P519,$R519,$T519,$V519,$X519,$Z519)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE519" s="67" t="n"/>
@@ -41577,7 +41590,7 @@
       <c r="AB520" s="68" t="n"/>
       <c r="AC520" s="69" t="n"/>
       <c r="AD520" s="70">
-        <f>IF(AND(COUNTIF($B$5:B520,B520)=1,$B520&lt;&gt;"",$AB520&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B520,B520)=1,$B520&lt;&gt;"",$AB520&lt;&gt;"",COUNTA($J520,$L520,$N520,$P520,$R520,$T520,$V520,$X520,$Z520)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE520" s="67" t="n"/>
@@ -41615,7 +41628,7 @@
       <c r="AB521" s="68" t="n"/>
       <c r="AC521" s="69" t="n"/>
       <c r="AD521" s="70">
-        <f>IF(AND(COUNTIF($B$5:B521,B521)=1,$B521&lt;&gt;"",$AB521&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B521,B521)=1,$B521&lt;&gt;"",$AB521&lt;&gt;"",COUNTA($J521,$L521,$N521,$P521,$R521,$T521,$V521,$X521,$Z521)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE521" s="67" t="n"/>
@@ -41653,7 +41666,7 @@
       <c r="AB522" s="68" t="n"/>
       <c r="AC522" s="69" t="n"/>
       <c r="AD522" s="70">
-        <f>IF(AND(COUNTIF($B$5:B522,B522)=1,$B522&lt;&gt;"",$AB522&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B522,B522)=1,$B522&lt;&gt;"",$AB522&lt;&gt;"",COUNTA($J522,$L522,$N522,$P522,$R522,$T522,$V522,$X522,$Z522)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE522" s="67" t="n"/>
@@ -41691,7 +41704,7 @@
       <c r="AB523" s="68" t="n"/>
       <c r="AC523" s="69" t="n"/>
       <c r="AD523" s="70">
-        <f>IF(AND(COUNTIF($B$5:B523,B523)=1,$B523&lt;&gt;"",$AB523&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B523,B523)=1,$B523&lt;&gt;"",$AB523&lt;&gt;"",COUNTA($J523,$L523,$N523,$P523,$R523,$T523,$V523,$X523,$Z523)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE523" s="67" t="n"/>
@@ -41729,7 +41742,7 @@
       <c r="AB524" s="68" t="n"/>
       <c r="AC524" s="69" t="n"/>
       <c r="AD524" s="70">
-        <f>IF(AND(COUNTIF($B$5:B524,B524)=1,$B524&lt;&gt;"",$AB524&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B524,B524)=1,$B524&lt;&gt;"",$AB524&lt;&gt;"",COUNTA($J524,$L524,$N524,$P524,$R524,$T524,$V524,$X524,$Z524)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE524" s="67" t="n"/>
@@ -41767,7 +41780,7 @@
       <c r="AB525" s="68" t="n"/>
       <c r="AC525" s="69" t="n"/>
       <c r="AD525" s="70">
-        <f>IF(AND(COUNTIF($B$5:B525,B525)=1,$B525&lt;&gt;"",$AB525&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B525,B525)=1,$B525&lt;&gt;"",$AB525&lt;&gt;"",COUNTA($J525,$L525,$N525,$P525,$R525,$T525,$V525,$X525,$Z525)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE525" s="67" t="n"/>
@@ -41805,7 +41818,7 @@
       <c r="AB526" s="68" t="n"/>
       <c r="AC526" s="69" t="n"/>
       <c r="AD526" s="70">
-        <f>IF(AND(COUNTIF($B$5:B526,B526)=1,$B526&lt;&gt;"",$AB526&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B526,B526)=1,$B526&lt;&gt;"",$AB526&lt;&gt;"",COUNTA($J526,$L526,$N526,$P526,$R526,$T526,$V526,$X526,$Z526)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE526" s="67" t="n"/>
@@ -41843,7 +41856,7 @@
       <c r="AB527" s="68" t="n"/>
       <c r="AC527" s="69" t="n"/>
       <c r="AD527" s="70">
-        <f>IF(AND(COUNTIF($B$5:B527,B527)=1,$B527&lt;&gt;"",$AB527&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B527,B527)=1,$B527&lt;&gt;"",$AB527&lt;&gt;"",COUNTA($J527,$L527,$N527,$P527,$R527,$T527,$V527,$X527,$Z527)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE527" s="67" t="n"/>
@@ -41881,7 +41894,7 @@
       <c r="AB528" s="68" t="n"/>
       <c r="AC528" s="69" t="n"/>
       <c r="AD528" s="70">
-        <f>IF(AND(COUNTIF($B$5:B528,B528)=1,$B528&lt;&gt;"",$AB528&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B528,B528)=1,$B528&lt;&gt;"",$AB528&lt;&gt;"",COUNTA($J528,$L528,$N528,$P528,$R528,$T528,$V528,$X528,$Z528)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE528" s="67" t="n"/>
@@ -41919,7 +41932,7 @@
       <c r="AB529" s="68" t="n"/>
       <c r="AC529" s="69" t="n"/>
       <c r="AD529" s="70">
-        <f>IF(AND(COUNTIF($B$5:B529,B529)=1,$B529&lt;&gt;"",$AB529&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B529,B529)=1,$B529&lt;&gt;"",$AB529&lt;&gt;"",COUNTA($J529,$L529,$N529,$P529,$R529,$T529,$V529,$X529,$Z529)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE529" s="67" t="n"/>
@@ -41957,7 +41970,7 @@
       <c r="AB530" s="68" t="n"/>
       <c r="AC530" s="69" t="n"/>
       <c r="AD530" s="70">
-        <f>IF(AND(COUNTIF($B$5:B530,B530)=1,$B530&lt;&gt;"",$AB530&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B530,B530)=1,$B530&lt;&gt;"",$AB530&lt;&gt;"",COUNTA($J530,$L530,$N530,$P530,$R530,$T530,$V530,$X530,$Z530)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE530" s="67" t="n"/>
@@ -41995,7 +42008,7 @@
       <c r="AB531" s="68" t="n"/>
       <c r="AC531" s="69" t="n"/>
       <c r="AD531" s="70">
-        <f>IF(AND(COUNTIF($B$5:B531,B531)=1,$B531&lt;&gt;"",$AB531&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B531,B531)=1,$B531&lt;&gt;"",$AB531&lt;&gt;"",COUNTA($J531,$L531,$N531,$P531,$R531,$T531,$V531,$X531,$Z531)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE531" s="67" t="n"/>
@@ -42033,7 +42046,7 @@
       <c r="AB532" s="68" t="n"/>
       <c r="AC532" s="69" t="n"/>
       <c r="AD532" s="70">
-        <f>IF(AND(COUNTIF($B$5:B532,B532)=1,$B532&lt;&gt;"",$AB532&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B532,B532)=1,$B532&lt;&gt;"",$AB532&lt;&gt;"",COUNTA($J532,$L532,$N532,$P532,$R532,$T532,$V532,$X532,$Z532)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE532" s="67" t="n"/>
@@ -42071,7 +42084,7 @@
       <c r="AB533" s="68" t="n"/>
       <c r="AC533" s="69" t="n"/>
       <c r="AD533" s="70">
-        <f>IF(AND(COUNTIF($B$5:B533,B533)=1,$B533&lt;&gt;"",$AB533&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B533,B533)=1,$B533&lt;&gt;"",$AB533&lt;&gt;"",COUNTA($J533,$L533,$N533,$P533,$R533,$T533,$V533,$X533,$Z533)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE533" s="67" t="n"/>
@@ -42109,7 +42122,7 @@
       <c r="AB534" s="68" t="n"/>
       <c r="AC534" s="69" t="n"/>
       <c r="AD534" s="70">
-        <f>IF(AND(COUNTIF($B$5:B534,B534)=1,$B534&lt;&gt;"",$AB534&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B534,B534)=1,$B534&lt;&gt;"",$AB534&lt;&gt;"",COUNTA($J534,$L534,$N534,$P534,$R534,$T534,$V534,$X534,$Z534)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE534" s="67" t="n"/>
@@ -42147,7 +42160,7 @@
       <c r="AB535" s="68" t="n"/>
       <c r="AC535" s="69" t="n"/>
       <c r="AD535" s="70">
-        <f>IF(AND(COUNTIF($B$5:B535,B535)=1,$B535&lt;&gt;"",$AB535&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B535,B535)=1,$B535&lt;&gt;"",$AB535&lt;&gt;"",COUNTA($J535,$L535,$N535,$P535,$R535,$T535,$V535,$X535,$Z535)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE535" s="67" t="n"/>
@@ -42185,7 +42198,7 @@
       <c r="AB536" s="68" t="n"/>
       <c r="AC536" s="69" t="n"/>
       <c r="AD536" s="70">
-        <f>IF(AND(COUNTIF($B$5:B536,B536)=1,$B536&lt;&gt;"",$AB536&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B536,B536)=1,$B536&lt;&gt;"",$AB536&lt;&gt;"",COUNTA($J536,$L536,$N536,$P536,$R536,$T536,$V536,$X536,$Z536)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE536" s="67" t="n"/>
@@ -42223,7 +42236,7 @@
       <c r="AB537" s="68" t="n"/>
       <c r="AC537" s="69" t="n"/>
       <c r="AD537" s="70">
-        <f>IF(AND(COUNTIF($B$5:B537,B537)=1,$B537&lt;&gt;"",$AB537&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B537,B537)=1,$B537&lt;&gt;"",$AB537&lt;&gt;"",COUNTA($J537,$L537,$N537,$P537,$R537,$T537,$V537,$X537,$Z537)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE537" s="67" t="n"/>
@@ -42261,7 +42274,7 @@
       <c r="AB538" s="68" t="n"/>
       <c r="AC538" s="69" t="n"/>
       <c r="AD538" s="70">
-        <f>IF(AND(COUNTIF($B$5:B538,B538)=1,$B538&lt;&gt;"",$AB538&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B538,B538)=1,$B538&lt;&gt;"",$AB538&lt;&gt;"",COUNTA($J538,$L538,$N538,$P538,$R538,$T538,$V538,$X538,$Z538)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE538" s="67" t="n"/>
@@ -42299,7 +42312,7 @@
       <c r="AB539" s="68" t="n"/>
       <c r="AC539" s="69" t="n"/>
       <c r="AD539" s="70">
-        <f>IF(AND(COUNTIF($B$5:B539,B539)=1,$B539&lt;&gt;"",$AB539&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B539,B539)=1,$B539&lt;&gt;"",$AB539&lt;&gt;"",COUNTA($J539,$L539,$N539,$P539,$R539,$T539,$V539,$X539,$Z539)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE539" s="67" t="n"/>
@@ -42337,7 +42350,7 @@
       <c r="AB540" s="68" t="n"/>
       <c r="AC540" s="69" t="n"/>
       <c r="AD540" s="70">
-        <f>IF(AND(COUNTIF($B$5:B540,B540)=1,$B540&lt;&gt;"",$AB540&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B540,B540)=1,$B540&lt;&gt;"",$AB540&lt;&gt;"",COUNTA($J540,$L540,$N540,$P540,$R540,$T540,$V540,$X540,$Z540)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE540" s="67" t="n"/>
@@ -42375,7 +42388,7 @@
       <c r="AB541" s="68" t="n"/>
       <c r="AC541" s="69" t="n"/>
       <c r="AD541" s="70">
-        <f>IF(AND(COUNTIF($B$5:B541,B541)=1,$B541&lt;&gt;"",$AB541&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B541,B541)=1,$B541&lt;&gt;"",$AB541&lt;&gt;"",COUNTA($J541,$L541,$N541,$P541,$R541,$T541,$V541,$X541,$Z541)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE541" s="67" t="n"/>
@@ -42413,7 +42426,7 @@
       <c r="AB542" s="68" t="n"/>
       <c r="AC542" s="69" t="n"/>
       <c r="AD542" s="70">
-        <f>IF(AND(COUNTIF($B$5:B542,B542)=1,$B542&lt;&gt;"",$AB542&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B542,B542)=1,$B542&lt;&gt;"",$AB542&lt;&gt;"",COUNTA($J542,$L542,$N542,$P542,$R542,$T542,$V542,$X542,$Z542)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE542" s="67" t="n"/>
@@ -42451,7 +42464,7 @@
       <c r="AB543" s="68" t="n"/>
       <c r="AC543" s="69" t="n"/>
       <c r="AD543" s="70">
-        <f>IF(AND(COUNTIF($B$5:B543,B543)=1,$B543&lt;&gt;"",$AB543&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B543,B543)=1,$B543&lt;&gt;"",$AB543&lt;&gt;"",COUNTA($J543,$L543,$N543,$P543,$R543,$T543,$V543,$X543,$Z543)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE543" s="67" t="n"/>
@@ -42489,7 +42502,7 @@
       <c r="AB544" s="68" t="n"/>
       <c r="AC544" s="69" t="n"/>
       <c r="AD544" s="70">
-        <f>IF(AND(COUNTIF($B$5:B544,B544)=1,$B544&lt;&gt;"",$AB544&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B544,B544)=1,$B544&lt;&gt;"",$AB544&lt;&gt;"",COUNTA($J544,$L544,$N544,$P544,$R544,$T544,$V544,$X544,$Z544)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE544" s="67" t="n"/>
@@ -42527,7 +42540,7 @@
       <c r="AB545" s="68" t="n"/>
       <c r="AC545" s="69" t="n"/>
       <c r="AD545" s="70">
-        <f>IF(AND(COUNTIF($B$5:B545,B545)=1,$B545&lt;&gt;"",$AB545&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B545,B545)=1,$B545&lt;&gt;"",$AB545&lt;&gt;"",COUNTA($J545,$L545,$N545,$P545,$R545,$T545,$V545,$X545,$Z545)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE545" s="67" t="n"/>
@@ -42565,7 +42578,7 @@
       <c r="AB546" s="68" t="n"/>
       <c r="AC546" s="69" t="n"/>
       <c r="AD546" s="70">
-        <f>IF(AND(COUNTIF($B$5:B546,B546)=1,$B546&lt;&gt;"",$AB546&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B546,B546)=1,$B546&lt;&gt;"",$AB546&lt;&gt;"",COUNTA($J546,$L546,$N546,$P546,$R546,$T546,$V546,$X546,$Z546)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE546" s="67" t="n"/>
@@ -42603,7 +42616,7 @@
       <c r="AB547" s="68" t="n"/>
       <c r="AC547" s="69" t="n"/>
       <c r="AD547" s="70">
-        <f>IF(AND(COUNTIF($B$5:B547,B547)=1,$B547&lt;&gt;"",$AB547&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B547,B547)=1,$B547&lt;&gt;"",$AB547&lt;&gt;"",COUNTA($J547,$L547,$N547,$P547,$R547,$T547,$V547,$X547,$Z547)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE547" s="67" t="n"/>
@@ -42641,7 +42654,7 @@
       <c r="AB548" s="68" t="n"/>
       <c r="AC548" s="69" t="n"/>
       <c r="AD548" s="70">
-        <f>IF(AND(COUNTIF($B$5:B548,B548)=1,$B548&lt;&gt;"",$AB548&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B548,B548)=1,$B548&lt;&gt;"",$AB548&lt;&gt;"",COUNTA($J548,$L548,$N548,$P548,$R548,$T548,$V548,$X548,$Z548)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE548" s="67" t="n"/>
@@ -42679,7 +42692,7 @@
       <c r="AB549" s="68" t="n"/>
       <c r="AC549" s="69" t="n"/>
       <c r="AD549" s="70">
-        <f>IF(AND(COUNTIF($B$5:B549,B549)=1,$B549&lt;&gt;"",$AB549&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B549,B549)=1,$B549&lt;&gt;"",$AB549&lt;&gt;"",COUNTA($J549,$L549,$N549,$P549,$R549,$T549,$V549,$X549,$Z549)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE549" s="67" t="n"/>
@@ -42717,7 +42730,7 @@
       <c r="AB550" s="68" t="n"/>
       <c r="AC550" s="69" t="n"/>
       <c r="AD550" s="70">
-        <f>IF(AND(COUNTIF($B$5:B550,B550)=1,$B550&lt;&gt;"",$AB550&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B550,B550)=1,$B550&lt;&gt;"",$AB550&lt;&gt;"",COUNTA($J550,$L550,$N550,$P550,$R550,$T550,$V550,$X550,$Z550)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE550" s="67" t="n"/>
@@ -42755,7 +42768,7 @@
       <c r="AB551" s="68" t="n"/>
       <c r="AC551" s="69" t="n"/>
       <c r="AD551" s="70">
-        <f>IF(AND(COUNTIF($B$5:B551,B551)=1,$B551&lt;&gt;"",$AB551&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B551,B551)=1,$B551&lt;&gt;"",$AB551&lt;&gt;"",COUNTA($J551,$L551,$N551,$P551,$R551,$T551,$V551,$X551,$Z551)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE551" s="67" t="n"/>
@@ -42793,7 +42806,7 @@
       <c r="AB552" s="68" t="n"/>
       <c r="AC552" s="69" t="n"/>
       <c r="AD552" s="70">
-        <f>IF(AND(COUNTIF($B$5:B552,B552)=1,$B552&lt;&gt;"",$AB552&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B552,B552)=1,$B552&lt;&gt;"",$AB552&lt;&gt;"",COUNTA($J552,$L552,$N552,$P552,$R552,$T552,$V552,$X552,$Z552)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE552" s="67" t="n"/>
@@ -42831,7 +42844,7 @@
       <c r="AB553" s="68" t="n"/>
       <c r="AC553" s="69" t="n"/>
       <c r="AD553" s="70">
-        <f>IF(AND(COUNTIF($B$5:B553,B553)=1,$B553&lt;&gt;"",$AB553&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B553,B553)=1,$B553&lt;&gt;"",$AB553&lt;&gt;"",COUNTA($J553,$L553,$N553,$P553,$R553,$T553,$V553,$X553,$Z553)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE553" s="67" t="n"/>
@@ -42869,7 +42882,7 @@
       <c r="AB554" s="68" t="n"/>
       <c r="AC554" s="69" t="n"/>
       <c r="AD554" s="70">
-        <f>IF(AND(COUNTIF($B$5:B554,B554)=1,$B554&lt;&gt;"",$AB554&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B554,B554)=1,$B554&lt;&gt;"",$AB554&lt;&gt;"",COUNTA($J554,$L554,$N554,$P554,$R554,$T554,$V554,$X554,$Z554)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE554" s="67" t="n"/>
@@ -42907,7 +42920,7 @@
       <c r="AB555" s="68" t="n"/>
       <c r="AC555" s="69" t="n"/>
       <c r="AD555" s="70">
-        <f>IF(AND(COUNTIF($B$5:B555,B555)=1,$B555&lt;&gt;"",$AB555&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B555,B555)=1,$B555&lt;&gt;"",$AB555&lt;&gt;"",COUNTA($J555,$L555,$N555,$P555,$R555,$T555,$V555,$X555,$Z555)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE555" s="67" t="n"/>
@@ -42945,7 +42958,7 @@
       <c r="AB556" s="68" t="n"/>
       <c r="AC556" s="69" t="n"/>
       <c r="AD556" s="70">
-        <f>IF(AND(COUNTIF($B$5:B556,B556)=1,$B556&lt;&gt;"",$AB556&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B556,B556)=1,$B556&lt;&gt;"",$AB556&lt;&gt;"",COUNTA($J556,$L556,$N556,$P556,$R556,$T556,$V556,$X556,$Z556)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE556" s="67" t="n"/>
@@ -42983,7 +42996,7 @@
       <c r="AB557" s="68" t="n"/>
       <c r="AC557" s="69" t="n"/>
       <c r="AD557" s="70">
-        <f>IF(AND(COUNTIF($B$5:B557,B557)=1,$B557&lt;&gt;"",$AB557&lt;&gt;""),1,0)</f>
+        <f>IF(AND(COUNTIF($B$5:B557,B557)=1,$B557&lt;&gt;"",$AB557&lt;&gt;"",COUNTA($J557,$L557,$N557,$P557,$R557,$T557,$V557,$X557,$Z557)=9),1,0)</f>
         <v/>
       </c>
       <c r="AE557" s="67" t="n"/>
@@ -42995,6 +43008,11 @@
     <mergeCell ref="A1:AE1"/>
     <mergeCell ref="A2:AE2"/>
   </mergeCells>
+  <conditionalFormatting sqref="AC5:AC557">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>OR(AND($AB5="neutral",$AC5&lt;&gt;""),AND($AB5&lt;&gt;"",$AB5&lt;&gt;"neutral",$AC5=""))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation sqref="C5:C557" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Infobae Colombia,El Tiempo,El Espectador,La Silla Vacía,Semana"</formula1>
